--- a/multas/Registro_Multas_Propietarios.xlsx
+++ b/multas/Registro_Multas_Propietarios.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
   <si>
     <t xml:space="preserve">CÓMO SE USA</t>
   </si>
@@ -53,6 +53,9 @@
     <t xml:space="preserve">6. IMPORTANTE: no borrar ni ordenar filas en 'Carga Vigilador'; si un acta se anula, escribirlo en Observaciones.</t>
   </si>
   <si>
+    <t xml:space="preserve">6b. Si un relato es muy largo y no entra en la celda de Administración, hacer clic en la celda: el texto completo aparece en la barra de fórmulas.</t>
+  </si>
+  <si>
     <t xml:space="preserve">7. La fila 4 tiene de ejemplo el acta del 13/10/2026 (lote 92). Reemplazar el nombre del vigilador.</t>
   </si>
   <si>
@@ -60,6 +63,9 @@
   </si>
   <si>
     <t xml:space="preserve">Subir el archivo → Abrir con Hojas de cálculo de Google → Archivo → Guardar como Hojas de cálculo de Google.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OJO: la vista previa de Drive (sin convertir) NO actualiza las fórmulas; hay que trabajar sobre la versión convertida a Hojas de cálculo de Google.</t>
   </si>
   <si>
     <t xml:space="preserve">Recomendado: Datos → Proteger hojas y rangos, para que la guardia solo edite 'Carga Vigilador' y la administración 'Carga Administración'.</t>
@@ -833,7 +839,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="105"/>
@@ -888,21 +894,31 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-    </row>
-    <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -935,35 +951,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -978,16 +994,16 @@
         <v>0.534027777777778</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E4" s="10" t="n">
         <v>92</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7011,7 +7027,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="70"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
@@ -7023,56 +7039,56 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7115,7 +7131,7 @@
         <v>Pendiente</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A5="","",'Carga Vigilador'!A5)</f>
         <v/>
@@ -7155,7 +7171,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A6="","",'Carga Vigilador'!A6)</f>
         <v/>
@@ -7195,7 +7211,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A7="","",'Carga Vigilador'!A7)</f>
         <v/>
@@ -7235,7 +7251,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A8="","",'Carga Vigilador'!A8)</f>
         <v/>
@@ -7275,7 +7291,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A9="","",'Carga Vigilador'!A9)</f>
         <v/>
@@ -7315,7 +7331,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A10="","",'Carga Vigilador'!A10)</f>
         <v/>
@@ -7355,7 +7371,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A11="","",'Carga Vigilador'!A11)</f>
         <v/>
@@ -7395,7 +7411,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A12="","",'Carga Vigilador'!A12)</f>
         <v/>
@@ -7435,7 +7451,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A13="","",'Carga Vigilador'!A13)</f>
         <v/>
@@ -7475,7 +7491,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A14="","",'Carga Vigilador'!A14)</f>
         <v/>
@@ -7515,7 +7531,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A15="","",'Carga Vigilador'!A15)</f>
         <v/>
@@ -7555,7 +7571,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A16="","",'Carga Vigilador'!A16)</f>
         <v/>
@@ -7595,7 +7611,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A17="","",'Carga Vigilador'!A17)</f>
         <v/>
@@ -7635,7 +7651,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A18="","",'Carga Vigilador'!A18)</f>
         <v/>
@@ -7675,7 +7691,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A19="","",'Carga Vigilador'!A19)</f>
         <v/>
@@ -7715,7 +7731,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A20="","",'Carga Vigilador'!A20)</f>
         <v/>
@@ -7755,7 +7771,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A21="","",'Carga Vigilador'!A21)</f>
         <v/>
@@ -7795,7 +7811,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A22="","",'Carga Vigilador'!A22)</f>
         <v/>
@@ -7835,7 +7851,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A23="","",'Carga Vigilador'!A23)</f>
         <v/>
@@ -7875,7 +7891,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A24="","",'Carga Vigilador'!A24)</f>
         <v/>
@@ -7915,7 +7931,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A25="","",'Carga Vigilador'!A25)</f>
         <v/>
@@ -7955,7 +7971,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A26="","",'Carga Vigilador'!A26)</f>
         <v/>
@@ -7995,7 +8011,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A27="","",'Carga Vigilador'!A27)</f>
         <v/>
@@ -8035,7 +8051,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A28="","",'Carga Vigilador'!A28)</f>
         <v/>
@@ -8075,7 +8091,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A29="","",'Carga Vigilador'!A29)</f>
         <v/>
@@ -8115,7 +8131,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A30="","",'Carga Vigilador'!A30)</f>
         <v/>
@@ -8155,7 +8171,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A31="","",'Carga Vigilador'!A31)</f>
         <v/>
@@ -8195,7 +8211,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A32="","",'Carga Vigilador'!A32)</f>
         <v/>
@@ -8235,7 +8251,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A33="","",'Carga Vigilador'!A33)</f>
         <v/>
@@ -8275,7 +8291,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A34="","",'Carga Vigilador'!A34)</f>
         <v/>
@@ -8315,7 +8331,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A35="","",'Carga Vigilador'!A35)</f>
         <v/>
@@ -8355,7 +8371,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A36="","",'Carga Vigilador'!A36)</f>
         <v/>
@@ -8395,7 +8411,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A37="","",'Carga Vigilador'!A37)</f>
         <v/>
@@ -8435,7 +8451,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A38="","",'Carga Vigilador'!A38)</f>
         <v/>
@@ -8475,7 +8491,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A39="","",'Carga Vigilador'!A39)</f>
         <v/>
@@ -8515,7 +8531,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A40="","",'Carga Vigilador'!A40)</f>
         <v/>
@@ -8555,7 +8571,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A41="","",'Carga Vigilador'!A41)</f>
         <v/>
@@ -8595,7 +8611,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A42="","",'Carga Vigilador'!A42)</f>
         <v/>
@@ -8635,7 +8651,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A43="","",'Carga Vigilador'!A43)</f>
         <v/>
@@ -8675,7 +8691,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A44="","",'Carga Vigilador'!A44)</f>
         <v/>
@@ -8715,7 +8731,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A45="","",'Carga Vigilador'!A45)</f>
         <v/>
@@ -8755,7 +8771,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A46="","",'Carga Vigilador'!A46)</f>
         <v/>
@@ -8795,7 +8811,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A47="","",'Carga Vigilador'!A47)</f>
         <v/>
@@ -8835,7 +8851,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A48="","",'Carga Vigilador'!A48)</f>
         <v/>
@@ -8875,7 +8891,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A49="","",'Carga Vigilador'!A49)</f>
         <v/>
@@ -8915,7 +8931,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A50="","",'Carga Vigilador'!A50)</f>
         <v/>
@@ -8955,7 +8971,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A51="","",'Carga Vigilador'!A51)</f>
         <v/>
@@ -8995,7 +9011,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A52="","",'Carga Vigilador'!A52)</f>
         <v/>
@@ -9035,7 +9051,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A53="","",'Carga Vigilador'!A53)</f>
         <v/>
@@ -9075,7 +9091,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A54="","",'Carga Vigilador'!A54)</f>
         <v/>
@@ -9115,7 +9131,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A55="","",'Carga Vigilador'!A55)</f>
         <v/>
@@ -9155,7 +9171,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A56="","",'Carga Vigilador'!A56)</f>
         <v/>
@@ -9195,7 +9211,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A57="","",'Carga Vigilador'!A57)</f>
         <v/>
@@ -9235,7 +9251,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A58="","",'Carga Vigilador'!A58)</f>
         <v/>
@@ -9275,7 +9291,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A59="","",'Carga Vigilador'!A59)</f>
         <v/>
@@ -9315,7 +9331,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A60="","",'Carga Vigilador'!A60)</f>
         <v/>
@@ -9355,7 +9371,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A61="","",'Carga Vigilador'!A61)</f>
         <v/>
@@ -9395,7 +9411,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A62="","",'Carga Vigilador'!A62)</f>
         <v/>
@@ -9435,7 +9451,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A63="","",'Carga Vigilador'!A63)</f>
         <v/>
@@ -9475,7 +9491,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A64="","",'Carga Vigilador'!A64)</f>
         <v/>
@@ -9515,7 +9531,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A65="","",'Carga Vigilador'!A65)</f>
         <v/>
@@ -9555,7 +9571,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A66="","",'Carga Vigilador'!A66)</f>
         <v/>
@@ -9595,7 +9611,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A67="","",'Carga Vigilador'!A67)</f>
         <v/>
@@ -9635,7 +9651,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A68="","",'Carga Vigilador'!A68)</f>
         <v/>
@@ -9675,7 +9691,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A69="","",'Carga Vigilador'!A69)</f>
         <v/>
@@ -9715,7 +9731,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A70="","",'Carga Vigilador'!A70)</f>
         <v/>
@@ -9755,7 +9771,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A71="","",'Carga Vigilador'!A71)</f>
         <v/>
@@ -9795,7 +9811,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A72="","",'Carga Vigilador'!A72)</f>
         <v/>
@@ -9835,7 +9851,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A73="","",'Carga Vigilador'!A73)</f>
         <v/>
@@ -9875,7 +9891,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A74="","",'Carga Vigilador'!A74)</f>
         <v/>
@@ -9915,7 +9931,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A75="","",'Carga Vigilador'!A75)</f>
         <v/>
@@ -9955,7 +9971,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A76="","",'Carga Vigilador'!A76)</f>
         <v/>
@@ -9995,7 +10011,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A77="","",'Carga Vigilador'!A77)</f>
         <v/>
@@ -10035,7 +10051,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A78="","",'Carga Vigilador'!A78)</f>
         <v/>
@@ -10075,7 +10091,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A79="","",'Carga Vigilador'!A79)</f>
         <v/>
@@ -10115,7 +10131,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A80="","",'Carga Vigilador'!A80)</f>
         <v/>
@@ -10155,7 +10171,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A81="","",'Carga Vigilador'!A81)</f>
         <v/>
@@ -10195,7 +10211,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A82="","",'Carga Vigilador'!A82)</f>
         <v/>
@@ -10235,7 +10251,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A83="","",'Carga Vigilador'!A83)</f>
         <v/>
@@ -10275,7 +10291,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A84="","",'Carga Vigilador'!A84)</f>
         <v/>
@@ -10315,7 +10331,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A85="","",'Carga Vigilador'!A85)</f>
         <v/>
@@ -10355,7 +10371,7 @@
         <v/>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A86="","",'Carga Vigilador'!A86)</f>
         <v/>
@@ -10395,7 +10411,7 @@
         <v/>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A87="","",'Carga Vigilador'!A87)</f>
         <v/>
@@ -10435,7 +10451,7 @@
         <v/>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A88="","",'Carga Vigilador'!A88)</f>
         <v/>
@@ -10475,7 +10491,7 @@
         <v/>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A89="","",'Carga Vigilador'!A89)</f>
         <v/>
@@ -10515,7 +10531,7 @@
         <v/>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A90="","",'Carga Vigilador'!A90)</f>
         <v/>
@@ -10555,7 +10571,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A91="","",'Carga Vigilador'!A91)</f>
         <v/>
@@ -10595,7 +10611,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A92="","",'Carga Vigilador'!A92)</f>
         <v/>
@@ -10635,7 +10651,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A93="","",'Carga Vigilador'!A93)</f>
         <v/>
@@ -10675,7 +10691,7 @@
         <v/>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A94="","",'Carga Vigilador'!A94)</f>
         <v/>
@@ -10715,7 +10731,7 @@
         <v/>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A95="","",'Carga Vigilador'!A95)</f>
         <v/>
@@ -10755,7 +10771,7 @@
         <v/>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A96="","",'Carga Vigilador'!A96)</f>
         <v/>
@@ -10795,7 +10811,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A97="","",'Carga Vigilador'!A97)</f>
         <v/>
@@ -10835,7 +10851,7 @@
         <v/>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A98="","",'Carga Vigilador'!A98)</f>
         <v/>
@@ -10875,7 +10891,7 @@
         <v/>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A99="","",'Carga Vigilador'!A99)</f>
         <v/>
@@ -10915,7 +10931,7 @@
         <v/>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A100="","",'Carga Vigilador'!A100)</f>
         <v/>
@@ -10955,7 +10971,7 @@
         <v/>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A101="","",'Carga Vigilador'!A101)</f>
         <v/>
@@ -10995,7 +11011,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A102="","",'Carga Vigilador'!A102)</f>
         <v/>
@@ -11035,7 +11051,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A103="","",'Carga Vigilador'!A103)</f>
         <v/>
@@ -11075,7 +11091,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A104="","",'Carga Vigilador'!A104)</f>
         <v/>
@@ -11115,7 +11131,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A105="","",'Carga Vigilador'!A105)</f>
         <v/>
@@ -11155,7 +11171,7 @@
         <v/>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A106="","",'Carga Vigilador'!A106)</f>
         <v/>
@@ -11195,7 +11211,7 @@
         <v/>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A107="","",'Carga Vigilador'!A107)</f>
         <v/>
@@ -11235,7 +11251,7 @@
         <v/>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A108="","",'Carga Vigilador'!A108)</f>
         <v/>
@@ -11275,7 +11291,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A109="","",'Carga Vigilador'!A109)</f>
         <v/>
@@ -11315,7 +11331,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A110="","",'Carga Vigilador'!A110)</f>
         <v/>
@@ -11355,7 +11371,7 @@
         <v/>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A111="","",'Carga Vigilador'!A111)</f>
         <v/>
@@ -11395,7 +11411,7 @@
         <v/>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A112="","",'Carga Vigilador'!A112)</f>
         <v/>
@@ -11435,7 +11451,7 @@
         <v/>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A113="","",'Carga Vigilador'!A113)</f>
         <v/>
@@ -11475,7 +11491,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A114="","",'Carga Vigilador'!A114)</f>
         <v/>
@@ -11515,7 +11531,7 @@
         <v/>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A115="","",'Carga Vigilador'!A115)</f>
         <v/>
@@ -11555,7 +11571,7 @@
         <v/>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A116="","",'Carga Vigilador'!A116)</f>
         <v/>
@@ -11595,7 +11611,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A117="","",'Carga Vigilador'!A117)</f>
         <v/>
@@ -11635,7 +11651,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A118="","",'Carga Vigilador'!A118)</f>
         <v/>
@@ -11675,7 +11691,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A119="","",'Carga Vigilador'!A119)</f>
         <v/>
@@ -11715,7 +11731,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A120="","",'Carga Vigilador'!A120)</f>
         <v/>
@@ -11755,7 +11771,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A121="","",'Carga Vigilador'!A121)</f>
         <v/>
@@ -11795,7 +11811,7 @@
         <v/>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A122="","",'Carga Vigilador'!A122)</f>
         <v/>
@@ -11835,7 +11851,7 @@
         <v/>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A123="","",'Carga Vigilador'!A123)</f>
         <v/>
@@ -11875,7 +11891,7 @@
         <v/>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A124="","",'Carga Vigilador'!A124)</f>
         <v/>
@@ -11915,7 +11931,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A125="","",'Carga Vigilador'!A125)</f>
         <v/>
@@ -11955,7 +11971,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A126="","",'Carga Vigilador'!A126)</f>
         <v/>
@@ -11995,7 +12011,7 @@
         <v/>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A127="","",'Carga Vigilador'!A127)</f>
         <v/>
@@ -12035,7 +12051,7 @@
         <v/>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A128="","",'Carga Vigilador'!A128)</f>
         <v/>
@@ -12075,7 +12091,7 @@
         <v/>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A129="","",'Carga Vigilador'!A129)</f>
         <v/>
@@ -12115,7 +12131,7 @@
         <v/>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A130="","",'Carga Vigilador'!A130)</f>
         <v/>
@@ -12155,7 +12171,7 @@
         <v/>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A131="","",'Carga Vigilador'!A131)</f>
         <v/>
@@ -12195,7 +12211,7 @@
         <v/>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A132="","",'Carga Vigilador'!A132)</f>
         <v/>
@@ -12235,7 +12251,7 @@
         <v/>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A133="","",'Carga Vigilador'!A133)</f>
         <v/>
@@ -12275,7 +12291,7 @@
         <v/>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A134="","",'Carga Vigilador'!A134)</f>
         <v/>
@@ -12315,7 +12331,7 @@
         <v/>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A135="","",'Carga Vigilador'!A135)</f>
         <v/>
@@ -12355,7 +12371,7 @@
         <v/>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A136="","",'Carga Vigilador'!A136)</f>
         <v/>
@@ -12395,7 +12411,7 @@
         <v/>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A137="","",'Carga Vigilador'!A137)</f>
         <v/>
@@ -12435,7 +12451,7 @@
         <v/>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A138="","",'Carga Vigilador'!A138)</f>
         <v/>
@@ -12475,7 +12491,7 @@
         <v/>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A139="","",'Carga Vigilador'!A139)</f>
         <v/>
@@ -12515,7 +12531,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A140="","",'Carga Vigilador'!A140)</f>
         <v/>
@@ -12555,7 +12571,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A141="","",'Carga Vigilador'!A141)</f>
         <v/>
@@ -12595,7 +12611,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A142="","",'Carga Vigilador'!A142)</f>
         <v/>
@@ -12635,7 +12651,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A143="","",'Carga Vigilador'!A143)</f>
         <v/>
@@ -12675,7 +12691,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A144="","",'Carga Vigilador'!A144)</f>
         <v/>
@@ -12715,7 +12731,7 @@
         <v/>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A145="","",'Carga Vigilador'!A145)</f>
         <v/>
@@ -12755,7 +12771,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A146="","",'Carga Vigilador'!A146)</f>
         <v/>
@@ -12795,7 +12811,7 @@
         <v/>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A147="","",'Carga Vigilador'!A147)</f>
         <v/>
@@ -12835,7 +12851,7 @@
         <v/>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A148="","",'Carga Vigilador'!A148)</f>
         <v/>
@@ -12875,7 +12891,7 @@
         <v/>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A149="","",'Carga Vigilador'!A149)</f>
         <v/>
@@ -12915,7 +12931,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A150="","",'Carga Vigilador'!A150)</f>
         <v/>
@@ -12955,7 +12971,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A151="","",'Carga Vigilador'!A151)</f>
         <v/>
@@ -12995,7 +13011,7 @@
         <v/>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A152="","",'Carga Vigilador'!A152)</f>
         <v/>
@@ -13035,7 +13051,7 @@
         <v/>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A153="","",'Carga Vigilador'!A153)</f>
         <v/>
@@ -13075,7 +13091,7 @@
         <v/>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A154="","",'Carga Vigilador'!A154)</f>
         <v/>
@@ -13115,7 +13131,7 @@
         <v/>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A155="","",'Carga Vigilador'!A155)</f>
         <v/>
@@ -13155,7 +13171,7 @@
         <v/>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A156="","",'Carga Vigilador'!A156)</f>
         <v/>
@@ -13195,7 +13211,7 @@
         <v/>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A157="","",'Carga Vigilador'!A157)</f>
         <v/>
@@ -13235,7 +13251,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A158="","",'Carga Vigilador'!A158)</f>
         <v/>
@@ -13275,7 +13291,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A159="","",'Carga Vigilador'!A159)</f>
         <v/>
@@ -13315,7 +13331,7 @@
         <v/>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A160="","",'Carga Vigilador'!A160)</f>
         <v/>
@@ -13355,7 +13371,7 @@
         <v/>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A161="","",'Carga Vigilador'!A161)</f>
         <v/>
@@ -13395,7 +13411,7 @@
         <v/>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A162="","",'Carga Vigilador'!A162)</f>
         <v/>
@@ -13435,7 +13451,7 @@
         <v/>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A163="","",'Carga Vigilador'!A163)</f>
         <v/>
@@ -13475,7 +13491,7 @@
         <v/>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A164="","",'Carga Vigilador'!A164)</f>
         <v/>
@@ -13515,7 +13531,7 @@
         <v/>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A165="","",'Carga Vigilador'!A165)</f>
         <v/>
@@ -13555,7 +13571,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A166="","",'Carga Vigilador'!A166)</f>
         <v/>
@@ -13595,7 +13611,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A167="","",'Carga Vigilador'!A167)</f>
         <v/>
@@ -13635,7 +13651,7 @@
         <v/>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A168="","",'Carga Vigilador'!A168)</f>
         <v/>
@@ -13675,7 +13691,7 @@
         <v/>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A169="","",'Carga Vigilador'!A169)</f>
         <v/>
@@ -13715,7 +13731,7 @@
         <v/>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A170="","",'Carga Vigilador'!A170)</f>
         <v/>
@@ -13755,7 +13771,7 @@
         <v/>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A171="","",'Carga Vigilador'!A171)</f>
         <v/>
@@ -13795,7 +13811,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A172="","",'Carga Vigilador'!A172)</f>
         <v/>
@@ -13835,7 +13851,7 @@
         <v/>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A173="","",'Carga Vigilador'!A173)</f>
         <v/>
@@ -13875,7 +13891,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A174="","",'Carga Vigilador'!A174)</f>
         <v/>
@@ -13915,7 +13931,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A175="","",'Carga Vigilador'!A175)</f>
         <v/>
@@ -13955,7 +13971,7 @@
         <v/>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A176="","",'Carga Vigilador'!A176)</f>
         <v/>
@@ -13995,7 +14011,7 @@
         <v/>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A177="","",'Carga Vigilador'!A177)</f>
         <v/>
@@ -14035,7 +14051,7 @@
         <v/>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A178="","",'Carga Vigilador'!A178)</f>
         <v/>
@@ -14075,7 +14091,7 @@
         <v/>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A179="","",'Carga Vigilador'!A179)</f>
         <v/>
@@ -14115,7 +14131,7 @@
         <v/>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A180="","",'Carga Vigilador'!A180)</f>
         <v/>
@@ -14155,7 +14171,7 @@
         <v/>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A181="","",'Carga Vigilador'!A181)</f>
         <v/>
@@ -14195,7 +14211,7 @@
         <v/>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A182="","",'Carga Vigilador'!A182)</f>
         <v/>
@@ -14235,7 +14251,7 @@
         <v/>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A183="","",'Carga Vigilador'!A183)</f>
         <v/>
@@ -14275,7 +14291,7 @@
         <v/>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A184="","",'Carga Vigilador'!A184)</f>
         <v/>
@@ -14315,7 +14331,7 @@
         <v/>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A185="","",'Carga Vigilador'!A185)</f>
         <v/>
@@ -14355,7 +14371,7 @@
         <v/>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A186="","",'Carga Vigilador'!A186)</f>
         <v/>
@@ -14395,7 +14411,7 @@
         <v/>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A187="","",'Carga Vigilador'!A187)</f>
         <v/>
@@ -14435,7 +14451,7 @@
         <v/>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A188="","",'Carga Vigilador'!A188)</f>
         <v/>
@@ -14475,7 +14491,7 @@
         <v/>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A189="","",'Carga Vigilador'!A189)</f>
         <v/>
@@ -14515,7 +14531,7 @@
         <v/>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A190="","",'Carga Vigilador'!A190)</f>
         <v/>
@@ -14555,7 +14571,7 @@
         <v/>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A191="","",'Carga Vigilador'!A191)</f>
         <v/>
@@ -14595,7 +14611,7 @@
         <v/>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A192="","",'Carga Vigilador'!A192)</f>
         <v/>
@@ -14635,7 +14651,7 @@
         <v/>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A193="","",'Carga Vigilador'!A193)</f>
         <v/>
@@ -14675,7 +14691,7 @@
         <v/>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A194="","",'Carga Vigilador'!A194)</f>
         <v/>
@@ -14715,7 +14731,7 @@
         <v/>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A195="","",'Carga Vigilador'!A195)</f>
         <v/>
@@ -14755,7 +14771,7 @@
         <v/>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A196="","",'Carga Vigilador'!A196)</f>
         <v/>
@@ -14795,7 +14811,7 @@
         <v/>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A197="","",'Carga Vigilador'!A197)</f>
         <v/>
@@ -14835,7 +14851,7 @@
         <v/>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A198="","",'Carga Vigilador'!A198)</f>
         <v/>
@@ -14875,7 +14891,7 @@
         <v/>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A199="","",'Carga Vigilador'!A199)</f>
         <v/>
@@ -14915,7 +14931,7 @@
         <v/>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A200="","",'Carga Vigilador'!A200)</f>
         <v/>
@@ -14955,7 +14971,7 @@
         <v/>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A201="","",'Carga Vigilador'!A201)</f>
         <v/>
@@ -14995,7 +15011,7 @@
         <v/>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A202="","",'Carga Vigilador'!A202)</f>
         <v/>
@@ -15035,7 +15051,7 @@
         <v/>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A203="","",'Carga Vigilador'!A203)</f>
         <v/>
@@ -15075,7 +15091,7 @@
         <v/>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A204="","",'Carga Vigilador'!A204)</f>
         <v/>
@@ -15115,7 +15131,7 @@
         <v/>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A205="","",'Carga Vigilador'!A205)</f>
         <v/>
@@ -15155,7 +15171,7 @@
         <v/>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A206="","",'Carga Vigilador'!A206)</f>
         <v/>
@@ -15195,7 +15211,7 @@
         <v/>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A207="","",'Carga Vigilador'!A207)</f>
         <v/>
@@ -15235,7 +15251,7 @@
         <v/>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A208="","",'Carga Vigilador'!A208)</f>
         <v/>
@@ -15275,7 +15291,7 @@
         <v/>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A209="","",'Carga Vigilador'!A209)</f>
         <v/>
@@ -15315,7 +15331,7 @@
         <v/>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A210="","",'Carga Vigilador'!A210)</f>
         <v/>
@@ -15355,7 +15371,7 @@
         <v/>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A211="","",'Carga Vigilador'!A211)</f>
         <v/>
@@ -15395,7 +15411,7 @@
         <v/>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A212="","",'Carga Vigilador'!A212)</f>
         <v/>
@@ -15435,7 +15451,7 @@
         <v/>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A213="","",'Carga Vigilador'!A213)</f>
         <v/>
@@ -15475,7 +15491,7 @@
         <v/>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A214="","",'Carga Vigilador'!A214)</f>
         <v/>
@@ -15515,7 +15531,7 @@
         <v/>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A215="","",'Carga Vigilador'!A215)</f>
         <v/>
@@ -15555,7 +15571,7 @@
         <v/>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A216="","",'Carga Vigilador'!A216)</f>
         <v/>
@@ -15595,7 +15611,7 @@
         <v/>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A217="","",'Carga Vigilador'!A217)</f>
         <v/>
@@ -15635,7 +15651,7 @@
         <v/>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A218="","",'Carga Vigilador'!A218)</f>
         <v/>
@@ -15675,7 +15691,7 @@
         <v/>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A219="","",'Carga Vigilador'!A219)</f>
         <v/>
@@ -15715,7 +15731,7 @@
         <v/>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A220="","",'Carga Vigilador'!A220)</f>
         <v/>
@@ -15755,7 +15771,7 @@
         <v/>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A221="","",'Carga Vigilador'!A221)</f>
         <v/>
@@ -15795,7 +15811,7 @@
         <v/>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A222="","",'Carga Vigilador'!A222)</f>
         <v/>
@@ -15835,7 +15851,7 @@
         <v/>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A223="","",'Carga Vigilador'!A223)</f>
         <v/>
@@ -15875,7 +15891,7 @@
         <v/>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A224="","",'Carga Vigilador'!A224)</f>
         <v/>
@@ -15915,7 +15931,7 @@
         <v/>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A225="","",'Carga Vigilador'!A225)</f>
         <v/>
@@ -15955,7 +15971,7 @@
         <v/>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A226="","",'Carga Vigilador'!A226)</f>
         <v/>
@@ -15995,7 +16011,7 @@
         <v/>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A227="","",'Carga Vigilador'!A227)</f>
         <v/>
@@ -16035,7 +16051,7 @@
         <v/>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A228="","",'Carga Vigilador'!A228)</f>
         <v/>
@@ -16075,7 +16091,7 @@
         <v/>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A229="","",'Carga Vigilador'!A229)</f>
         <v/>
@@ -16115,7 +16131,7 @@
         <v/>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A230="","",'Carga Vigilador'!A230)</f>
         <v/>
@@ -16155,7 +16171,7 @@
         <v/>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A231="","",'Carga Vigilador'!A231)</f>
         <v/>
@@ -16195,7 +16211,7 @@
         <v/>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A232="","",'Carga Vigilador'!A232)</f>
         <v/>
@@ -16235,7 +16251,7 @@
         <v/>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A233="","",'Carga Vigilador'!A233)</f>
         <v/>
@@ -16275,7 +16291,7 @@
         <v/>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A234="","",'Carga Vigilador'!A234)</f>
         <v/>
@@ -16315,7 +16331,7 @@
         <v/>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A235="","",'Carga Vigilador'!A235)</f>
         <v/>
@@ -16355,7 +16371,7 @@
         <v/>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A236="","",'Carga Vigilador'!A236)</f>
         <v/>
@@ -16395,7 +16411,7 @@
         <v/>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A237="","",'Carga Vigilador'!A237)</f>
         <v/>
@@ -16435,7 +16451,7 @@
         <v/>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A238="","",'Carga Vigilador'!A238)</f>
         <v/>
@@ -16475,7 +16491,7 @@
         <v/>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A239="","",'Carga Vigilador'!A239)</f>
         <v/>
@@ -16515,7 +16531,7 @@
         <v/>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A240="","",'Carga Vigilador'!A240)</f>
         <v/>
@@ -16555,7 +16571,7 @@
         <v/>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A241="","",'Carga Vigilador'!A241)</f>
         <v/>
@@ -16595,7 +16611,7 @@
         <v/>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A242="","",'Carga Vigilador'!A242)</f>
         <v/>
@@ -16635,7 +16651,7 @@
         <v/>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A243="","",'Carga Vigilador'!A243)</f>
         <v/>
@@ -16675,7 +16691,7 @@
         <v/>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A244="","",'Carga Vigilador'!A244)</f>
         <v/>
@@ -16715,7 +16731,7 @@
         <v/>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A245="","",'Carga Vigilador'!A245)</f>
         <v/>
@@ -16755,7 +16771,7 @@
         <v/>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A246="","",'Carga Vigilador'!A246)</f>
         <v/>
@@ -16795,7 +16811,7 @@
         <v/>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A247="","",'Carga Vigilador'!A247)</f>
         <v/>
@@ -16835,7 +16851,7 @@
         <v/>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A248="","",'Carga Vigilador'!A248)</f>
         <v/>
@@ -16875,7 +16891,7 @@
         <v/>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A249="","",'Carga Vigilador'!A249)</f>
         <v/>
@@ -16915,7 +16931,7 @@
         <v/>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A250="","",'Carga Vigilador'!A250)</f>
         <v/>
@@ -16955,7 +16971,7 @@
         <v/>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A251="","",'Carga Vigilador'!A251)</f>
         <v/>
@@ -16995,7 +17011,7 @@
         <v/>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A252="","",'Carga Vigilador'!A252)</f>
         <v/>
@@ -17035,7 +17051,7 @@
         <v/>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A253="","",'Carga Vigilador'!A253)</f>
         <v/>
@@ -17075,7 +17091,7 @@
         <v/>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A254="","",'Carga Vigilador'!A254)</f>
         <v/>
@@ -17115,7 +17131,7 @@
         <v/>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A255="","",'Carga Vigilador'!A255)</f>
         <v/>
@@ -17155,7 +17171,7 @@
         <v/>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A256="","",'Carga Vigilador'!A256)</f>
         <v/>
@@ -17195,7 +17211,7 @@
         <v/>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A257="","",'Carga Vigilador'!A257)</f>
         <v/>
@@ -17235,7 +17251,7 @@
         <v/>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A258="","",'Carga Vigilador'!A258)</f>
         <v/>
@@ -17275,7 +17291,7 @@
         <v/>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A259="","",'Carga Vigilador'!A259)</f>
         <v/>
@@ -17315,7 +17331,7 @@
         <v/>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A260="","",'Carga Vigilador'!A260)</f>
         <v/>
@@ -17355,7 +17371,7 @@
         <v/>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A261="","",'Carga Vigilador'!A261)</f>
         <v/>
@@ -17395,7 +17411,7 @@
         <v/>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A262="","",'Carga Vigilador'!A262)</f>
         <v/>
@@ -17435,7 +17451,7 @@
         <v/>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A263="","",'Carga Vigilador'!A263)</f>
         <v/>
@@ -17475,7 +17491,7 @@
         <v/>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A264="","",'Carga Vigilador'!A264)</f>
         <v/>
@@ -17515,7 +17531,7 @@
         <v/>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A265="","",'Carga Vigilador'!A265)</f>
         <v/>
@@ -17555,7 +17571,7 @@
         <v/>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A266="","",'Carga Vigilador'!A266)</f>
         <v/>
@@ -17595,7 +17611,7 @@
         <v/>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A267="","",'Carga Vigilador'!A267)</f>
         <v/>
@@ -17635,7 +17651,7 @@
         <v/>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A268="","",'Carga Vigilador'!A268)</f>
         <v/>
@@ -17675,7 +17691,7 @@
         <v/>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A269="","",'Carga Vigilador'!A269)</f>
         <v/>
@@ -17715,7 +17731,7 @@
         <v/>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A270="","",'Carga Vigilador'!A270)</f>
         <v/>
@@ -17755,7 +17771,7 @@
         <v/>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A271="","",'Carga Vigilador'!A271)</f>
         <v/>
@@ -17795,7 +17811,7 @@
         <v/>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A272="","",'Carga Vigilador'!A272)</f>
         <v/>
@@ -17835,7 +17851,7 @@
         <v/>
       </c>
     </row>
-    <row r="273" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A273="","",'Carga Vigilador'!A273)</f>
         <v/>
@@ -17875,7 +17891,7 @@
         <v/>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A274="","",'Carga Vigilador'!A274)</f>
         <v/>
@@ -17915,7 +17931,7 @@
         <v/>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="275" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A275="","",'Carga Vigilador'!A275)</f>
         <v/>
@@ -17955,7 +17971,7 @@
         <v/>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A276="","",'Carga Vigilador'!A276)</f>
         <v/>
@@ -17995,7 +18011,7 @@
         <v/>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A277="","",'Carga Vigilador'!A277)</f>
         <v/>
@@ -18035,7 +18051,7 @@
         <v/>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A278="","",'Carga Vigilador'!A278)</f>
         <v/>
@@ -18075,7 +18091,7 @@
         <v/>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A279="","",'Carga Vigilador'!A279)</f>
         <v/>
@@ -18115,7 +18131,7 @@
         <v/>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A280="","",'Carga Vigilador'!A280)</f>
         <v/>
@@ -18155,7 +18171,7 @@
         <v/>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A281="","",'Carga Vigilador'!A281)</f>
         <v/>
@@ -18195,7 +18211,7 @@
         <v/>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A282="","",'Carga Vigilador'!A282)</f>
         <v/>
@@ -18235,7 +18251,7 @@
         <v/>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A283="","",'Carga Vigilador'!A283)</f>
         <v/>
@@ -18275,7 +18291,7 @@
         <v/>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A284="","",'Carga Vigilador'!A284)</f>
         <v/>
@@ -18315,7 +18331,7 @@
         <v/>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A285="","",'Carga Vigilador'!A285)</f>
         <v/>
@@ -18355,7 +18371,7 @@
         <v/>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A286="","",'Carga Vigilador'!A286)</f>
         <v/>
@@ -18395,7 +18411,7 @@
         <v/>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="287" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A287="","",'Carga Vigilador'!A287)</f>
         <v/>
@@ -18435,7 +18451,7 @@
         <v/>
       </c>
     </row>
-    <row r="288" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="288" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A288="","",'Carga Vigilador'!A288)</f>
         <v/>
@@ -18475,7 +18491,7 @@
         <v/>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="289" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A289="","",'Carga Vigilador'!A289)</f>
         <v/>
@@ -18515,7 +18531,7 @@
         <v/>
       </c>
     </row>
-    <row r="290" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="290" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A290="","",'Carga Vigilador'!A290)</f>
         <v/>
@@ -18555,7 +18571,7 @@
         <v/>
       </c>
     </row>
-    <row r="291" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A291="","",'Carga Vigilador'!A291)</f>
         <v/>
@@ -18595,7 +18611,7 @@
         <v/>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A292="","",'Carga Vigilador'!A292)</f>
         <v/>
@@ -18635,7 +18651,7 @@
         <v/>
       </c>
     </row>
-    <row r="293" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A293="","",'Carga Vigilador'!A293)</f>
         <v/>
@@ -18675,7 +18691,7 @@
         <v/>
       </c>
     </row>
-    <row r="294" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A294="","",'Carga Vigilador'!A294)</f>
         <v/>
@@ -18715,7 +18731,7 @@
         <v/>
       </c>
     </row>
-    <row r="295" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="295" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A295="","",'Carga Vigilador'!A295)</f>
         <v/>
@@ -18755,7 +18771,7 @@
         <v/>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A296="","",'Carga Vigilador'!A296)</f>
         <v/>
@@ -18795,7 +18811,7 @@
         <v/>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A297="","",'Carga Vigilador'!A297)</f>
         <v/>
@@ -18835,7 +18851,7 @@
         <v/>
       </c>
     </row>
-    <row r="298" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A298="","",'Carga Vigilador'!A298)</f>
         <v/>
@@ -18875,7 +18891,7 @@
         <v/>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="299" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A299="","",'Carga Vigilador'!A299)</f>
         <v/>
@@ -18915,7 +18931,7 @@
         <v/>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A300="","",'Carga Vigilador'!A300)</f>
         <v/>
@@ -18955,7 +18971,7 @@
         <v/>
       </c>
     </row>
-    <row r="301" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="301" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A301="","",'Carga Vigilador'!A301)</f>
         <v/>
@@ -18995,7 +19011,7 @@
         <v/>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A302="","",'Carga Vigilador'!A302)</f>
         <v/>
@@ -19035,7 +19051,7 @@
         <v/>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A303="","",'Carga Vigilador'!A303)</f>
         <v/>
@@ -19075,7 +19091,7 @@
         <v/>
       </c>
     </row>
-    <row r="304" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="304" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A304="","",'Carga Vigilador'!A304)</f>
         <v/>
@@ -19115,7 +19131,7 @@
         <v/>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="305" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A305="","",'Carga Vigilador'!A305)</f>
         <v/>
@@ -19155,7 +19171,7 @@
         <v/>
       </c>
     </row>
-    <row r="306" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="306" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A306="","",'Carga Vigilador'!A306)</f>
         <v/>
@@ -19195,7 +19211,7 @@
         <v/>
       </c>
     </row>
-    <row r="307" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="307" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A307="","",'Carga Vigilador'!A307)</f>
         <v/>
@@ -19235,7 +19251,7 @@
         <v/>
       </c>
     </row>
-    <row r="308" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="308" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A308="","",'Carga Vigilador'!A308)</f>
         <v/>
@@ -19275,7 +19291,7 @@
         <v/>
       </c>
     </row>
-    <row r="309" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="309" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A309="","",'Carga Vigilador'!A309)</f>
         <v/>
@@ -19315,7 +19331,7 @@
         <v/>
       </c>
     </row>
-    <row r="310" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="310" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A310="","",'Carga Vigilador'!A310)</f>
         <v/>
@@ -19355,7 +19371,7 @@
         <v/>
       </c>
     </row>
-    <row r="311" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="311" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A311="","",'Carga Vigilador'!A311)</f>
         <v/>
@@ -19395,7 +19411,7 @@
         <v/>
       </c>
     </row>
-    <row r="312" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="312" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A312="","",'Carga Vigilador'!A312)</f>
         <v/>
@@ -19435,7 +19451,7 @@
         <v/>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="313" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A313="","",'Carga Vigilador'!A313)</f>
         <v/>
@@ -19475,7 +19491,7 @@
         <v/>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A314="","",'Carga Vigilador'!A314)</f>
         <v/>
@@ -19515,7 +19531,7 @@
         <v/>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A315="","",'Carga Vigilador'!A315)</f>
         <v/>
@@ -19555,7 +19571,7 @@
         <v/>
       </c>
     </row>
-    <row r="316" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="316" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A316="","",'Carga Vigilador'!A316)</f>
         <v/>
@@ -19595,7 +19611,7 @@
         <v/>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="317" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A317="","",'Carga Vigilador'!A317)</f>
         <v/>
@@ -19635,7 +19651,7 @@
         <v/>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A318="","",'Carga Vigilador'!A318)</f>
         <v/>
@@ -19675,7 +19691,7 @@
         <v/>
       </c>
     </row>
-    <row r="319" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="319" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A319="","",'Carga Vigilador'!A319)</f>
         <v/>
@@ -19715,7 +19731,7 @@
         <v/>
       </c>
     </row>
-    <row r="320" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="320" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A320="","",'Carga Vigilador'!A320)</f>
         <v/>
@@ -19755,7 +19771,7 @@
         <v/>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="321" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A321="","",'Carga Vigilador'!A321)</f>
         <v/>
@@ -19795,7 +19811,7 @@
         <v/>
       </c>
     </row>
-    <row r="322" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="322" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A322="","",'Carga Vigilador'!A322)</f>
         <v/>
@@ -19835,7 +19851,7 @@
         <v/>
       </c>
     </row>
-    <row r="323" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="323" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A323="","",'Carga Vigilador'!A323)</f>
         <v/>
@@ -19875,7 +19891,7 @@
         <v/>
       </c>
     </row>
-    <row r="324" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="324" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A324="","",'Carga Vigilador'!A324)</f>
         <v/>
@@ -19915,7 +19931,7 @@
         <v/>
       </c>
     </row>
-    <row r="325" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="325" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A325="","",'Carga Vigilador'!A325)</f>
         <v/>
@@ -19955,7 +19971,7 @@
         <v/>
       </c>
     </row>
-    <row r="326" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="326" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A326="","",'Carga Vigilador'!A326)</f>
         <v/>
@@ -19995,7 +20011,7 @@
         <v/>
       </c>
     </row>
-    <row r="327" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="327" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A327="","",'Carga Vigilador'!A327)</f>
         <v/>
@@ -20035,7 +20051,7 @@
         <v/>
       </c>
     </row>
-    <row r="328" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="328" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A328="","",'Carga Vigilador'!A328)</f>
         <v/>
@@ -20075,7 +20091,7 @@
         <v/>
       </c>
     </row>
-    <row r="329" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="329" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A329="","",'Carga Vigilador'!A329)</f>
         <v/>
@@ -20115,7 +20131,7 @@
         <v/>
       </c>
     </row>
-    <row r="330" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="330" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A330="","",'Carga Vigilador'!A330)</f>
         <v/>
@@ -20155,7 +20171,7 @@
         <v/>
       </c>
     </row>
-    <row r="331" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="331" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A331="","",'Carga Vigilador'!A331)</f>
         <v/>
@@ -20195,7 +20211,7 @@
         <v/>
       </c>
     </row>
-    <row r="332" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="332" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A332="","",'Carga Vigilador'!A332)</f>
         <v/>
@@ -20235,7 +20251,7 @@
         <v/>
       </c>
     </row>
-    <row r="333" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="333" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A333="","",'Carga Vigilador'!A333)</f>
         <v/>
@@ -20275,7 +20291,7 @@
         <v/>
       </c>
     </row>
-    <row r="334" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="334" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A334="","",'Carga Vigilador'!A334)</f>
         <v/>
@@ -20315,7 +20331,7 @@
         <v/>
       </c>
     </row>
-    <row r="335" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="335" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A335="","",'Carga Vigilador'!A335)</f>
         <v/>
@@ -20355,7 +20371,7 @@
         <v/>
       </c>
     </row>
-    <row r="336" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="336" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A336="","",'Carga Vigilador'!A336)</f>
         <v/>
@@ -20395,7 +20411,7 @@
         <v/>
       </c>
     </row>
-    <row r="337" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="337" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A337="","",'Carga Vigilador'!A337)</f>
         <v/>
@@ -20435,7 +20451,7 @@
         <v/>
       </c>
     </row>
-    <row r="338" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="338" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A338="","",'Carga Vigilador'!A338)</f>
         <v/>
@@ -20475,7 +20491,7 @@
         <v/>
       </c>
     </row>
-    <row r="339" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="339" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A339="","",'Carga Vigilador'!A339)</f>
         <v/>
@@ -20515,7 +20531,7 @@
         <v/>
       </c>
     </row>
-    <row r="340" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="340" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A340="","",'Carga Vigilador'!A340)</f>
         <v/>
@@ -20555,7 +20571,7 @@
         <v/>
       </c>
     </row>
-    <row r="341" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="341" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A341="","",'Carga Vigilador'!A341)</f>
         <v/>
@@ -20595,7 +20611,7 @@
         <v/>
       </c>
     </row>
-    <row r="342" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="342" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A342="","",'Carga Vigilador'!A342)</f>
         <v/>
@@ -20635,7 +20651,7 @@
         <v/>
       </c>
     </row>
-    <row r="343" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="343" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A343="","",'Carga Vigilador'!A343)</f>
         <v/>
@@ -20675,7 +20691,7 @@
         <v/>
       </c>
     </row>
-    <row r="344" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="344" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A344="","",'Carga Vigilador'!A344)</f>
         <v/>
@@ -20715,7 +20731,7 @@
         <v/>
       </c>
     </row>
-    <row r="345" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="345" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A345="","",'Carga Vigilador'!A345)</f>
         <v/>
@@ -20755,7 +20771,7 @@
         <v/>
       </c>
     </row>
-    <row r="346" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="346" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A346="","",'Carga Vigilador'!A346)</f>
         <v/>
@@ -20795,7 +20811,7 @@
         <v/>
       </c>
     </row>
-    <row r="347" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="347" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A347="","",'Carga Vigilador'!A347)</f>
         <v/>
@@ -20835,7 +20851,7 @@
         <v/>
       </c>
     </row>
-    <row r="348" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="348" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A348="","",'Carga Vigilador'!A348)</f>
         <v/>
@@ -20875,7 +20891,7 @@
         <v/>
       </c>
     </row>
-    <row r="349" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="349" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A349="","",'Carga Vigilador'!A349)</f>
         <v/>
@@ -20915,7 +20931,7 @@
         <v/>
       </c>
     </row>
-    <row r="350" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="350" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A350="","",'Carga Vigilador'!A350)</f>
         <v/>
@@ -20955,7 +20971,7 @@
         <v/>
       </c>
     </row>
-    <row r="351" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="351" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A351="","",'Carga Vigilador'!A351)</f>
         <v/>
@@ -20995,7 +21011,7 @@
         <v/>
       </c>
     </row>
-    <row r="352" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="352" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A352="","",'Carga Vigilador'!A352)</f>
         <v/>
@@ -21035,7 +21051,7 @@
         <v/>
       </c>
     </row>
-    <row r="353" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="353" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A353="","",'Carga Vigilador'!A353)</f>
         <v/>
@@ -21075,7 +21091,7 @@
         <v/>
       </c>
     </row>
-    <row r="354" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="354" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A354="","",'Carga Vigilador'!A354)</f>
         <v/>
@@ -21115,7 +21131,7 @@
         <v/>
       </c>
     </row>
-    <row r="355" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="355" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A355="","",'Carga Vigilador'!A355)</f>
         <v/>
@@ -21155,7 +21171,7 @@
         <v/>
       </c>
     </row>
-    <row r="356" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="356" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A356="","",'Carga Vigilador'!A356)</f>
         <v/>
@@ -21195,7 +21211,7 @@
         <v/>
       </c>
     </row>
-    <row r="357" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="357" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A357="","",'Carga Vigilador'!A357)</f>
         <v/>
@@ -21235,7 +21251,7 @@
         <v/>
       </c>
     </row>
-    <row r="358" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="358" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A358="","",'Carga Vigilador'!A358)</f>
         <v/>
@@ -21275,7 +21291,7 @@
         <v/>
       </c>
     </row>
-    <row r="359" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="359" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A359="","",'Carga Vigilador'!A359)</f>
         <v/>
@@ -21315,7 +21331,7 @@
         <v/>
       </c>
     </row>
-    <row r="360" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="360" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A360="","",'Carga Vigilador'!A360)</f>
         <v/>
@@ -21355,7 +21371,7 @@
         <v/>
       </c>
     </row>
-    <row r="361" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="361" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A361="","",'Carga Vigilador'!A361)</f>
         <v/>
@@ -21395,7 +21411,7 @@
         <v/>
       </c>
     </row>
-    <row r="362" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="362" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A362="","",'Carga Vigilador'!A362)</f>
         <v/>
@@ -21435,7 +21451,7 @@
         <v/>
       </c>
     </row>
-    <row r="363" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="363" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A363="","",'Carga Vigilador'!A363)</f>
         <v/>
@@ -21475,7 +21491,7 @@
         <v/>
       </c>
     </row>
-    <row r="364" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="364" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A364="","",'Carga Vigilador'!A364)</f>
         <v/>
@@ -21515,7 +21531,7 @@
         <v/>
       </c>
     </row>
-    <row r="365" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="365" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A365="","",'Carga Vigilador'!A365)</f>
         <v/>
@@ -21555,7 +21571,7 @@
         <v/>
       </c>
     </row>
-    <row r="366" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="366" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A366="","",'Carga Vigilador'!A366)</f>
         <v/>
@@ -21595,7 +21611,7 @@
         <v/>
       </c>
     </row>
-    <row r="367" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="367" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A367="","",'Carga Vigilador'!A367)</f>
         <v/>
@@ -21635,7 +21651,7 @@
         <v/>
       </c>
     </row>
-    <row r="368" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A368="","",'Carga Vigilador'!A368)</f>
         <v/>
@@ -21675,7 +21691,7 @@
         <v/>
       </c>
     </row>
-    <row r="369" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="369" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A369="","",'Carga Vigilador'!A369)</f>
         <v/>
@@ -21715,7 +21731,7 @@
         <v/>
       </c>
     </row>
-    <row r="370" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="370" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A370="","",'Carga Vigilador'!A370)</f>
         <v/>
@@ -21755,7 +21771,7 @@
         <v/>
       </c>
     </row>
-    <row r="371" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="371" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A371="","",'Carga Vigilador'!A371)</f>
         <v/>
@@ -21795,7 +21811,7 @@
         <v/>
       </c>
     </row>
-    <row r="372" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="372" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A372="","",'Carga Vigilador'!A372)</f>
         <v/>
@@ -21835,7 +21851,7 @@
         <v/>
       </c>
     </row>
-    <row r="373" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="373" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A373="","",'Carga Vigilador'!A373)</f>
         <v/>
@@ -21875,7 +21891,7 @@
         <v/>
       </c>
     </row>
-    <row r="374" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="374" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A374="","",'Carga Vigilador'!A374)</f>
         <v/>
@@ -21915,7 +21931,7 @@
         <v/>
       </c>
     </row>
-    <row r="375" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="375" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A375="","",'Carga Vigilador'!A375)</f>
         <v/>
@@ -21955,7 +21971,7 @@
         <v/>
       </c>
     </row>
-    <row r="376" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="376" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A376="","",'Carga Vigilador'!A376)</f>
         <v/>
@@ -21995,7 +22011,7 @@
         <v/>
       </c>
     </row>
-    <row r="377" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="377" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A377="","",'Carga Vigilador'!A377)</f>
         <v/>
@@ -22035,7 +22051,7 @@
         <v/>
       </c>
     </row>
-    <row r="378" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="378" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A378="","",'Carga Vigilador'!A378)</f>
         <v/>
@@ -22075,7 +22091,7 @@
         <v/>
       </c>
     </row>
-    <row r="379" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="379" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A379="","",'Carga Vigilador'!A379)</f>
         <v/>
@@ -22115,7 +22131,7 @@
         <v/>
       </c>
     </row>
-    <row r="380" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="380" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A380="","",'Carga Vigilador'!A380)</f>
         <v/>
@@ -22155,7 +22171,7 @@
         <v/>
       </c>
     </row>
-    <row r="381" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="381" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A381="","",'Carga Vigilador'!A381)</f>
         <v/>
@@ -22195,7 +22211,7 @@
         <v/>
       </c>
     </row>
-    <row r="382" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="382" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A382="","",'Carga Vigilador'!A382)</f>
         <v/>
@@ -22235,7 +22251,7 @@
         <v/>
       </c>
     </row>
-    <row r="383" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="383" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A383="","",'Carga Vigilador'!A383)</f>
         <v/>
@@ -22275,7 +22291,7 @@
         <v/>
       </c>
     </row>
-    <row r="384" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="384" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A384="","",'Carga Vigilador'!A384)</f>
         <v/>
@@ -22315,7 +22331,7 @@
         <v/>
       </c>
     </row>
-    <row r="385" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="385" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A385="","",'Carga Vigilador'!A385)</f>
         <v/>
@@ -22355,7 +22371,7 @@
         <v/>
       </c>
     </row>
-    <row r="386" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="386" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A386="","",'Carga Vigilador'!A386)</f>
         <v/>
@@ -22395,7 +22411,7 @@
         <v/>
       </c>
     </row>
-    <row r="387" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="387" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A387="","",'Carga Vigilador'!A387)</f>
         <v/>
@@ -22435,7 +22451,7 @@
         <v/>
       </c>
     </row>
-    <row r="388" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A388="","",'Carga Vigilador'!A388)</f>
         <v/>
@@ -22475,7 +22491,7 @@
         <v/>
       </c>
     </row>
-    <row r="389" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="389" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A389="","",'Carga Vigilador'!A389)</f>
         <v/>
@@ -22515,7 +22531,7 @@
         <v/>
       </c>
     </row>
-    <row r="390" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A390="","",'Carga Vigilador'!A390)</f>
         <v/>
@@ -22555,7 +22571,7 @@
         <v/>
       </c>
     </row>
-    <row r="391" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="391" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A391="","",'Carga Vigilador'!A391)</f>
         <v/>
@@ -22595,7 +22611,7 @@
         <v/>
       </c>
     </row>
-    <row r="392" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="392" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A392="","",'Carga Vigilador'!A392)</f>
         <v/>
@@ -22635,7 +22651,7 @@
         <v/>
       </c>
     </row>
-    <row r="393" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A393="","",'Carga Vigilador'!A393)</f>
         <v/>
@@ -22675,7 +22691,7 @@
         <v/>
       </c>
     </row>
-    <row r="394" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="394" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A394="","",'Carga Vigilador'!A394)</f>
         <v/>
@@ -22715,7 +22731,7 @@
         <v/>
       </c>
     </row>
-    <row r="395" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A395="","",'Carga Vigilador'!A395)</f>
         <v/>
@@ -22755,7 +22771,7 @@
         <v/>
       </c>
     </row>
-    <row r="396" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="396" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A396="","",'Carga Vigilador'!A396)</f>
         <v/>
@@ -22795,7 +22811,7 @@
         <v/>
       </c>
     </row>
-    <row r="397" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="397" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A397="","",'Carga Vigilador'!A397)</f>
         <v/>
@@ -22835,7 +22851,7 @@
         <v/>
       </c>
     </row>
-    <row r="398" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="398" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A398="","",'Carga Vigilador'!A398)</f>
         <v/>
@@ -22875,7 +22891,7 @@
         <v/>
       </c>
     </row>
-    <row r="399" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="399" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A399="","",'Carga Vigilador'!A399)</f>
         <v/>
@@ -22915,7 +22931,7 @@
         <v/>
       </c>
     </row>
-    <row r="400" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="400" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A400="","",'Carga Vigilador'!A400)</f>
         <v/>
@@ -22955,7 +22971,7 @@
         <v/>
       </c>
     </row>
-    <row r="401" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="401" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A401="","",'Carga Vigilador'!A401)</f>
         <v/>
@@ -22995,7 +23011,7 @@
         <v/>
       </c>
     </row>
-    <row r="402" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="402" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A402="","",'Carga Vigilador'!A402)</f>
         <v/>
@@ -23035,7 +23051,7 @@
         <v/>
       </c>
     </row>
-    <row r="403" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="403" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A403="","",'Carga Vigilador'!A403)</f>
         <v/>
@@ -23075,7 +23091,7 @@
         <v/>
       </c>
     </row>
-    <row r="404" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="404" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A404="","",'Carga Vigilador'!A404)</f>
         <v/>
@@ -23115,7 +23131,7 @@
         <v/>
       </c>
     </row>
-    <row r="405" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="405" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A405="","",'Carga Vigilador'!A405)</f>
         <v/>
@@ -23155,7 +23171,7 @@
         <v/>
       </c>
     </row>
-    <row r="406" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="406" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A406="","",'Carga Vigilador'!A406)</f>
         <v/>
@@ -23195,7 +23211,7 @@
         <v/>
       </c>
     </row>
-    <row r="407" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A407="","",'Carga Vigilador'!A407)</f>
         <v/>
@@ -23235,7 +23251,7 @@
         <v/>
       </c>
     </row>
-    <row r="408" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="408" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A408="","",'Carga Vigilador'!A408)</f>
         <v/>
@@ -23275,7 +23291,7 @@
         <v/>
       </c>
     </row>
-    <row r="409" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="409" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A409="","",'Carga Vigilador'!A409)</f>
         <v/>
@@ -23315,7 +23331,7 @@
         <v/>
       </c>
     </row>
-    <row r="410" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="410" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A410="","",'Carga Vigilador'!A410)</f>
         <v/>
@@ -23355,7 +23371,7 @@
         <v/>
       </c>
     </row>
-    <row r="411" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="411" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A411="","",'Carga Vigilador'!A411)</f>
         <v/>
@@ -23395,7 +23411,7 @@
         <v/>
       </c>
     </row>
-    <row r="412" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="412" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A412="","",'Carga Vigilador'!A412)</f>
         <v/>
@@ -23435,7 +23451,7 @@
         <v/>
       </c>
     </row>
-    <row r="413" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="413" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A413="","",'Carga Vigilador'!A413)</f>
         <v/>
@@ -23475,7 +23491,7 @@
         <v/>
       </c>
     </row>
-    <row r="414" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="414" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A414="","",'Carga Vigilador'!A414)</f>
         <v/>
@@ -23515,7 +23531,7 @@
         <v/>
       </c>
     </row>
-    <row r="415" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="415" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A415="","",'Carga Vigilador'!A415)</f>
         <v/>
@@ -23555,7 +23571,7 @@
         <v/>
       </c>
     </row>
-    <row r="416" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="416" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A416="","",'Carga Vigilador'!A416)</f>
         <v/>
@@ -23595,7 +23611,7 @@
         <v/>
       </c>
     </row>
-    <row r="417" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="417" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A417="","",'Carga Vigilador'!A417)</f>
         <v/>
@@ -23635,7 +23651,7 @@
         <v/>
       </c>
     </row>
-    <row r="418" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="418" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A418="","",'Carga Vigilador'!A418)</f>
         <v/>
@@ -23675,7 +23691,7 @@
         <v/>
       </c>
     </row>
-    <row r="419" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="419" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A419="","",'Carga Vigilador'!A419)</f>
         <v/>
@@ -23715,7 +23731,7 @@
         <v/>
       </c>
     </row>
-    <row r="420" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="420" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A420="","",'Carga Vigilador'!A420)</f>
         <v/>
@@ -23755,7 +23771,7 @@
         <v/>
       </c>
     </row>
-    <row r="421" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="421" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A421="","",'Carga Vigilador'!A421)</f>
         <v/>
@@ -23795,7 +23811,7 @@
         <v/>
       </c>
     </row>
-    <row r="422" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="422" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A422="","",'Carga Vigilador'!A422)</f>
         <v/>
@@ -23835,7 +23851,7 @@
         <v/>
       </c>
     </row>
-    <row r="423" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="423" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A423="","",'Carga Vigilador'!A423)</f>
         <v/>
@@ -23875,7 +23891,7 @@
         <v/>
       </c>
     </row>
-    <row r="424" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="424" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A424="","",'Carga Vigilador'!A424)</f>
         <v/>
@@ -23915,7 +23931,7 @@
         <v/>
       </c>
     </row>
-    <row r="425" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A425="","",'Carga Vigilador'!A425)</f>
         <v/>
@@ -23955,7 +23971,7 @@
         <v/>
       </c>
     </row>
-    <row r="426" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A426="","",'Carga Vigilador'!A426)</f>
         <v/>
@@ -23995,7 +24011,7 @@
         <v/>
       </c>
     </row>
-    <row r="427" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="427" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A427="","",'Carga Vigilador'!A427)</f>
         <v/>
@@ -24035,7 +24051,7 @@
         <v/>
       </c>
     </row>
-    <row r="428" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="428" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A428="","",'Carga Vigilador'!A428)</f>
         <v/>
@@ -24075,7 +24091,7 @@
         <v/>
       </c>
     </row>
-    <row r="429" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="429" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A429="","",'Carga Vigilador'!A429)</f>
         <v/>
@@ -24115,7 +24131,7 @@
         <v/>
       </c>
     </row>
-    <row r="430" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="430" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A430="","",'Carga Vigilador'!A430)</f>
         <v/>
@@ -24155,7 +24171,7 @@
         <v/>
       </c>
     </row>
-    <row r="431" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="431" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A431="","",'Carga Vigilador'!A431)</f>
         <v/>
@@ -24195,7 +24211,7 @@
         <v/>
       </c>
     </row>
-    <row r="432" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="432" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A432="","",'Carga Vigilador'!A432)</f>
         <v/>
@@ -24235,7 +24251,7 @@
         <v/>
       </c>
     </row>
-    <row r="433" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A433="","",'Carga Vigilador'!A433)</f>
         <v/>
@@ -24275,7 +24291,7 @@
         <v/>
       </c>
     </row>
-    <row r="434" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="434" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A434="","",'Carga Vigilador'!A434)</f>
         <v/>
@@ -24315,7 +24331,7 @@
         <v/>
       </c>
     </row>
-    <row r="435" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="435" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A435="","",'Carga Vigilador'!A435)</f>
         <v/>
@@ -24355,7 +24371,7 @@
         <v/>
       </c>
     </row>
-    <row r="436" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="436" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A436="","",'Carga Vigilador'!A436)</f>
         <v/>
@@ -24395,7 +24411,7 @@
         <v/>
       </c>
     </row>
-    <row r="437" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A437="","",'Carga Vigilador'!A437)</f>
         <v/>
@@ -24435,7 +24451,7 @@
         <v/>
       </c>
     </row>
-    <row r="438" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="438" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A438="","",'Carga Vigilador'!A438)</f>
         <v/>
@@ -24475,7 +24491,7 @@
         <v/>
       </c>
     </row>
-    <row r="439" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="439" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A439="","",'Carga Vigilador'!A439)</f>
         <v/>
@@ -24515,7 +24531,7 @@
         <v/>
       </c>
     </row>
-    <row r="440" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="440" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A440="","",'Carga Vigilador'!A440)</f>
         <v/>
@@ -24555,7 +24571,7 @@
         <v/>
       </c>
     </row>
-    <row r="441" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="441" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A441="","",'Carga Vigilador'!A441)</f>
         <v/>
@@ -24595,7 +24611,7 @@
         <v/>
       </c>
     </row>
-    <row r="442" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="442" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A442="","",'Carga Vigilador'!A442)</f>
         <v/>
@@ -24635,7 +24651,7 @@
         <v/>
       </c>
     </row>
-    <row r="443" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="443" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A443="","",'Carga Vigilador'!A443)</f>
         <v/>
@@ -24675,7 +24691,7 @@
         <v/>
       </c>
     </row>
-    <row r="444" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="444" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A444="","",'Carga Vigilador'!A444)</f>
         <v/>
@@ -24715,7 +24731,7 @@
         <v/>
       </c>
     </row>
-    <row r="445" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="445" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A445="","",'Carga Vigilador'!A445)</f>
         <v/>
@@ -24755,7 +24771,7 @@
         <v/>
       </c>
     </row>
-    <row r="446" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="446" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A446="","",'Carga Vigilador'!A446)</f>
         <v/>
@@ -24795,7 +24811,7 @@
         <v/>
       </c>
     </row>
-    <row r="447" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="447" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A447="","",'Carga Vigilador'!A447)</f>
         <v/>
@@ -24835,7 +24851,7 @@
         <v/>
       </c>
     </row>
-    <row r="448" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="448" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A448="","",'Carga Vigilador'!A448)</f>
         <v/>
@@ -24875,7 +24891,7 @@
         <v/>
       </c>
     </row>
-    <row r="449" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="449" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A449="","",'Carga Vigilador'!A449)</f>
         <v/>
@@ -24915,7 +24931,7 @@
         <v/>
       </c>
     </row>
-    <row r="450" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="450" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A450="","",'Carga Vigilador'!A450)</f>
         <v/>
@@ -24955,7 +24971,7 @@
         <v/>
       </c>
     </row>
-    <row r="451" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="451" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A451="","",'Carga Vigilador'!A451)</f>
         <v/>
@@ -24995,7 +25011,7 @@
         <v/>
       </c>
     </row>
-    <row r="452" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="452" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A452="","",'Carga Vigilador'!A452)</f>
         <v/>
@@ -25035,7 +25051,7 @@
         <v/>
       </c>
     </row>
-    <row r="453" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="453" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A453="","",'Carga Vigilador'!A453)</f>
         <v/>
@@ -25075,7 +25091,7 @@
         <v/>
       </c>
     </row>
-    <row r="454" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="454" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A454="","",'Carga Vigilador'!A454)</f>
         <v/>
@@ -25115,7 +25131,7 @@
         <v/>
       </c>
     </row>
-    <row r="455" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="455" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A455="","",'Carga Vigilador'!A455)</f>
         <v/>
@@ -25155,7 +25171,7 @@
         <v/>
       </c>
     </row>
-    <row r="456" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="456" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A456="","",'Carga Vigilador'!A456)</f>
         <v/>
@@ -25195,7 +25211,7 @@
         <v/>
       </c>
     </row>
-    <row r="457" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A457="","",'Carga Vigilador'!A457)</f>
         <v/>
@@ -25235,7 +25251,7 @@
         <v/>
       </c>
     </row>
-    <row r="458" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="458" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A458="","",'Carga Vigilador'!A458)</f>
         <v/>
@@ -25275,7 +25291,7 @@
         <v/>
       </c>
     </row>
-    <row r="459" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="459" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A459="","",'Carga Vigilador'!A459)</f>
         <v/>
@@ -25315,7 +25331,7 @@
         <v/>
       </c>
     </row>
-    <row r="460" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="460" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A460="","",'Carga Vigilador'!A460)</f>
         <v/>
@@ -25355,7 +25371,7 @@
         <v/>
       </c>
     </row>
-    <row r="461" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="461" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A461="","",'Carga Vigilador'!A461)</f>
         <v/>
@@ -25395,7 +25411,7 @@
         <v/>
       </c>
     </row>
-    <row r="462" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="462" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A462="","",'Carga Vigilador'!A462)</f>
         <v/>
@@ -25435,7 +25451,7 @@
         <v/>
       </c>
     </row>
-    <row r="463" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="463" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A463="","",'Carga Vigilador'!A463)</f>
         <v/>
@@ -25475,7 +25491,7 @@
         <v/>
       </c>
     </row>
-    <row r="464" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="464" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A464="","",'Carga Vigilador'!A464)</f>
         <v/>
@@ -25515,7 +25531,7 @@
         <v/>
       </c>
     </row>
-    <row r="465" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="465" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A465="","",'Carga Vigilador'!A465)</f>
         <v/>
@@ -25555,7 +25571,7 @@
         <v/>
       </c>
     </row>
-    <row r="466" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="466" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A466="","",'Carga Vigilador'!A466)</f>
         <v/>
@@ -25595,7 +25611,7 @@
         <v/>
       </c>
     </row>
-    <row r="467" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="467" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A467="","",'Carga Vigilador'!A467)</f>
         <v/>
@@ -25635,7 +25651,7 @@
         <v/>
       </c>
     </row>
-    <row r="468" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="468" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A468="","",'Carga Vigilador'!A468)</f>
         <v/>
@@ -25675,7 +25691,7 @@
         <v/>
       </c>
     </row>
-    <row r="469" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="469" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A469="","",'Carga Vigilador'!A469)</f>
         <v/>
@@ -25715,7 +25731,7 @@
         <v/>
       </c>
     </row>
-    <row r="470" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A470="","",'Carga Vigilador'!A470)</f>
         <v/>
@@ -25755,7 +25771,7 @@
         <v/>
       </c>
     </row>
-    <row r="471" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="471" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A471="","",'Carga Vigilador'!A471)</f>
         <v/>
@@ -25795,7 +25811,7 @@
         <v/>
       </c>
     </row>
-    <row r="472" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="472" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A472="","",'Carga Vigilador'!A472)</f>
         <v/>
@@ -25835,7 +25851,7 @@
         <v/>
       </c>
     </row>
-    <row r="473" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="473" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A473="","",'Carga Vigilador'!A473)</f>
         <v/>
@@ -25875,7 +25891,7 @@
         <v/>
       </c>
     </row>
-    <row r="474" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="474" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A474="","",'Carga Vigilador'!A474)</f>
         <v/>
@@ -25915,7 +25931,7 @@
         <v/>
       </c>
     </row>
-    <row r="475" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="475" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A475="","",'Carga Vigilador'!A475)</f>
         <v/>
@@ -25955,7 +25971,7 @@
         <v/>
       </c>
     </row>
-    <row r="476" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="476" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A476="","",'Carga Vigilador'!A476)</f>
         <v/>
@@ -25995,7 +26011,7 @@
         <v/>
       </c>
     </row>
-    <row r="477" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="477" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A477="","",'Carga Vigilador'!A477)</f>
         <v/>
@@ -26035,7 +26051,7 @@
         <v/>
       </c>
     </row>
-    <row r="478" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="478" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A478="","",'Carga Vigilador'!A478)</f>
         <v/>
@@ -26075,7 +26091,7 @@
         <v/>
       </c>
     </row>
-    <row r="479" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="479" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A479="","",'Carga Vigilador'!A479)</f>
         <v/>
@@ -26115,7 +26131,7 @@
         <v/>
       </c>
     </row>
-    <row r="480" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A480="","",'Carga Vigilador'!A480)</f>
         <v/>
@@ -26155,7 +26171,7 @@
         <v/>
       </c>
     </row>
-    <row r="481" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="481" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A481="","",'Carga Vigilador'!A481)</f>
         <v/>
@@ -26195,7 +26211,7 @@
         <v/>
       </c>
     </row>
-    <row r="482" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="482" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A482="","",'Carga Vigilador'!A482)</f>
         <v/>
@@ -26235,7 +26251,7 @@
         <v/>
       </c>
     </row>
-    <row r="483" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="483" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A483="","",'Carga Vigilador'!A483)</f>
         <v/>
@@ -26275,7 +26291,7 @@
         <v/>
       </c>
     </row>
-    <row r="484" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A484="","",'Carga Vigilador'!A484)</f>
         <v/>
@@ -26315,7 +26331,7 @@
         <v/>
       </c>
     </row>
-    <row r="485" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A485="","",'Carga Vigilador'!A485)</f>
         <v/>
@@ -26355,7 +26371,7 @@
         <v/>
       </c>
     </row>
-    <row r="486" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="486" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A486="","",'Carga Vigilador'!A486)</f>
         <v/>
@@ -26395,7 +26411,7 @@
         <v/>
       </c>
     </row>
-    <row r="487" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="487" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A487="","",'Carga Vigilador'!A487)</f>
         <v/>
@@ -26435,7 +26451,7 @@
         <v/>
       </c>
     </row>
-    <row r="488" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="488" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A488="","",'Carga Vigilador'!A488)</f>
         <v/>
@@ -26475,7 +26491,7 @@
         <v/>
       </c>
     </row>
-    <row r="489" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="489" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A489="","",'Carga Vigilador'!A489)</f>
         <v/>
@@ -26515,7 +26531,7 @@
         <v/>
       </c>
     </row>
-    <row r="490" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="490" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A490="","",'Carga Vigilador'!A490)</f>
         <v/>
@@ -26555,7 +26571,7 @@
         <v/>
       </c>
     </row>
-    <row r="491" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="491" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A491="","",'Carga Vigilador'!A491)</f>
         <v/>
@@ -26595,7 +26611,7 @@
         <v/>
       </c>
     </row>
-    <row r="492" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="492" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A492="","",'Carga Vigilador'!A492)</f>
         <v/>
@@ -26635,7 +26651,7 @@
         <v/>
       </c>
     </row>
-    <row r="493" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="493" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A493="","",'Carga Vigilador'!A493)</f>
         <v/>
@@ -26675,7 +26691,7 @@
         <v/>
       </c>
     </row>
-    <row r="494" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="494" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A494="","",'Carga Vigilador'!A494)</f>
         <v/>
@@ -26715,7 +26731,7 @@
         <v/>
       </c>
     </row>
-    <row r="495" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="495" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A495="","",'Carga Vigilador'!A495)</f>
         <v/>
@@ -26755,7 +26771,7 @@
         <v/>
       </c>
     </row>
-    <row r="496" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="496" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A496="","",'Carga Vigilador'!A496)</f>
         <v/>
@@ -26795,7 +26811,7 @@
         <v/>
       </c>
     </row>
-    <row r="497" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="497" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A497="","",'Carga Vigilador'!A497)</f>
         <v/>
@@ -26835,7 +26851,7 @@
         <v/>
       </c>
     </row>
-    <row r="498" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="498" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A498="","",'Carga Vigilador'!A498)</f>
         <v/>
@@ -26875,7 +26891,7 @@
         <v/>
       </c>
     </row>
-    <row r="499" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="499" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A499="","",'Carga Vigilador'!A499)</f>
         <v/>
@@ -26915,7 +26931,7 @@
         <v/>
       </c>
     </row>
-    <row r="500" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="500" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A500="","",'Carga Vigilador'!A500)</f>
         <v/>
@@ -26955,7 +26971,7 @@
         <v/>
       </c>
     </row>
-    <row r="501" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="501" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A501="","",'Carga Vigilador'!A501)</f>
         <v/>
@@ -26995,7 +27011,7 @@
         <v/>
       </c>
     </row>
-    <row r="502" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="502" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A502="","",'Carga Vigilador'!A502)</f>
         <v/>
@@ -27035,7 +27051,7 @@
         <v/>
       </c>
     </row>
-    <row r="503" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="503" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="6" t="str">
         <f aca="false">IF('Carga Vigilador'!A503="","",'Carga Vigilador'!A503)</f>
         <v/>
@@ -27127,17 +27143,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B4" s="20" t="n">
         <v>46296</v>
@@ -27145,7 +27161,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B5" s="20" t="n">
         <v>46326</v>
@@ -27153,82 +27169,82 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="19" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B6" s="21"/>
       <c r="C6" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="22" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" s="24" t="n">
         <f aca="false">IF($B$6="",COUNTIFS('Carga Administración'!$B$4:$B$503,"&gt;="&amp;$B$4,'Carga Administración'!$B$4:$B$503,"&lt;="&amp;$B$5),COUNTIFS('Carga Administración'!$B$4:$B$503,"&gt;="&amp;$B$4,'Carga Administración'!$B$4:$B$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6))</f>
         <v>1</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B10" s="24" t="n">
         <f aca="false">IF($B$6="",COUNTIFS('Carga Administración'!$H$4:$H$503,"Sí",'Carga Administración'!$I$4:$I$503,"&gt;="&amp;$B$4,'Carga Administración'!$I$4:$I$503,"&lt;="&amp;$B$5),COUNTIFS('Carga Administración'!$H$4:$H$503,"Sí",'Carga Administración'!$I$4:$I$503,"&gt;="&amp;$B$4,'Carga Administración'!$I$4:$I$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6))</f>
         <v>0</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B11" s="24" t="n">
         <f aca="false">IF($B$6="",COUNTIFS('Carga Administración'!$J$4:$J$503,"Sí",'Carga Administración'!$K$4:$K$503,"&gt;="&amp;$B$4,'Carga Administración'!$K$4:$K$503,"&lt;="&amp;$B$5),COUNTIFS('Carga Administración'!$J$4:$J$503,"Sí",'Carga Administración'!$K$4:$K$503,"&gt;="&amp;$B$4,'Carga Administración'!$K$4:$K$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6))</f>
         <v>0</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B12" s="26" t="n">
         <f aca="false">IF($B$6="",SUMIFS('Carga Administración'!$L$4:$L$503,'Carga Administración'!$J$4:$J$503,"Sí",'Carga Administración'!$K$4:$K$503,"&gt;="&amp;$B$4,'Carga Administración'!$K$4:$K$503,"&lt;="&amp;$B$5),SUMIFS('Carga Administración'!$L$4:$L$503,'Carga Administración'!$J$4:$J$503,"Sí",'Carga Administración'!$K$4:$K$503,"&gt;="&amp;$B$4,'Carga Administración'!$K$4:$K$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6))</f>
         <v>0</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B13" s="24" t="n">
         <f aca="false">IF($B$6="",COUNTIFS('Carga Administración'!$N$4:$N$503,"Pendiente",'Carga Administración'!$B$4:$B$503,"&gt;="&amp;$B$4,'Carga Administración'!$B$4:$B$503,"&lt;="&amp;$B$5),COUNTIFS('Carga Administración'!$N$4:$N$503,"Pendiente",'Carga Administración'!$B$4:$B$503,"&gt;="&amp;$B$4,'Carga Administración'!$B$4:$B$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6))</f>
         <v>1</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/multas/Registro_Multas_Propietarios.xlsx
+++ b/multas/Registro_Multas_Propietarios.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Estadísticas" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Carga Administración'!$A$3:$N$503</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Carga Administración'!$A$3:$M$503</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Carga Vigilador'!$A$3:$G$503</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="55">
   <si>
     <t xml:space="preserve">CÓMO SE USA</t>
   </si>
@@ -38,10 +38,10 @@
     <t xml:space="preserve">2. ADMINISTRACIÓN → hoja 'Carga Administración': cada acta ya aparece sola en la misma fila. Completar solo lo amarillo:</t>
   </si>
   <si>
-    <t xml:space="preserve">     descargo enviado (Sí/No) y su fecha · multa aplicada (Sí/No) y su fecha · valor de la multa · observaciones.</t>
+    <t xml:space="preserve">     descargo enviado (SI/NO) y su fecha · estado (PENDIENTE / MULTA APLICADA / MULTA DE BAJA) y su fecha · valor de la multa · observaciones.</t>
   </si>
   <si>
-    <t xml:space="preserve">3. La columna 'Estado' se calcula sola: Pendiente → Descargo enviado → Multa aplicada / Sin multa.</t>
+    <t xml:space="preserve">3. Estado: se elige del desplegable. Amarillo = PENDIENTE · Rojo = MULTA APLICADA · Verde = MULTA DE BAJA.</t>
   </si>
   <si>
     <t xml:space="preserve">4. ESTADÍSTICAS → elegir DESDE / HASTA (y un lote si se quiere) y ver cuántas actas, descargos y multas hubo y el monto.</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">Fecha descargo</t>
   </si>
   <si>
-    <t xml:space="preserve">Multa aplicada</t>
+    <t xml:space="preserve">Estado</t>
   </si>
   <si>
-    <t xml:space="preserve">Fecha multa</t>
+    <t xml:space="preserve">Fecha multa / baja</t>
   </si>
   <si>
     <t xml:space="preserve">Valor multa ($)</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">Observaciones</t>
   </si>
   <si>
-    <t xml:space="preserve">Estado</t>
+    <t xml:space="preserve">PENDIENTE</t>
   </si>
   <si>
     <t xml:space="preserve">ESTADÍSTICAS</t>
@@ -176,16 +176,22 @@
     <t xml:space="preserve">Multas aplicadas</t>
   </si>
   <si>
-    <t xml:space="preserve">Fecha de aplicación de la multa</t>
+    <t xml:space="preserve">Fecha de la multa</t>
   </si>
   <si>
     <t xml:space="preserve">Monto total de multas ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">Actas pendientes (sin resolver)</t>
+    <t xml:space="preserve">Multas de baja</t>
   </si>
   <si>
-    <t xml:space="preserve">Actas del período aún sin descargo ni multa</t>
+    <t xml:space="preserve">Fecha de la baja</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actas pendientes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actas del período sin multa aplicada ni baja</t>
   </si>
 </sst>
 </file>
@@ -385,7 +391,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -458,10 +464,6 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -503,7 +505,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="10">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -554,8 +556,15 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="FFF8CBAD"/>
+          <fgColor rgb="FFFFE699"/>
           <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFE699"/>
         </patternFill>
       </fill>
     </dxf>
@@ -569,21 +578,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9D9D9"/>
         </patternFill>
       </fill>
     </dxf>
@@ -613,7 +608,7 @@
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9D9D9"/>
+      <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FFFFFF00"/>
@@ -7018,7 +7013,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:N503"/>
+  <dimension ref="A1:M503"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -7030,11 +7025,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="70"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7087,9 +7081,6 @@
       <c r="M3" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="5" t="s">
-        <v>34</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="n">
@@ -7122,14 +7113,12 @@
       </c>
       <c r="H4" s="14"/>
       <c r="I4" s="15"/>
-      <c r="J4" s="14"/>
+      <c r="J4" s="14" t="s">
+        <v>34</v>
+      </c>
       <c r="K4" s="15"/>
       <c r="L4" s="16"/>
       <c r="M4" s="17"/>
-      <c r="N4" s="18" t="str">
-        <f aca="false">IF(B4="","",IF(J4="Sí","Multa aplicada",IF(J4="No","Sin multa",IF(H4="Sí","Descargo enviado","Pendiente"))))</f>
-        <v>Pendiente</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="str">
@@ -7166,10 +7155,6 @@
       <c r="K5" s="15"/>
       <c r="L5" s="16"/>
       <c r="M5" s="17"/>
-      <c r="N5" s="18" t="str">
-        <f aca="false">IF(B5="","",IF(J5="Sí","Multa aplicada",IF(J5="No","Sin multa",IF(H5="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="6" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="str">
@@ -7206,10 +7191,6 @@
       <c r="K6" s="15"/>
       <c r="L6" s="16"/>
       <c r="M6" s="17"/>
-      <c r="N6" s="18" t="str">
-        <f aca="false">IF(B6="","",IF(J6="Sí","Multa aplicada",IF(J6="No","Sin multa",IF(H6="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="7" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="str">
@@ -7246,10 +7227,6 @@
       <c r="K7" s="15"/>
       <c r="L7" s="16"/>
       <c r="M7" s="17"/>
-      <c r="N7" s="18" t="str">
-        <f aca="false">IF(B7="","",IF(J7="Sí","Multa aplicada",IF(J7="No","Sin multa",IF(H7="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="8" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="str">
@@ -7286,10 +7263,6 @@
       <c r="K8" s="15"/>
       <c r="L8" s="16"/>
       <c r="M8" s="17"/>
-      <c r="N8" s="18" t="str">
-        <f aca="false">IF(B8="","",IF(J8="Sí","Multa aplicada",IF(J8="No","Sin multa",IF(H8="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="9" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="str">
@@ -7326,10 +7299,6 @@
       <c r="K9" s="15"/>
       <c r="L9" s="16"/>
       <c r="M9" s="17"/>
-      <c r="N9" s="18" t="str">
-        <f aca="false">IF(B9="","",IF(J9="Sí","Multa aplicada",IF(J9="No","Sin multa",IF(H9="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="10" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="str">
@@ -7366,10 +7335,6 @@
       <c r="K10" s="15"/>
       <c r="L10" s="16"/>
       <c r="M10" s="17"/>
-      <c r="N10" s="18" t="str">
-        <f aca="false">IF(B10="","",IF(J10="Sí","Multa aplicada",IF(J10="No","Sin multa",IF(H10="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="11" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="str">
@@ -7406,10 +7371,6 @@
       <c r="K11" s="15"/>
       <c r="L11" s="16"/>
       <c r="M11" s="17"/>
-      <c r="N11" s="18" t="str">
-        <f aca="false">IF(B11="","",IF(J11="Sí","Multa aplicada",IF(J11="No","Sin multa",IF(H11="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="12" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="str">
@@ -7446,10 +7407,6 @@
       <c r="K12" s="15"/>
       <c r="L12" s="16"/>
       <c r="M12" s="17"/>
-      <c r="N12" s="18" t="str">
-        <f aca="false">IF(B12="","",IF(J12="Sí","Multa aplicada",IF(J12="No","Sin multa",IF(H12="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="13" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="str">
@@ -7486,10 +7443,6 @@
       <c r="K13" s="15"/>
       <c r="L13" s="16"/>
       <c r="M13" s="17"/>
-      <c r="N13" s="18" t="str">
-        <f aca="false">IF(B13="","",IF(J13="Sí","Multa aplicada",IF(J13="No","Sin multa",IF(H13="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="14" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="str">
@@ -7526,10 +7479,6 @@
       <c r="K14" s="15"/>
       <c r="L14" s="16"/>
       <c r="M14" s="17"/>
-      <c r="N14" s="18" t="str">
-        <f aca="false">IF(B14="","",IF(J14="Sí","Multa aplicada",IF(J14="No","Sin multa",IF(H14="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="15" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="str">
@@ -7566,10 +7515,6 @@
       <c r="K15" s="15"/>
       <c r="L15" s="16"/>
       <c r="M15" s="17"/>
-      <c r="N15" s="18" t="str">
-        <f aca="false">IF(B15="","",IF(J15="Sí","Multa aplicada",IF(J15="No","Sin multa",IF(H15="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="16" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="str">
@@ -7606,10 +7551,6 @@
       <c r="K16" s="15"/>
       <c r="L16" s="16"/>
       <c r="M16" s="17"/>
-      <c r="N16" s="18" t="str">
-        <f aca="false">IF(B16="","",IF(J16="Sí","Multa aplicada",IF(J16="No","Sin multa",IF(H16="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="17" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="str">
@@ -7646,10 +7587,6 @@
       <c r="K17" s="15"/>
       <c r="L17" s="16"/>
       <c r="M17" s="17"/>
-      <c r="N17" s="18" t="str">
-        <f aca="false">IF(B17="","",IF(J17="Sí","Multa aplicada",IF(J17="No","Sin multa",IF(H17="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="18" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="str">
@@ -7686,10 +7623,6 @@
       <c r="K18" s="15"/>
       <c r="L18" s="16"/>
       <c r="M18" s="17"/>
-      <c r="N18" s="18" t="str">
-        <f aca="false">IF(B18="","",IF(J18="Sí","Multa aplicada",IF(J18="No","Sin multa",IF(H18="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="19" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="str">
@@ -7726,10 +7659,6 @@
       <c r="K19" s="15"/>
       <c r="L19" s="16"/>
       <c r="M19" s="17"/>
-      <c r="N19" s="18" t="str">
-        <f aca="false">IF(B19="","",IF(J19="Sí","Multa aplicada",IF(J19="No","Sin multa",IF(H19="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="20" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="str">
@@ -7766,10 +7695,6 @@
       <c r="K20" s="15"/>
       <c r="L20" s="16"/>
       <c r="M20" s="17"/>
-      <c r="N20" s="18" t="str">
-        <f aca="false">IF(B20="","",IF(J20="Sí","Multa aplicada",IF(J20="No","Sin multa",IF(H20="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="21" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="str">
@@ -7806,10 +7731,6 @@
       <c r="K21" s="15"/>
       <c r="L21" s="16"/>
       <c r="M21" s="17"/>
-      <c r="N21" s="18" t="str">
-        <f aca="false">IF(B21="","",IF(J21="Sí","Multa aplicada",IF(J21="No","Sin multa",IF(H21="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="22" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="str">
@@ -7846,10 +7767,6 @@
       <c r="K22" s="15"/>
       <c r="L22" s="16"/>
       <c r="M22" s="17"/>
-      <c r="N22" s="18" t="str">
-        <f aca="false">IF(B22="","",IF(J22="Sí","Multa aplicada",IF(J22="No","Sin multa",IF(H22="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="23" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="str">
@@ -7886,10 +7803,6 @@
       <c r="K23" s="15"/>
       <c r="L23" s="16"/>
       <c r="M23" s="17"/>
-      <c r="N23" s="18" t="str">
-        <f aca="false">IF(B23="","",IF(J23="Sí","Multa aplicada",IF(J23="No","Sin multa",IF(H23="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="24" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="str">
@@ -7926,10 +7839,6 @@
       <c r="K24" s="15"/>
       <c r="L24" s="16"/>
       <c r="M24" s="17"/>
-      <c r="N24" s="18" t="str">
-        <f aca="false">IF(B24="","",IF(J24="Sí","Multa aplicada",IF(J24="No","Sin multa",IF(H24="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="25" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="str">
@@ -7966,10 +7875,6 @@
       <c r="K25" s="15"/>
       <c r="L25" s="16"/>
       <c r="M25" s="17"/>
-      <c r="N25" s="18" t="str">
-        <f aca="false">IF(B25="","",IF(J25="Sí","Multa aplicada",IF(J25="No","Sin multa",IF(H25="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="26" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="6" t="str">
@@ -8006,10 +7911,6 @@
       <c r="K26" s="15"/>
       <c r="L26" s="16"/>
       <c r="M26" s="17"/>
-      <c r="N26" s="18" t="str">
-        <f aca="false">IF(B26="","",IF(J26="Sí","Multa aplicada",IF(J26="No","Sin multa",IF(H26="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="27" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="6" t="str">
@@ -8046,10 +7947,6 @@
       <c r="K27" s="15"/>
       <c r="L27" s="16"/>
       <c r="M27" s="17"/>
-      <c r="N27" s="18" t="str">
-        <f aca="false">IF(B27="","",IF(J27="Sí","Multa aplicada",IF(J27="No","Sin multa",IF(H27="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="28" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="str">
@@ -8086,10 +7983,6 @@
       <c r="K28" s="15"/>
       <c r="L28" s="16"/>
       <c r="M28" s="17"/>
-      <c r="N28" s="18" t="str">
-        <f aca="false">IF(B28="","",IF(J28="Sí","Multa aplicada",IF(J28="No","Sin multa",IF(H28="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="29" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="str">
@@ -8126,10 +8019,6 @@
       <c r="K29" s="15"/>
       <c r="L29" s="16"/>
       <c r="M29" s="17"/>
-      <c r="N29" s="18" t="str">
-        <f aca="false">IF(B29="","",IF(J29="Sí","Multa aplicada",IF(J29="No","Sin multa",IF(H29="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="30" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="6" t="str">
@@ -8166,10 +8055,6 @@
       <c r="K30" s="15"/>
       <c r="L30" s="16"/>
       <c r="M30" s="17"/>
-      <c r="N30" s="18" t="str">
-        <f aca="false">IF(B30="","",IF(J30="Sí","Multa aplicada",IF(J30="No","Sin multa",IF(H30="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="31" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="str">
@@ -8206,10 +8091,6 @@
       <c r="K31" s="15"/>
       <c r="L31" s="16"/>
       <c r="M31" s="17"/>
-      <c r="N31" s="18" t="str">
-        <f aca="false">IF(B31="","",IF(J31="Sí","Multa aplicada",IF(J31="No","Sin multa",IF(H31="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="32" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="6" t="str">
@@ -8246,10 +8127,6 @@
       <c r="K32" s="15"/>
       <c r="L32" s="16"/>
       <c r="M32" s="17"/>
-      <c r="N32" s="18" t="str">
-        <f aca="false">IF(B32="","",IF(J32="Sí","Multa aplicada",IF(J32="No","Sin multa",IF(H32="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="33" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="str">
@@ -8286,10 +8163,6 @@
       <c r="K33" s="15"/>
       <c r="L33" s="16"/>
       <c r="M33" s="17"/>
-      <c r="N33" s="18" t="str">
-        <f aca="false">IF(B33="","",IF(J33="Sí","Multa aplicada",IF(J33="No","Sin multa",IF(H33="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="34" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="6" t="str">
@@ -8326,10 +8199,6 @@
       <c r="K34" s="15"/>
       <c r="L34" s="16"/>
       <c r="M34" s="17"/>
-      <c r="N34" s="18" t="str">
-        <f aca="false">IF(B34="","",IF(J34="Sí","Multa aplicada",IF(J34="No","Sin multa",IF(H34="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="35" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="str">
@@ -8366,10 +8235,6 @@
       <c r="K35" s="15"/>
       <c r="L35" s="16"/>
       <c r="M35" s="17"/>
-      <c r="N35" s="18" t="str">
-        <f aca="false">IF(B35="","",IF(J35="Sí","Multa aplicada",IF(J35="No","Sin multa",IF(H35="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="36" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="str">
@@ -8406,10 +8271,6 @@
       <c r="K36" s="15"/>
       <c r="L36" s="16"/>
       <c r="M36" s="17"/>
-      <c r="N36" s="18" t="str">
-        <f aca="false">IF(B36="","",IF(J36="Sí","Multa aplicada",IF(J36="No","Sin multa",IF(H36="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="37" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="str">
@@ -8446,10 +8307,6 @@
       <c r="K37" s="15"/>
       <c r="L37" s="16"/>
       <c r="M37" s="17"/>
-      <c r="N37" s="18" t="str">
-        <f aca="false">IF(B37="","",IF(J37="Sí","Multa aplicada",IF(J37="No","Sin multa",IF(H37="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="38" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="6" t="str">
@@ -8486,10 +8343,6 @@
       <c r="K38" s="15"/>
       <c r="L38" s="16"/>
       <c r="M38" s="17"/>
-      <c r="N38" s="18" t="str">
-        <f aca="false">IF(B38="","",IF(J38="Sí","Multa aplicada",IF(J38="No","Sin multa",IF(H38="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="39" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="str">
@@ -8526,10 +8379,6 @@
       <c r="K39" s="15"/>
       <c r="L39" s="16"/>
       <c r="M39" s="17"/>
-      <c r="N39" s="18" t="str">
-        <f aca="false">IF(B39="","",IF(J39="Sí","Multa aplicada",IF(J39="No","Sin multa",IF(H39="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="40" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="6" t="str">
@@ -8566,10 +8415,6 @@
       <c r="K40" s="15"/>
       <c r="L40" s="16"/>
       <c r="M40" s="17"/>
-      <c r="N40" s="18" t="str">
-        <f aca="false">IF(B40="","",IF(J40="Sí","Multa aplicada",IF(J40="No","Sin multa",IF(H40="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="41" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="str">
@@ -8606,10 +8451,6 @@
       <c r="K41" s="15"/>
       <c r="L41" s="16"/>
       <c r="M41" s="17"/>
-      <c r="N41" s="18" t="str">
-        <f aca="false">IF(B41="","",IF(J41="Sí","Multa aplicada",IF(J41="No","Sin multa",IF(H41="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="42" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="6" t="str">
@@ -8646,10 +8487,6 @@
       <c r="K42" s="15"/>
       <c r="L42" s="16"/>
       <c r="M42" s="17"/>
-      <c r="N42" s="18" t="str">
-        <f aca="false">IF(B42="","",IF(J42="Sí","Multa aplicada",IF(J42="No","Sin multa",IF(H42="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="43" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="6" t="str">
@@ -8686,10 +8523,6 @@
       <c r="K43" s="15"/>
       <c r="L43" s="16"/>
       <c r="M43" s="17"/>
-      <c r="N43" s="18" t="str">
-        <f aca="false">IF(B43="","",IF(J43="Sí","Multa aplicada",IF(J43="No","Sin multa",IF(H43="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="44" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="6" t="str">
@@ -8726,10 +8559,6 @@
       <c r="K44" s="15"/>
       <c r="L44" s="16"/>
       <c r="M44" s="17"/>
-      <c r="N44" s="18" t="str">
-        <f aca="false">IF(B44="","",IF(J44="Sí","Multa aplicada",IF(J44="No","Sin multa",IF(H44="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="45" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="6" t="str">
@@ -8766,10 +8595,6 @@
       <c r="K45" s="15"/>
       <c r="L45" s="16"/>
       <c r="M45" s="17"/>
-      <c r="N45" s="18" t="str">
-        <f aca="false">IF(B45="","",IF(J45="Sí","Multa aplicada",IF(J45="No","Sin multa",IF(H45="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="46" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="6" t="str">
@@ -8806,10 +8631,6 @@
       <c r="K46" s="15"/>
       <c r="L46" s="16"/>
       <c r="M46" s="17"/>
-      <c r="N46" s="18" t="str">
-        <f aca="false">IF(B46="","",IF(J46="Sí","Multa aplicada",IF(J46="No","Sin multa",IF(H46="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="47" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="6" t="str">
@@ -8846,10 +8667,6 @@
       <c r="K47" s="15"/>
       <c r="L47" s="16"/>
       <c r="M47" s="17"/>
-      <c r="N47" s="18" t="str">
-        <f aca="false">IF(B47="","",IF(J47="Sí","Multa aplicada",IF(J47="No","Sin multa",IF(H47="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="48" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="6" t="str">
@@ -8886,10 +8703,6 @@
       <c r="K48" s="15"/>
       <c r="L48" s="16"/>
       <c r="M48" s="17"/>
-      <c r="N48" s="18" t="str">
-        <f aca="false">IF(B48="","",IF(J48="Sí","Multa aplicada",IF(J48="No","Sin multa",IF(H48="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="49" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="6" t="str">
@@ -8926,10 +8739,6 @@
       <c r="K49" s="15"/>
       <c r="L49" s="16"/>
       <c r="M49" s="17"/>
-      <c r="N49" s="18" t="str">
-        <f aca="false">IF(B49="","",IF(J49="Sí","Multa aplicada",IF(J49="No","Sin multa",IF(H49="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="50" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="6" t="str">
@@ -8966,10 +8775,6 @@
       <c r="K50" s="15"/>
       <c r="L50" s="16"/>
       <c r="M50" s="17"/>
-      <c r="N50" s="18" t="str">
-        <f aca="false">IF(B50="","",IF(J50="Sí","Multa aplicada",IF(J50="No","Sin multa",IF(H50="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="51" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="6" t="str">
@@ -9006,10 +8811,6 @@
       <c r="K51" s="15"/>
       <c r="L51" s="16"/>
       <c r="M51" s="17"/>
-      <c r="N51" s="18" t="str">
-        <f aca="false">IF(B51="","",IF(J51="Sí","Multa aplicada",IF(J51="No","Sin multa",IF(H51="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="52" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="6" t="str">
@@ -9046,10 +8847,6 @@
       <c r="K52" s="15"/>
       <c r="L52" s="16"/>
       <c r="M52" s="17"/>
-      <c r="N52" s="18" t="str">
-        <f aca="false">IF(B52="","",IF(J52="Sí","Multa aplicada",IF(J52="No","Sin multa",IF(H52="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="53" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="6" t="str">
@@ -9086,10 +8883,6 @@
       <c r="K53" s="15"/>
       <c r="L53" s="16"/>
       <c r="M53" s="17"/>
-      <c r="N53" s="18" t="str">
-        <f aca="false">IF(B53="","",IF(J53="Sí","Multa aplicada",IF(J53="No","Sin multa",IF(H53="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="54" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="6" t="str">
@@ -9126,10 +8919,6 @@
       <c r="K54" s="15"/>
       <c r="L54" s="16"/>
       <c r="M54" s="17"/>
-      <c r="N54" s="18" t="str">
-        <f aca="false">IF(B54="","",IF(J54="Sí","Multa aplicada",IF(J54="No","Sin multa",IF(H54="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="55" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="6" t="str">
@@ -9166,10 +8955,6 @@
       <c r="K55" s="15"/>
       <c r="L55" s="16"/>
       <c r="M55" s="17"/>
-      <c r="N55" s="18" t="str">
-        <f aca="false">IF(B55="","",IF(J55="Sí","Multa aplicada",IF(J55="No","Sin multa",IF(H55="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="56" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="6" t="str">
@@ -9206,10 +8991,6 @@
       <c r="K56" s="15"/>
       <c r="L56" s="16"/>
       <c r="M56" s="17"/>
-      <c r="N56" s="18" t="str">
-        <f aca="false">IF(B56="","",IF(J56="Sí","Multa aplicada",IF(J56="No","Sin multa",IF(H56="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="57" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="6" t="str">
@@ -9246,10 +9027,6 @@
       <c r="K57" s="15"/>
       <c r="L57" s="16"/>
       <c r="M57" s="17"/>
-      <c r="N57" s="18" t="str">
-        <f aca="false">IF(B57="","",IF(J57="Sí","Multa aplicada",IF(J57="No","Sin multa",IF(H57="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="58" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="6" t="str">
@@ -9286,10 +9063,6 @@
       <c r="K58" s="15"/>
       <c r="L58" s="16"/>
       <c r="M58" s="17"/>
-      <c r="N58" s="18" t="str">
-        <f aca="false">IF(B58="","",IF(J58="Sí","Multa aplicada",IF(J58="No","Sin multa",IF(H58="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="59" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="6" t="str">
@@ -9326,10 +9099,6 @@
       <c r="K59" s="15"/>
       <c r="L59" s="16"/>
       <c r="M59" s="17"/>
-      <c r="N59" s="18" t="str">
-        <f aca="false">IF(B59="","",IF(J59="Sí","Multa aplicada",IF(J59="No","Sin multa",IF(H59="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="60" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="6" t="str">
@@ -9366,10 +9135,6 @@
       <c r="K60" s="15"/>
       <c r="L60" s="16"/>
       <c r="M60" s="17"/>
-      <c r="N60" s="18" t="str">
-        <f aca="false">IF(B60="","",IF(J60="Sí","Multa aplicada",IF(J60="No","Sin multa",IF(H60="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="61" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="6" t="str">
@@ -9406,10 +9171,6 @@
       <c r="K61" s="15"/>
       <c r="L61" s="16"/>
       <c r="M61" s="17"/>
-      <c r="N61" s="18" t="str">
-        <f aca="false">IF(B61="","",IF(J61="Sí","Multa aplicada",IF(J61="No","Sin multa",IF(H61="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="62" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="6" t="str">
@@ -9446,10 +9207,6 @@
       <c r="K62" s="15"/>
       <c r="L62" s="16"/>
       <c r="M62" s="17"/>
-      <c r="N62" s="18" t="str">
-        <f aca="false">IF(B62="","",IF(J62="Sí","Multa aplicada",IF(J62="No","Sin multa",IF(H62="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="63" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="6" t="str">
@@ -9486,10 +9243,6 @@
       <c r="K63" s="15"/>
       <c r="L63" s="16"/>
       <c r="M63" s="17"/>
-      <c r="N63" s="18" t="str">
-        <f aca="false">IF(B63="","",IF(J63="Sí","Multa aplicada",IF(J63="No","Sin multa",IF(H63="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="64" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="6" t="str">
@@ -9526,10 +9279,6 @@
       <c r="K64" s="15"/>
       <c r="L64" s="16"/>
       <c r="M64" s="17"/>
-      <c r="N64" s="18" t="str">
-        <f aca="false">IF(B64="","",IF(J64="Sí","Multa aplicada",IF(J64="No","Sin multa",IF(H64="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="65" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="6" t="str">
@@ -9566,10 +9315,6 @@
       <c r="K65" s="15"/>
       <c r="L65" s="16"/>
       <c r="M65" s="17"/>
-      <c r="N65" s="18" t="str">
-        <f aca="false">IF(B65="","",IF(J65="Sí","Multa aplicada",IF(J65="No","Sin multa",IF(H65="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="66" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="6" t="str">
@@ -9606,10 +9351,6 @@
       <c r="K66" s="15"/>
       <c r="L66" s="16"/>
       <c r="M66" s="17"/>
-      <c r="N66" s="18" t="str">
-        <f aca="false">IF(B66="","",IF(J66="Sí","Multa aplicada",IF(J66="No","Sin multa",IF(H66="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="67" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="6" t="str">
@@ -9646,10 +9387,6 @@
       <c r="K67" s="15"/>
       <c r="L67" s="16"/>
       <c r="M67" s="17"/>
-      <c r="N67" s="18" t="str">
-        <f aca="false">IF(B67="","",IF(J67="Sí","Multa aplicada",IF(J67="No","Sin multa",IF(H67="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="68" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="6" t="str">
@@ -9686,10 +9423,6 @@
       <c r="K68" s="15"/>
       <c r="L68" s="16"/>
       <c r="M68" s="17"/>
-      <c r="N68" s="18" t="str">
-        <f aca="false">IF(B68="","",IF(J68="Sí","Multa aplicada",IF(J68="No","Sin multa",IF(H68="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="69" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="6" t="str">
@@ -9726,10 +9459,6 @@
       <c r="K69" s="15"/>
       <c r="L69" s="16"/>
       <c r="M69" s="17"/>
-      <c r="N69" s="18" t="str">
-        <f aca="false">IF(B69="","",IF(J69="Sí","Multa aplicada",IF(J69="No","Sin multa",IF(H69="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="70" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="6" t="str">
@@ -9766,10 +9495,6 @@
       <c r="K70" s="15"/>
       <c r="L70" s="16"/>
       <c r="M70" s="17"/>
-      <c r="N70" s="18" t="str">
-        <f aca="false">IF(B70="","",IF(J70="Sí","Multa aplicada",IF(J70="No","Sin multa",IF(H70="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="71" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="6" t="str">
@@ -9806,10 +9531,6 @@
       <c r="K71" s="15"/>
       <c r="L71" s="16"/>
       <c r="M71" s="17"/>
-      <c r="N71" s="18" t="str">
-        <f aca="false">IF(B71="","",IF(J71="Sí","Multa aplicada",IF(J71="No","Sin multa",IF(H71="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="72" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="6" t="str">
@@ -9846,10 +9567,6 @@
       <c r="K72" s="15"/>
       <c r="L72" s="16"/>
       <c r="M72" s="17"/>
-      <c r="N72" s="18" t="str">
-        <f aca="false">IF(B72="","",IF(J72="Sí","Multa aplicada",IF(J72="No","Sin multa",IF(H72="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="73" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="6" t="str">
@@ -9886,10 +9603,6 @@
       <c r="K73" s="15"/>
       <c r="L73" s="16"/>
       <c r="M73" s="17"/>
-      <c r="N73" s="18" t="str">
-        <f aca="false">IF(B73="","",IF(J73="Sí","Multa aplicada",IF(J73="No","Sin multa",IF(H73="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="74" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="6" t="str">
@@ -9926,10 +9639,6 @@
       <c r="K74" s="15"/>
       <c r="L74" s="16"/>
       <c r="M74" s="17"/>
-      <c r="N74" s="18" t="str">
-        <f aca="false">IF(B74="","",IF(J74="Sí","Multa aplicada",IF(J74="No","Sin multa",IF(H74="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="75" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="6" t="str">
@@ -9966,10 +9675,6 @@
       <c r="K75" s="15"/>
       <c r="L75" s="16"/>
       <c r="M75" s="17"/>
-      <c r="N75" s="18" t="str">
-        <f aca="false">IF(B75="","",IF(J75="Sí","Multa aplicada",IF(J75="No","Sin multa",IF(H75="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="76" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="6" t="str">
@@ -10006,10 +9711,6 @@
       <c r="K76" s="15"/>
       <c r="L76" s="16"/>
       <c r="M76" s="17"/>
-      <c r="N76" s="18" t="str">
-        <f aca="false">IF(B76="","",IF(J76="Sí","Multa aplicada",IF(J76="No","Sin multa",IF(H76="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="77" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="6" t="str">
@@ -10046,10 +9747,6 @@
       <c r="K77" s="15"/>
       <c r="L77" s="16"/>
       <c r="M77" s="17"/>
-      <c r="N77" s="18" t="str">
-        <f aca="false">IF(B77="","",IF(J77="Sí","Multa aplicada",IF(J77="No","Sin multa",IF(H77="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="78" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="6" t="str">
@@ -10086,10 +9783,6 @@
       <c r="K78" s="15"/>
       <c r="L78" s="16"/>
       <c r="M78" s="17"/>
-      <c r="N78" s="18" t="str">
-        <f aca="false">IF(B78="","",IF(J78="Sí","Multa aplicada",IF(J78="No","Sin multa",IF(H78="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="79" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="6" t="str">
@@ -10126,10 +9819,6 @@
       <c r="K79" s="15"/>
       <c r="L79" s="16"/>
       <c r="M79" s="17"/>
-      <c r="N79" s="18" t="str">
-        <f aca="false">IF(B79="","",IF(J79="Sí","Multa aplicada",IF(J79="No","Sin multa",IF(H79="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="80" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="6" t="str">
@@ -10166,10 +9855,6 @@
       <c r="K80" s="15"/>
       <c r="L80" s="16"/>
       <c r="M80" s="17"/>
-      <c r="N80" s="18" t="str">
-        <f aca="false">IF(B80="","",IF(J80="Sí","Multa aplicada",IF(J80="No","Sin multa",IF(H80="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="81" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="6" t="str">
@@ -10206,10 +9891,6 @@
       <c r="K81" s="15"/>
       <c r="L81" s="16"/>
       <c r="M81" s="17"/>
-      <c r="N81" s="18" t="str">
-        <f aca="false">IF(B81="","",IF(J81="Sí","Multa aplicada",IF(J81="No","Sin multa",IF(H81="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="82" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="6" t="str">
@@ -10246,10 +9927,6 @@
       <c r="K82" s="15"/>
       <c r="L82" s="16"/>
       <c r="M82" s="17"/>
-      <c r="N82" s="18" t="str">
-        <f aca="false">IF(B82="","",IF(J82="Sí","Multa aplicada",IF(J82="No","Sin multa",IF(H82="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="83" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="6" t="str">
@@ -10286,10 +9963,6 @@
       <c r="K83" s="15"/>
       <c r="L83" s="16"/>
       <c r="M83" s="17"/>
-      <c r="N83" s="18" t="str">
-        <f aca="false">IF(B83="","",IF(J83="Sí","Multa aplicada",IF(J83="No","Sin multa",IF(H83="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="84" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="6" t="str">
@@ -10326,10 +9999,6 @@
       <c r="K84" s="15"/>
       <c r="L84" s="16"/>
       <c r="M84" s="17"/>
-      <c r="N84" s="18" t="str">
-        <f aca="false">IF(B84="","",IF(J84="Sí","Multa aplicada",IF(J84="No","Sin multa",IF(H84="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="85" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="6" t="str">
@@ -10366,10 +10035,6 @@
       <c r="K85" s="15"/>
       <c r="L85" s="16"/>
       <c r="M85" s="17"/>
-      <c r="N85" s="18" t="str">
-        <f aca="false">IF(B85="","",IF(J85="Sí","Multa aplicada",IF(J85="No","Sin multa",IF(H85="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="86" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="6" t="str">
@@ -10406,10 +10071,6 @@
       <c r="K86" s="15"/>
       <c r="L86" s="16"/>
       <c r="M86" s="17"/>
-      <c r="N86" s="18" t="str">
-        <f aca="false">IF(B86="","",IF(J86="Sí","Multa aplicada",IF(J86="No","Sin multa",IF(H86="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="87" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="6" t="str">
@@ -10446,10 +10107,6 @@
       <c r="K87" s="15"/>
       <c r="L87" s="16"/>
       <c r="M87" s="17"/>
-      <c r="N87" s="18" t="str">
-        <f aca="false">IF(B87="","",IF(J87="Sí","Multa aplicada",IF(J87="No","Sin multa",IF(H87="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="88" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="6" t="str">
@@ -10486,10 +10143,6 @@
       <c r="K88" s="15"/>
       <c r="L88" s="16"/>
       <c r="M88" s="17"/>
-      <c r="N88" s="18" t="str">
-        <f aca="false">IF(B88="","",IF(J88="Sí","Multa aplicada",IF(J88="No","Sin multa",IF(H88="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="89" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="6" t="str">
@@ -10526,10 +10179,6 @@
       <c r="K89" s="15"/>
       <c r="L89" s="16"/>
       <c r="M89" s="17"/>
-      <c r="N89" s="18" t="str">
-        <f aca="false">IF(B89="","",IF(J89="Sí","Multa aplicada",IF(J89="No","Sin multa",IF(H89="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="90" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="6" t="str">
@@ -10566,10 +10215,6 @@
       <c r="K90" s="15"/>
       <c r="L90" s="16"/>
       <c r="M90" s="17"/>
-      <c r="N90" s="18" t="str">
-        <f aca="false">IF(B90="","",IF(J90="Sí","Multa aplicada",IF(J90="No","Sin multa",IF(H90="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="91" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="6" t="str">
@@ -10606,10 +10251,6 @@
       <c r="K91" s="15"/>
       <c r="L91" s="16"/>
       <c r="M91" s="17"/>
-      <c r="N91" s="18" t="str">
-        <f aca="false">IF(B91="","",IF(J91="Sí","Multa aplicada",IF(J91="No","Sin multa",IF(H91="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="92" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="6" t="str">
@@ -10646,10 +10287,6 @@
       <c r="K92" s="15"/>
       <c r="L92" s="16"/>
       <c r="M92" s="17"/>
-      <c r="N92" s="18" t="str">
-        <f aca="false">IF(B92="","",IF(J92="Sí","Multa aplicada",IF(J92="No","Sin multa",IF(H92="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="93" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="6" t="str">
@@ -10686,10 +10323,6 @@
       <c r="K93" s="15"/>
       <c r="L93" s="16"/>
       <c r="M93" s="17"/>
-      <c r="N93" s="18" t="str">
-        <f aca="false">IF(B93="","",IF(J93="Sí","Multa aplicada",IF(J93="No","Sin multa",IF(H93="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="94" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="6" t="str">
@@ -10726,10 +10359,6 @@
       <c r="K94" s="15"/>
       <c r="L94" s="16"/>
       <c r="M94" s="17"/>
-      <c r="N94" s="18" t="str">
-        <f aca="false">IF(B94="","",IF(J94="Sí","Multa aplicada",IF(J94="No","Sin multa",IF(H94="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="95" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="6" t="str">
@@ -10766,10 +10395,6 @@
       <c r="K95" s="15"/>
       <c r="L95" s="16"/>
       <c r="M95" s="17"/>
-      <c r="N95" s="18" t="str">
-        <f aca="false">IF(B95="","",IF(J95="Sí","Multa aplicada",IF(J95="No","Sin multa",IF(H95="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="96" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="6" t="str">
@@ -10806,10 +10431,6 @@
       <c r="K96" s="15"/>
       <c r="L96" s="16"/>
       <c r="M96" s="17"/>
-      <c r="N96" s="18" t="str">
-        <f aca="false">IF(B96="","",IF(J96="Sí","Multa aplicada",IF(J96="No","Sin multa",IF(H96="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="97" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="6" t="str">
@@ -10846,10 +10467,6 @@
       <c r="K97" s="15"/>
       <c r="L97" s="16"/>
       <c r="M97" s="17"/>
-      <c r="N97" s="18" t="str">
-        <f aca="false">IF(B97="","",IF(J97="Sí","Multa aplicada",IF(J97="No","Sin multa",IF(H97="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="98" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="6" t="str">
@@ -10886,10 +10503,6 @@
       <c r="K98" s="15"/>
       <c r="L98" s="16"/>
       <c r="M98" s="17"/>
-      <c r="N98" s="18" t="str">
-        <f aca="false">IF(B98="","",IF(J98="Sí","Multa aplicada",IF(J98="No","Sin multa",IF(H98="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="99" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="6" t="str">
@@ -10926,10 +10539,6 @@
       <c r="K99" s="15"/>
       <c r="L99" s="16"/>
       <c r="M99" s="17"/>
-      <c r="N99" s="18" t="str">
-        <f aca="false">IF(B99="","",IF(J99="Sí","Multa aplicada",IF(J99="No","Sin multa",IF(H99="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="100" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="6" t="str">
@@ -10966,10 +10575,6 @@
       <c r="K100" s="15"/>
       <c r="L100" s="16"/>
       <c r="M100" s="17"/>
-      <c r="N100" s="18" t="str">
-        <f aca="false">IF(B100="","",IF(J100="Sí","Multa aplicada",IF(J100="No","Sin multa",IF(H100="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="101" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="6" t="str">
@@ -11006,10 +10611,6 @@
       <c r="K101" s="15"/>
       <c r="L101" s="16"/>
       <c r="M101" s="17"/>
-      <c r="N101" s="18" t="str">
-        <f aca="false">IF(B101="","",IF(J101="Sí","Multa aplicada",IF(J101="No","Sin multa",IF(H101="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="102" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="6" t="str">
@@ -11046,10 +10647,6 @@
       <c r="K102" s="15"/>
       <c r="L102" s="16"/>
       <c r="M102" s="17"/>
-      <c r="N102" s="18" t="str">
-        <f aca="false">IF(B102="","",IF(J102="Sí","Multa aplicada",IF(J102="No","Sin multa",IF(H102="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="103" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="6" t="str">
@@ -11086,10 +10683,6 @@
       <c r="K103" s="15"/>
       <c r="L103" s="16"/>
       <c r="M103" s="17"/>
-      <c r="N103" s="18" t="str">
-        <f aca="false">IF(B103="","",IF(J103="Sí","Multa aplicada",IF(J103="No","Sin multa",IF(H103="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="104" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="6" t="str">
@@ -11126,10 +10719,6 @@
       <c r="K104" s="15"/>
       <c r="L104" s="16"/>
       <c r="M104" s="17"/>
-      <c r="N104" s="18" t="str">
-        <f aca="false">IF(B104="","",IF(J104="Sí","Multa aplicada",IF(J104="No","Sin multa",IF(H104="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="105" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="6" t="str">
@@ -11166,10 +10755,6 @@
       <c r="K105" s="15"/>
       <c r="L105" s="16"/>
       <c r="M105" s="17"/>
-      <c r="N105" s="18" t="str">
-        <f aca="false">IF(B105="","",IF(J105="Sí","Multa aplicada",IF(J105="No","Sin multa",IF(H105="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="106" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="6" t="str">
@@ -11206,10 +10791,6 @@
       <c r="K106" s="15"/>
       <c r="L106" s="16"/>
       <c r="M106" s="17"/>
-      <c r="N106" s="18" t="str">
-        <f aca="false">IF(B106="","",IF(J106="Sí","Multa aplicada",IF(J106="No","Sin multa",IF(H106="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="107" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="6" t="str">
@@ -11246,10 +10827,6 @@
       <c r="K107" s="15"/>
       <c r="L107" s="16"/>
       <c r="M107" s="17"/>
-      <c r="N107" s="18" t="str">
-        <f aca="false">IF(B107="","",IF(J107="Sí","Multa aplicada",IF(J107="No","Sin multa",IF(H107="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="108" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="6" t="str">
@@ -11286,10 +10863,6 @@
       <c r="K108" s="15"/>
       <c r="L108" s="16"/>
       <c r="M108" s="17"/>
-      <c r="N108" s="18" t="str">
-        <f aca="false">IF(B108="","",IF(J108="Sí","Multa aplicada",IF(J108="No","Sin multa",IF(H108="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="109" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="6" t="str">
@@ -11326,10 +10899,6 @@
       <c r="K109" s="15"/>
       <c r="L109" s="16"/>
       <c r="M109" s="17"/>
-      <c r="N109" s="18" t="str">
-        <f aca="false">IF(B109="","",IF(J109="Sí","Multa aplicada",IF(J109="No","Sin multa",IF(H109="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="110" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="6" t="str">
@@ -11366,10 +10935,6 @@
       <c r="K110" s="15"/>
       <c r="L110" s="16"/>
       <c r="M110" s="17"/>
-      <c r="N110" s="18" t="str">
-        <f aca="false">IF(B110="","",IF(J110="Sí","Multa aplicada",IF(J110="No","Sin multa",IF(H110="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="111" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="6" t="str">
@@ -11406,10 +10971,6 @@
       <c r="K111" s="15"/>
       <c r="L111" s="16"/>
       <c r="M111" s="17"/>
-      <c r="N111" s="18" t="str">
-        <f aca="false">IF(B111="","",IF(J111="Sí","Multa aplicada",IF(J111="No","Sin multa",IF(H111="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="112" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="6" t="str">
@@ -11446,10 +11007,6 @@
       <c r="K112" s="15"/>
       <c r="L112" s="16"/>
       <c r="M112" s="17"/>
-      <c r="N112" s="18" t="str">
-        <f aca="false">IF(B112="","",IF(J112="Sí","Multa aplicada",IF(J112="No","Sin multa",IF(H112="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="113" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="6" t="str">
@@ -11486,10 +11043,6 @@
       <c r="K113" s="15"/>
       <c r="L113" s="16"/>
       <c r="M113" s="17"/>
-      <c r="N113" s="18" t="str">
-        <f aca="false">IF(B113="","",IF(J113="Sí","Multa aplicada",IF(J113="No","Sin multa",IF(H113="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="114" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="6" t="str">
@@ -11526,10 +11079,6 @@
       <c r="K114" s="15"/>
       <c r="L114" s="16"/>
       <c r="M114" s="17"/>
-      <c r="N114" s="18" t="str">
-        <f aca="false">IF(B114="","",IF(J114="Sí","Multa aplicada",IF(J114="No","Sin multa",IF(H114="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="115" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="6" t="str">
@@ -11566,10 +11115,6 @@
       <c r="K115" s="15"/>
       <c r="L115" s="16"/>
       <c r="M115" s="17"/>
-      <c r="N115" s="18" t="str">
-        <f aca="false">IF(B115="","",IF(J115="Sí","Multa aplicada",IF(J115="No","Sin multa",IF(H115="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="116" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="6" t="str">
@@ -11606,10 +11151,6 @@
       <c r="K116" s="15"/>
       <c r="L116" s="16"/>
       <c r="M116" s="17"/>
-      <c r="N116" s="18" t="str">
-        <f aca="false">IF(B116="","",IF(J116="Sí","Multa aplicada",IF(J116="No","Sin multa",IF(H116="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="117" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="6" t="str">
@@ -11646,10 +11187,6 @@
       <c r="K117" s="15"/>
       <c r="L117" s="16"/>
       <c r="M117" s="17"/>
-      <c r="N117" s="18" t="str">
-        <f aca="false">IF(B117="","",IF(J117="Sí","Multa aplicada",IF(J117="No","Sin multa",IF(H117="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="118" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="6" t="str">
@@ -11686,10 +11223,6 @@
       <c r="K118" s="15"/>
       <c r="L118" s="16"/>
       <c r="M118" s="17"/>
-      <c r="N118" s="18" t="str">
-        <f aca="false">IF(B118="","",IF(J118="Sí","Multa aplicada",IF(J118="No","Sin multa",IF(H118="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="119" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="6" t="str">
@@ -11726,10 +11259,6 @@
       <c r="K119" s="15"/>
       <c r="L119" s="16"/>
       <c r="M119" s="17"/>
-      <c r="N119" s="18" t="str">
-        <f aca="false">IF(B119="","",IF(J119="Sí","Multa aplicada",IF(J119="No","Sin multa",IF(H119="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="120" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="6" t="str">
@@ -11766,10 +11295,6 @@
       <c r="K120" s="15"/>
       <c r="L120" s="16"/>
       <c r="M120" s="17"/>
-      <c r="N120" s="18" t="str">
-        <f aca="false">IF(B120="","",IF(J120="Sí","Multa aplicada",IF(J120="No","Sin multa",IF(H120="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="121" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="6" t="str">
@@ -11806,10 +11331,6 @@
       <c r="K121" s="15"/>
       <c r="L121" s="16"/>
       <c r="M121" s="17"/>
-      <c r="N121" s="18" t="str">
-        <f aca="false">IF(B121="","",IF(J121="Sí","Multa aplicada",IF(J121="No","Sin multa",IF(H121="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="122" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="6" t="str">
@@ -11846,10 +11367,6 @@
       <c r="K122" s="15"/>
       <c r="L122" s="16"/>
       <c r="M122" s="17"/>
-      <c r="N122" s="18" t="str">
-        <f aca="false">IF(B122="","",IF(J122="Sí","Multa aplicada",IF(J122="No","Sin multa",IF(H122="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="123" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="6" t="str">
@@ -11886,10 +11403,6 @@
       <c r="K123" s="15"/>
       <c r="L123" s="16"/>
       <c r="M123" s="17"/>
-      <c r="N123" s="18" t="str">
-        <f aca="false">IF(B123="","",IF(J123="Sí","Multa aplicada",IF(J123="No","Sin multa",IF(H123="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="124" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="6" t="str">
@@ -11926,10 +11439,6 @@
       <c r="K124" s="15"/>
       <c r="L124" s="16"/>
       <c r="M124" s="17"/>
-      <c r="N124" s="18" t="str">
-        <f aca="false">IF(B124="","",IF(J124="Sí","Multa aplicada",IF(J124="No","Sin multa",IF(H124="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="125" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="6" t="str">
@@ -11966,10 +11475,6 @@
       <c r="K125" s="15"/>
       <c r="L125" s="16"/>
       <c r="M125" s="17"/>
-      <c r="N125" s="18" t="str">
-        <f aca="false">IF(B125="","",IF(J125="Sí","Multa aplicada",IF(J125="No","Sin multa",IF(H125="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="126" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="6" t="str">
@@ -12006,10 +11511,6 @@
       <c r="K126" s="15"/>
       <c r="L126" s="16"/>
       <c r="M126" s="17"/>
-      <c r="N126" s="18" t="str">
-        <f aca="false">IF(B126="","",IF(J126="Sí","Multa aplicada",IF(J126="No","Sin multa",IF(H126="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="127" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="6" t="str">
@@ -12046,10 +11547,6 @@
       <c r="K127" s="15"/>
       <c r="L127" s="16"/>
       <c r="M127" s="17"/>
-      <c r="N127" s="18" t="str">
-        <f aca="false">IF(B127="","",IF(J127="Sí","Multa aplicada",IF(J127="No","Sin multa",IF(H127="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="128" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="6" t="str">
@@ -12086,10 +11583,6 @@
       <c r="K128" s="15"/>
       <c r="L128" s="16"/>
       <c r="M128" s="17"/>
-      <c r="N128" s="18" t="str">
-        <f aca="false">IF(B128="","",IF(J128="Sí","Multa aplicada",IF(J128="No","Sin multa",IF(H128="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="129" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="6" t="str">
@@ -12126,10 +11619,6 @@
       <c r="K129" s="15"/>
       <c r="L129" s="16"/>
       <c r="M129" s="17"/>
-      <c r="N129" s="18" t="str">
-        <f aca="false">IF(B129="","",IF(J129="Sí","Multa aplicada",IF(J129="No","Sin multa",IF(H129="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="130" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="6" t="str">
@@ -12166,10 +11655,6 @@
       <c r="K130" s="15"/>
       <c r="L130" s="16"/>
       <c r="M130" s="17"/>
-      <c r="N130" s="18" t="str">
-        <f aca="false">IF(B130="","",IF(J130="Sí","Multa aplicada",IF(J130="No","Sin multa",IF(H130="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="131" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="6" t="str">
@@ -12206,10 +11691,6 @@
       <c r="K131" s="15"/>
       <c r="L131" s="16"/>
       <c r="M131" s="17"/>
-      <c r="N131" s="18" t="str">
-        <f aca="false">IF(B131="","",IF(J131="Sí","Multa aplicada",IF(J131="No","Sin multa",IF(H131="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="132" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="6" t="str">
@@ -12246,10 +11727,6 @@
       <c r="K132" s="15"/>
       <c r="L132" s="16"/>
       <c r="M132" s="17"/>
-      <c r="N132" s="18" t="str">
-        <f aca="false">IF(B132="","",IF(J132="Sí","Multa aplicada",IF(J132="No","Sin multa",IF(H132="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="133" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="6" t="str">
@@ -12286,10 +11763,6 @@
       <c r="K133" s="15"/>
       <c r="L133" s="16"/>
       <c r="M133" s="17"/>
-      <c r="N133" s="18" t="str">
-        <f aca="false">IF(B133="","",IF(J133="Sí","Multa aplicada",IF(J133="No","Sin multa",IF(H133="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="134" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="6" t="str">
@@ -12326,10 +11799,6 @@
       <c r="K134" s="15"/>
       <c r="L134" s="16"/>
       <c r="M134" s="17"/>
-      <c r="N134" s="18" t="str">
-        <f aca="false">IF(B134="","",IF(J134="Sí","Multa aplicada",IF(J134="No","Sin multa",IF(H134="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="135" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="6" t="str">
@@ -12366,10 +11835,6 @@
       <c r="K135" s="15"/>
       <c r="L135" s="16"/>
       <c r="M135" s="17"/>
-      <c r="N135" s="18" t="str">
-        <f aca="false">IF(B135="","",IF(J135="Sí","Multa aplicada",IF(J135="No","Sin multa",IF(H135="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="136" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="6" t="str">
@@ -12406,10 +11871,6 @@
       <c r="K136" s="15"/>
       <c r="L136" s="16"/>
       <c r="M136" s="17"/>
-      <c r="N136" s="18" t="str">
-        <f aca="false">IF(B136="","",IF(J136="Sí","Multa aplicada",IF(J136="No","Sin multa",IF(H136="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="137" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="6" t="str">
@@ -12446,10 +11907,6 @@
       <c r="K137" s="15"/>
       <c r="L137" s="16"/>
       <c r="M137" s="17"/>
-      <c r="N137" s="18" t="str">
-        <f aca="false">IF(B137="","",IF(J137="Sí","Multa aplicada",IF(J137="No","Sin multa",IF(H137="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="138" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="6" t="str">
@@ -12486,10 +11943,6 @@
       <c r="K138" s="15"/>
       <c r="L138" s="16"/>
       <c r="M138" s="17"/>
-      <c r="N138" s="18" t="str">
-        <f aca="false">IF(B138="","",IF(J138="Sí","Multa aplicada",IF(J138="No","Sin multa",IF(H138="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="139" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="6" t="str">
@@ -12526,10 +11979,6 @@
       <c r="K139" s="15"/>
       <c r="L139" s="16"/>
       <c r="M139" s="17"/>
-      <c r="N139" s="18" t="str">
-        <f aca="false">IF(B139="","",IF(J139="Sí","Multa aplicada",IF(J139="No","Sin multa",IF(H139="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="140" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="6" t="str">
@@ -12566,10 +12015,6 @@
       <c r="K140" s="15"/>
       <c r="L140" s="16"/>
       <c r="M140" s="17"/>
-      <c r="N140" s="18" t="str">
-        <f aca="false">IF(B140="","",IF(J140="Sí","Multa aplicada",IF(J140="No","Sin multa",IF(H140="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="141" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="6" t="str">
@@ -12606,10 +12051,6 @@
       <c r="K141" s="15"/>
       <c r="L141" s="16"/>
       <c r="M141" s="17"/>
-      <c r="N141" s="18" t="str">
-        <f aca="false">IF(B141="","",IF(J141="Sí","Multa aplicada",IF(J141="No","Sin multa",IF(H141="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="142" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="6" t="str">
@@ -12646,10 +12087,6 @@
       <c r="K142" s="15"/>
       <c r="L142" s="16"/>
       <c r="M142" s="17"/>
-      <c r="N142" s="18" t="str">
-        <f aca="false">IF(B142="","",IF(J142="Sí","Multa aplicada",IF(J142="No","Sin multa",IF(H142="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="143" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="6" t="str">
@@ -12686,10 +12123,6 @@
       <c r="K143" s="15"/>
       <c r="L143" s="16"/>
       <c r="M143" s="17"/>
-      <c r="N143" s="18" t="str">
-        <f aca="false">IF(B143="","",IF(J143="Sí","Multa aplicada",IF(J143="No","Sin multa",IF(H143="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="144" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="6" t="str">
@@ -12726,10 +12159,6 @@
       <c r="K144" s="15"/>
       <c r="L144" s="16"/>
       <c r="M144" s="17"/>
-      <c r="N144" s="18" t="str">
-        <f aca="false">IF(B144="","",IF(J144="Sí","Multa aplicada",IF(J144="No","Sin multa",IF(H144="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="145" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="6" t="str">
@@ -12766,10 +12195,6 @@
       <c r="K145" s="15"/>
       <c r="L145" s="16"/>
       <c r="M145" s="17"/>
-      <c r="N145" s="18" t="str">
-        <f aca="false">IF(B145="","",IF(J145="Sí","Multa aplicada",IF(J145="No","Sin multa",IF(H145="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="146" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="6" t="str">
@@ -12806,10 +12231,6 @@
       <c r="K146" s="15"/>
       <c r="L146" s="16"/>
       <c r="M146" s="17"/>
-      <c r="N146" s="18" t="str">
-        <f aca="false">IF(B146="","",IF(J146="Sí","Multa aplicada",IF(J146="No","Sin multa",IF(H146="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="147" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="6" t="str">
@@ -12846,10 +12267,6 @@
       <c r="K147" s="15"/>
       <c r="L147" s="16"/>
       <c r="M147" s="17"/>
-      <c r="N147" s="18" t="str">
-        <f aca="false">IF(B147="","",IF(J147="Sí","Multa aplicada",IF(J147="No","Sin multa",IF(H147="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="148" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="6" t="str">
@@ -12886,10 +12303,6 @@
       <c r="K148" s="15"/>
       <c r="L148" s="16"/>
       <c r="M148" s="17"/>
-      <c r="N148" s="18" t="str">
-        <f aca="false">IF(B148="","",IF(J148="Sí","Multa aplicada",IF(J148="No","Sin multa",IF(H148="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="149" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="6" t="str">
@@ -12926,10 +12339,6 @@
       <c r="K149" s="15"/>
       <c r="L149" s="16"/>
       <c r="M149" s="17"/>
-      <c r="N149" s="18" t="str">
-        <f aca="false">IF(B149="","",IF(J149="Sí","Multa aplicada",IF(J149="No","Sin multa",IF(H149="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="150" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="6" t="str">
@@ -12966,10 +12375,6 @@
       <c r="K150" s="15"/>
       <c r="L150" s="16"/>
       <c r="M150" s="17"/>
-      <c r="N150" s="18" t="str">
-        <f aca="false">IF(B150="","",IF(J150="Sí","Multa aplicada",IF(J150="No","Sin multa",IF(H150="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="151" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="6" t="str">
@@ -13006,10 +12411,6 @@
       <c r="K151" s="15"/>
       <c r="L151" s="16"/>
       <c r="M151" s="17"/>
-      <c r="N151" s="18" t="str">
-        <f aca="false">IF(B151="","",IF(J151="Sí","Multa aplicada",IF(J151="No","Sin multa",IF(H151="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="152" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="6" t="str">
@@ -13046,10 +12447,6 @@
       <c r="K152" s="15"/>
       <c r="L152" s="16"/>
       <c r="M152" s="17"/>
-      <c r="N152" s="18" t="str">
-        <f aca="false">IF(B152="","",IF(J152="Sí","Multa aplicada",IF(J152="No","Sin multa",IF(H152="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="153" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="6" t="str">
@@ -13086,10 +12483,6 @@
       <c r="K153" s="15"/>
       <c r="L153" s="16"/>
       <c r="M153" s="17"/>
-      <c r="N153" s="18" t="str">
-        <f aca="false">IF(B153="","",IF(J153="Sí","Multa aplicada",IF(J153="No","Sin multa",IF(H153="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="154" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="6" t="str">
@@ -13126,10 +12519,6 @@
       <c r="K154" s="15"/>
       <c r="L154" s="16"/>
       <c r="M154" s="17"/>
-      <c r="N154" s="18" t="str">
-        <f aca="false">IF(B154="","",IF(J154="Sí","Multa aplicada",IF(J154="No","Sin multa",IF(H154="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="155" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="6" t="str">
@@ -13166,10 +12555,6 @@
       <c r="K155" s="15"/>
       <c r="L155" s="16"/>
       <c r="M155" s="17"/>
-      <c r="N155" s="18" t="str">
-        <f aca="false">IF(B155="","",IF(J155="Sí","Multa aplicada",IF(J155="No","Sin multa",IF(H155="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="156" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="6" t="str">
@@ -13206,10 +12591,6 @@
       <c r="K156" s="15"/>
       <c r="L156" s="16"/>
       <c r="M156" s="17"/>
-      <c r="N156" s="18" t="str">
-        <f aca="false">IF(B156="","",IF(J156="Sí","Multa aplicada",IF(J156="No","Sin multa",IF(H156="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="157" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="6" t="str">
@@ -13246,10 +12627,6 @@
       <c r="K157" s="15"/>
       <c r="L157" s="16"/>
       <c r="M157" s="17"/>
-      <c r="N157" s="18" t="str">
-        <f aca="false">IF(B157="","",IF(J157="Sí","Multa aplicada",IF(J157="No","Sin multa",IF(H157="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="158" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="6" t="str">
@@ -13286,10 +12663,6 @@
       <c r="K158" s="15"/>
       <c r="L158" s="16"/>
       <c r="M158" s="17"/>
-      <c r="N158" s="18" t="str">
-        <f aca="false">IF(B158="","",IF(J158="Sí","Multa aplicada",IF(J158="No","Sin multa",IF(H158="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="159" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="6" t="str">
@@ -13326,10 +12699,6 @@
       <c r="K159" s="15"/>
       <c r="L159" s="16"/>
       <c r="M159" s="17"/>
-      <c r="N159" s="18" t="str">
-        <f aca="false">IF(B159="","",IF(J159="Sí","Multa aplicada",IF(J159="No","Sin multa",IF(H159="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="160" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="6" t="str">
@@ -13366,10 +12735,6 @@
       <c r="K160" s="15"/>
       <c r="L160" s="16"/>
       <c r="M160" s="17"/>
-      <c r="N160" s="18" t="str">
-        <f aca="false">IF(B160="","",IF(J160="Sí","Multa aplicada",IF(J160="No","Sin multa",IF(H160="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="161" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="6" t="str">
@@ -13406,10 +12771,6 @@
       <c r="K161" s="15"/>
       <c r="L161" s="16"/>
       <c r="M161" s="17"/>
-      <c r="N161" s="18" t="str">
-        <f aca="false">IF(B161="","",IF(J161="Sí","Multa aplicada",IF(J161="No","Sin multa",IF(H161="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="162" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="6" t="str">
@@ -13446,10 +12807,6 @@
       <c r="K162" s="15"/>
       <c r="L162" s="16"/>
       <c r="M162" s="17"/>
-      <c r="N162" s="18" t="str">
-        <f aca="false">IF(B162="","",IF(J162="Sí","Multa aplicada",IF(J162="No","Sin multa",IF(H162="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="163" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="6" t="str">
@@ -13486,10 +12843,6 @@
       <c r="K163" s="15"/>
       <c r="L163" s="16"/>
       <c r="M163" s="17"/>
-      <c r="N163" s="18" t="str">
-        <f aca="false">IF(B163="","",IF(J163="Sí","Multa aplicada",IF(J163="No","Sin multa",IF(H163="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="164" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="6" t="str">
@@ -13526,10 +12879,6 @@
       <c r="K164" s="15"/>
       <c r="L164" s="16"/>
       <c r="M164" s="17"/>
-      <c r="N164" s="18" t="str">
-        <f aca="false">IF(B164="","",IF(J164="Sí","Multa aplicada",IF(J164="No","Sin multa",IF(H164="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="165" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="6" t="str">
@@ -13566,10 +12915,6 @@
       <c r="K165" s="15"/>
       <c r="L165" s="16"/>
       <c r="M165" s="17"/>
-      <c r="N165" s="18" t="str">
-        <f aca="false">IF(B165="","",IF(J165="Sí","Multa aplicada",IF(J165="No","Sin multa",IF(H165="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="166" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="6" t="str">
@@ -13606,10 +12951,6 @@
       <c r="K166" s="15"/>
       <c r="L166" s="16"/>
       <c r="M166" s="17"/>
-      <c r="N166" s="18" t="str">
-        <f aca="false">IF(B166="","",IF(J166="Sí","Multa aplicada",IF(J166="No","Sin multa",IF(H166="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="167" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="6" t="str">
@@ -13646,10 +12987,6 @@
       <c r="K167" s="15"/>
       <c r="L167" s="16"/>
       <c r="M167" s="17"/>
-      <c r="N167" s="18" t="str">
-        <f aca="false">IF(B167="","",IF(J167="Sí","Multa aplicada",IF(J167="No","Sin multa",IF(H167="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="168" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="6" t="str">
@@ -13686,10 +13023,6 @@
       <c r="K168" s="15"/>
       <c r="L168" s="16"/>
       <c r="M168" s="17"/>
-      <c r="N168" s="18" t="str">
-        <f aca="false">IF(B168="","",IF(J168="Sí","Multa aplicada",IF(J168="No","Sin multa",IF(H168="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="169" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="6" t="str">
@@ -13726,10 +13059,6 @@
       <c r="K169" s="15"/>
       <c r="L169" s="16"/>
       <c r="M169" s="17"/>
-      <c r="N169" s="18" t="str">
-        <f aca="false">IF(B169="","",IF(J169="Sí","Multa aplicada",IF(J169="No","Sin multa",IF(H169="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="170" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="6" t="str">
@@ -13766,10 +13095,6 @@
       <c r="K170" s="15"/>
       <c r="L170" s="16"/>
       <c r="M170" s="17"/>
-      <c r="N170" s="18" t="str">
-        <f aca="false">IF(B170="","",IF(J170="Sí","Multa aplicada",IF(J170="No","Sin multa",IF(H170="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="171" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="6" t="str">
@@ -13806,10 +13131,6 @@
       <c r="K171" s="15"/>
       <c r="L171" s="16"/>
       <c r="M171" s="17"/>
-      <c r="N171" s="18" t="str">
-        <f aca="false">IF(B171="","",IF(J171="Sí","Multa aplicada",IF(J171="No","Sin multa",IF(H171="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="172" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="6" t="str">
@@ -13846,10 +13167,6 @@
       <c r="K172" s="15"/>
       <c r="L172" s="16"/>
       <c r="M172" s="17"/>
-      <c r="N172" s="18" t="str">
-        <f aca="false">IF(B172="","",IF(J172="Sí","Multa aplicada",IF(J172="No","Sin multa",IF(H172="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="173" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="6" t="str">
@@ -13886,10 +13203,6 @@
       <c r="K173" s="15"/>
       <c r="L173" s="16"/>
       <c r="M173" s="17"/>
-      <c r="N173" s="18" t="str">
-        <f aca="false">IF(B173="","",IF(J173="Sí","Multa aplicada",IF(J173="No","Sin multa",IF(H173="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="174" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="6" t="str">
@@ -13926,10 +13239,6 @@
       <c r="K174" s="15"/>
       <c r="L174" s="16"/>
       <c r="M174" s="17"/>
-      <c r="N174" s="18" t="str">
-        <f aca="false">IF(B174="","",IF(J174="Sí","Multa aplicada",IF(J174="No","Sin multa",IF(H174="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="175" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="6" t="str">
@@ -13966,10 +13275,6 @@
       <c r="K175" s="15"/>
       <c r="L175" s="16"/>
       <c r="M175" s="17"/>
-      <c r="N175" s="18" t="str">
-        <f aca="false">IF(B175="","",IF(J175="Sí","Multa aplicada",IF(J175="No","Sin multa",IF(H175="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="176" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="6" t="str">
@@ -14006,10 +13311,6 @@
       <c r="K176" s="15"/>
       <c r="L176" s="16"/>
       <c r="M176" s="17"/>
-      <c r="N176" s="18" t="str">
-        <f aca="false">IF(B176="","",IF(J176="Sí","Multa aplicada",IF(J176="No","Sin multa",IF(H176="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="177" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="6" t="str">
@@ -14046,10 +13347,6 @@
       <c r="K177" s="15"/>
       <c r="L177" s="16"/>
       <c r="M177" s="17"/>
-      <c r="N177" s="18" t="str">
-        <f aca="false">IF(B177="","",IF(J177="Sí","Multa aplicada",IF(J177="No","Sin multa",IF(H177="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="178" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="6" t="str">
@@ -14086,10 +13383,6 @@
       <c r="K178" s="15"/>
       <c r="L178" s="16"/>
       <c r="M178" s="17"/>
-      <c r="N178" s="18" t="str">
-        <f aca="false">IF(B178="","",IF(J178="Sí","Multa aplicada",IF(J178="No","Sin multa",IF(H178="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="179" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="6" t="str">
@@ -14126,10 +13419,6 @@
       <c r="K179" s="15"/>
       <c r="L179" s="16"/>
       <c r="M179" s="17"/>
-      <c r="N179" s="18" t="str">
-        <f aca="false">IF(B179="","",IF(J179="Sí","Multa aplicada",IF(J179="No","Sin multa",IF(H179="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="180" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="6" t="str">
@@ -14166,10 +13455,6 @@
       <c r="K180" s="15"/>
       <c r="L180" s="16"/>
       <c r="M180" s="17"/>
-      <c r="N180" s="18" t="str">
-        <f aca="false">IF(B180="","",IF(J180="Sí","Multa aplicada",IF(J180="No","Sin multa",IF(H180="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="181" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="6" t="str">
@@ -14206,10 +13491,6 @@
       <c r="K181" s="15"/>
       <c r="L181" s="16"/>
       <c r="M181" s="17"/>
-      <c r="N181" s="18" t="str">
-        <f aca="false">IF(B181="","",IF(J181="Sí","Multa aplicada",IF(J181="No","Sin multa",IF(H181="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="182" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="6" t="str">
@@ -14246,10 +13527,6 @@
       <c r="K182" s="15"/>
       <c r="L182" s="16"/>
       <c r="M182" s="17"/>
-      <c r="N182" s="18" t="str">
-        <f aca="false">IF(B182="","",IF(J182="Sí","Multa aplicada",IF(J182="No","Sin multa",IF(H182="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="183" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="6" t="str">
@@ -14286,10 +13563,6 @@
       <c r="K183" s="15"/>
       <c r="L183" s="16"/>
       <c r="M183" s="17"/>
-      <c r="N183" s="18" t="str">
-        <f aca="false">IF(B183="","",IF(J183="Sí","Multa aplicada",IF(J183="No","Sin multa",IF(H183="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="184" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="6" t="str">
@@ -14326,10 +13599,6 @@
       <c r="K184" s="15"/>
       <c r="L184" s="16"/>
       <c r="M184" s="17"/>
-      <c r="N184" s="18" t="str">
-        <f aca="false">IF(B184="","",IF(J184="Sí","Multa aplicada",IF(J184="No","Sin multa",IF(H184="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="185" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="6" t="str">
@@ -14366,10 +13635,6 @@
       <c r="K185" s="15"/>
       <c r="L185" s="16"/>
       <c r="M185" s="17"/>
-      <c r="N185" s="18" t="str">
-        <f aca="false">IF(B185="","",IF(J185="Sí","Multa aplicada",IF(J185="No","Sin multa",IF(H185="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="186" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="6" t="str">
@@ -14406,10 +13671,6 @@
       <c r="K186" s="15"/>
       <c r="L186" s="16"/>
       <c r="M186" s="17"/>
-      <c r="N186" s="18" t="str">
-        <f aca="false">IF(B186="","",IF(J186="Sí","Multa aplicada",IF(J186="No","Sin multa",IF(H186="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="187" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="6" t="str">
@@ -14446,10 +13707,6 @@
       <c r="K187" s="15"/>
       <c r="L187" s="16"/>
       <c r="M187" s="17"/>
-      <c r="N187" s="18" t="str">
-        <f aca="false">IF(B187="","",IF(J187="Sí","Multa aplicada",IF(J187="No","Sin multa",IF(H187="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="188" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="6" t="str">
@@ -14486,10 +13743,6 @@
       <c r="K188" s="15"/>
       <c r="L188" s="16"/>
       <c r="M188" s="17"/>
-      <c r="N188" s="18" t="str">
-        <f aca="false">IF(B188="","",IF(J188="Sí","Multa aplicada",IF(J188="No","Sin multa",IF(H188="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="189" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="6" t="str">
@@ -14526,10 +13779,6 @@
       <c r="K189" s="15"/>
       <c r="L189" s="16"/>
       <c r="M189" s="17"/>
-      <c r="N189" s="18" t="str">
-        <f aca="false">IF(B189="","",IF(J189="Sí","Multa aplicada",IF(J189="No","Sin multa",IF(H189="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="190" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="6" t="str">
@@ -14566,10 +13815,6 @@
       <c r="K190" s="15"/>
       <c r="L190" s="16"/>
       <c r="M190" s="17"/>
-      <c r="N190" s="18" t="str">
-        <f aca="false">IF(B190="","",IF(J190="Sí","Multa aplicada",IF(J190="No","Sin multa",IF(H190="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="191" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="6" t="str">
@@ -14606,10 +13851,6 @@
       <c r="K191" s="15"/>
       <c r="L191" s="16"/>
       <c r="M191" s="17"/>
-      <c r="N191" s="18" t="str">
-        <f aca="false">IF(B191="","",IF(J191="Sí","Multa aplicada",IF(J191="No","Sin multa",IF(H191="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="192" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="6" t="str">
@@ -14646,10 +13887,6 @@
       <c r="K192" s="15"/>
       <c r="L192" s="16"/>
       <c r="M192" s="17"/>
-      <c r="N192" s="18" t="str">
-        <f aca="false">IF(B192="","",IF(J192="Sí","Multa aplicada",IF(J192="No","Sin multa",IF(H192="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="193" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="6" t="str">
@@ -14686,10 +13923,6 @@
       <c r="K193" s="15"/>
       <c r="L193" s="16"/>
       <c r="M193" s="17"/>
-      <c r="N193" s="18" t="str">
-        <f aca="false">IF(B193="","",IF(J193="Sí","Multa aplicada",IF(J193="No","Sin multa",IF(H193="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="194" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="6" t="str">
@@ -14726,10 +13959,6 @@
       <c r="K194" s="15"/>
       <c r="L194" s="16"/>
       <c r="M194" s="17"/>
-      <c r="N194" s="18" t="str">
-        <f aca="false">IF(B194="","",IF(J194="Sí","Multa aplicada",IF(J194="No","Sin multa",IF(H194="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="195" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="6" t="str">
@@ -14766,10 +13995,6 @@
       <c r="K195" s="15"/>
       <c r="L195" s="16"/>
       <c r="M195" s="17"/>
-      <c r="N195" s="18" t="str">
-        <f aca="false">IF(B195="","",IF(J195="Sí","Multa aplicada",IF(J195="No","Sin multa",IF(H195="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="196" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="6" t="str">
@@ -14806,10 +14031,6 @@
       <c r="K196" s="15"/>
       <c r="L196" s="16"/>
       <c r="M196" s="17"/>
-      <c r="N196" s="18" t="str">
-        <f aca="false">IF(B196="","",IF(J196="Sí","Multa aplicada",IF(J196="No","Sin multa",IF(H196="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="197" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="6" t="str">
@@ -14846,10 +14067,6 @@
       <c r="K197" s="15"/>
       <c r="L197" s="16"/>
       <c r="M197" s="17"/>
-      <c r="N197" s="18" t="str">
-        <f aca="false">IF(B197="","",IF(J197="Sí","Multa aplicada",IF(J197="No","Sin multa",IF(H197="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="198" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="6" t="str">
@@ -14886,10 +14103,6 @@
       <c r="K198" s="15"/>
       <c r="L198" s="16"/>
       <c r="M198" s="17"/>
-      <c r="N198" s="18" t="str">
-        <f aca="false">IF(B198="","",IF(J198="Sí","Multa aplicada",IF(J198="No","Sin multa",IF(H198="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="199" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="6" t="str">
@@ -14926,10 +14139,6 @@
       <c r="K199" s="15"/>
       <c r="L199" s="16"/>
       <c r="M199" s="17"/>
-      <c r="N199" s="18" t="str">
-        <f aca="false">IF(B199="","",IF(J199="Sí","Multa aplicada",IF(J199="No","Sin multa",IF(H199="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="200" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="6" t="str">
@@ -14966,10 +14175,6 @@
       <c r="K200" s="15"/>
       <c r="L200" s="16"/>
       <c r="M200" s="17"/>
-      <c r="N200" s="18" t="str">
-        <f aca="false">IF(B200="","",IF(J200="Sí","Multa aplicada",IF(J200="No","Sin multa",IF(H200="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="201" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="6" t="str">
@@ -15006,10 +14211,6 @@
       <c r="K201" s="15"/>
       <c r="L201" s="16"/>
       <c r="M201" s="17"/>
-      <c r="N201" s="18" t="str">
-        <f aca="false">IF(B201="","",IF(J201="Sí","Multa aplicada",IF(J201="No","Sin multa",IF(H201="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="202" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="6" t="str">
@@ -15046,10 +14247,6 @@
       <c r="K202" s="15"/>
       <c r="L202" s="16"/>
       <c r="M202" s="17"/>
-      <c r="N202" s="18" t="str">
-        <f aca="false">IF(B202="","",IF(J202="Sí","Multa aplicada",IF(J202="No","Sin multa",IF(H202="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="203" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="6" t="str">
@@ -15086,10 +14283,6 @@
       <c r="K203" s="15"/>
       <c r="L203" s="16"/>
       <c r="M203" s="17"/>
-      <c r="N203" s="18" t="str">
-        <f aca="false">IF(B203="","",IF(J203="Sí","Multa aplicada",IF(J203="No","Sin multa",IF(H203="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="204" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="6" t="str">
@@ -15126,10 +14319,6 @@
       <c r="K204" s="15"/>
       <c r="L204" s="16"/>
       <c r="M204" s="17"/>
-      <c r="N204" s="18" t="str">
-        <f aca="false">IF(B204="","",IF(J204="Sí","Multa aplicada",IF(J204="No","Sin multa",IF(H204="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="205" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="6" t="str">
@@ -15166,10 +14355,6 @@
       <c r="K205" s="15"/>
       <c r="L205" s="16"/>
       <c r="M205" s="17"/>
-      <c r="N205" s="18" t="str">
-        <f aca="false">IF(B205="","",IF(J205="Sí","Multa aplicada",IF(J205="No","Sin multa",IF(H205="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="206" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="6" t="str">
@@ -15206,10 +14391,6 @@
       <c r="K206" s="15"/>
       <c r="L206" s="16"/>
       <c r="M206" s="17"/>
-      <c r="N206" s="18" t="str">
-        <f aca="false">IF(B206="","",IF(J206="Sí","Multa aplicada",IF(J206="No","Sin multa",IF(H206="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="207" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="6" t="str">
@@ -15246,10 +14427,6 @@
       <c r="K207" s="15"/>
       <c r="L207" s="16"/>
       <c r="M207" s="17"/>
-      <c r="N207" s="18" t="str">
-        <f aca="false">IF(B207="","",IF(J207="Sí","Multa aplicada",IF(J207="No","Sin multa",IF(H207="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="208" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="6" t="str">
@@ -15286,10 +14463,6 @@
       <c r="K208" s="15"/>
       <c r="L208" s="16"/>
       <c r="M208" s="17"/>
-      <c r="N208" s="18" t="str">
-        <f aca="false">IF(B208="","",IF(J208="Sí","Multa aplicada",IF(J208="No","Sin multa",IF(H208="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="209" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="6" t="str">
@@ -15326,10 +14499,6 @@
       <c r="K209" s="15"/>
       <c r="L209" s="16"/>
       <c r="M209" s="17"/>
-      <c r="N209" s="18" t="str">
-        <f aca="false">IF(B209="","",IF(J209="Sí","Multa aplicada",IF(J209="No","Sin multa",IF(H209="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="210" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="6" t="str">
@@ -15366,10 +14535,6 @@
       <c r="K210" s="15"/>
       <c r="L210" s="16"/>
       <c r="M210" s="17"/>
-      <c r="N210" s="18" t="str">
-        <f aca="false">IF(B210="","",IF(J210="Sí","Multa aplicada",IF(J210="No","Sin multa",IF(H210="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="211" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="6" t="str">
@@ -15406,10 +14571,6 @@
       <c r="K211" s="15"/>
       <c r="L211" s="16"/>
       <c r="M211" s="17"/>
-      <c r="N211" s="18" t="str">
-        <f aca="false">IF(B211="","",IF(J211="Sí","Multa aplicada",IF(J211="No","Sin multa",IF(H211="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="212" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="6" t="str">
@@ -15446,10 +14607,6 @@
       <c r="K212" s="15"/>
       <c r="L212" s="16"/>
       <c r="M212" s="17"/>
-      <c r="N212" s="18" t="str">
-        <f aca="false">IF(B212="","",IF(J212="Sí","Multa aplicada",IF(J212="No","Sin multa",IF(H212="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="213" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="6" t="str">
@@ -15486,10 +14643,6 @@
       <c r="K213" s="15"/>
       <c r="L213" s="16"/>
       <c r="M213" s="17"/>
-      <c r="N213" s="18" t="str">
-        <f aca="false">IF(B213="","",IF(J213="Sí","Multa aplicada",IF(J213="No","Sin multa",IF(H213="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="214" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="6" t="str">
@@ -15526,10 +14679,6 @@
       <c r="K214" s="15"/>
       <c r="L214" s="16"/>
       <c r="M214" s="17"/>
-      <c r="N214" s="18" t="str">
-        <f aca="false">IF(B214="","",IF(J214="Sí","Multa aplicada",IF(J214="No","Sin multa",IF(H214="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="215" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="6" t="str">
@@ -15566,10 +14715,6 @@
       <c r="K215" s="15"/>
       <c r="L215" s="16"/>
       <c r="M215" s="17"/>
-      <c r="N215" s="18" t="str">
-        <f aca="false">IF(B215="","",IF(J215="Sí","Multa aplicada",IF(J215="No","Sin multa",IF(H215="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="216" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="6" t="str">
@@ -15606,10 +14751,6 @@
       <c r="K216" s="15"/>
       <c r="L216" s="16"/>
       <c r="M216" s="17"/>
-      <c r="N216" s="18" t="str">
-        <f aca="false">IF(B216="","",IF(J216="Sí","Multa aplicada",IF(J216="No","Sin multa",IF(H216="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="217" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="6" t="str">
@@ -15646,10 +14787,6 @@
       <c r="K217" s="15"/>
       <c r="L217" s="16"/>
       <c r="M217" s="17"/>
-      <c r="N217" s="18" t="str">
-        <f aca="false">IF(B217="","",IF(J217="Sí","Multa aplicada",IF(J217="No","Sin multa",IF(H217="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="218" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="6" t="str">
@@ -15686,10 +14823,6 @@
       <c r="K218" s="15"/>
       <c r="L218" s="16"/>
       <c r="M218" s="17"/>
-      <c r="N218" s="18" t="str">
-        <f aca="false">IF(B218="","",IF(J218="Sí","Multa aplicada",IF(J218="No","Sin multa",IF(H218="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="219" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="6" t="str">
@@ -15726,10 +14859,6 @@
       <c r="K219" s="15"/>
       <c r="L219" s="16"/>
       <c r="M219" s="17"/>
-      <c r="N219" s="18" t="str">
-        <f aca="false">IF(B219="","",IF(J219="Sí","Multa aplicada",IF(J219="No","Sin multa",IF(H219="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="220" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="6" t="str">
@@ -15766,10 +14895,6 @@
       <c r="K220" s="15"/>
       <c r="L220" s="16"/>
       <c r="M220" s="17"/>
-      <c r="N220" s="18" t="str">
-        <f aca="false">IF(B220="","",IF(J220="Sí","Multa aplicada",IF(J220="No","Sin multa",IF(H220="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="221" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="6" t="str">
@@ -15806,10 +14931,6 @@
       <c r="K221" s="15"/>
       <c r="L221" s="16"/>
       <c r="M221" s="17"/>
-      <c r="N221" s="18" t="str">
-        <f aca="false">IF(B221="","",IF(J221="Sí","Multa aplicada",IF(J221="No","Sin multa",IF(H221="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="222" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="6" t="str">
@@ -15846,10 +14967,6 @@
       <c r="K222" s="15"/>
       <c r="L222" s="16"/>
       <c r="M222" s="17"/>
-      <c r="N222" s="18" t="str">
-        <f aca="false">IF(B222="","",IF(J222="Sí","Multa aplicada",IF(J222="No","Sin multa",IF(H222="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="223" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="6" t="str">
@@ -15886,10 +15003,6 @@
       <c r="K223" s="15"/>
       <c r="L223" s="16"/>
       <c r="M223" s="17"/>
-      <c r="N223" s="18" t="str">
-        <f aca="false">IF(B223="","",IF(J223="Sí","Multa aplicada",IF(J223="No","Sin multa",IF(H223="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="224" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="6" t="str">
@@ -15926,10 +15039,6 @@
       <c r="K224" s="15"/>
       <c r="L224" s="16"/>
       <c r="M224" s="17"/>
-      <c r="N224" s="18" t="str">
-        <f aca="false">IF(B224="","",IF(J224="Sí","Multa aplicada",IF(J224="No","Sin multa",IF(H224="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="225" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="6" t="str">
@@ -15966,10 +15075,6 @@
       <c r="K225" s="15"/>
       <c r="L225" s="16"/>
       <c r="M225" s="17"/>
-      <c r="N225" s="18" t="str">
-        <f aca="false">IF(B225="","",IF(J225="Sí","Multa aplicada",IF(J225="No","Sin multa",IF(H225="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="226" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="6" t="str">
@@ -16006,10 +15111,6 @@
       <c r="K226" s="15"/>
       <c r="L226" s="16"/>
       <c r="M226" s="17"/>
-      <c r="N226" s="18" t="str">
-        <f aca="false">IF(B226="","",IF(J226="Sí","Multa aplicada",IF(J226="No","Sin multa",IF(H226="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="227" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="6" t="str">
@@ -16046,10 +15147,6 @@
       <c r="K227" s="15"/>
       <c r="L227" s="16"/>
       <c r="M227" s="17"/>
-      <c r="N227" s="18" t="str">
-        <f aca="false">IF(B227="","",IF(J227="Sí","Multa aplicada",IF(J227="No","Sin multa",IF(H227="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="228" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="6" t="str">
@@ -16086,10 +15183,6 @@
       <c r="K228" s="15"/>
       <c r="L228" s="16"/>
       <c r="M228" s="17"/>
-      <c r="N228" s="18" t="str">
-        <f aca="false">IF(B228="","",IF(J228="Sí","Multa aplicada",IF(J228="No","Sin multa",IF(H228="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="229" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="6" t="str">
@@ -16126,10 +15219,6 @@
       <c r="K229" s="15"/>
       <c r="L229" s="16"/>
       <c r="M229" s="17"/>
-      <c r="N229" s="18" t="str">
-        <f aca="false">IF(B229="","",IF(J229="Sí","Multa aplicada",IF(J229="No","Sin multa",IF(H229="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="230" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="6" t="str">
@@ -16166,10 +15255,6 @@
       <c r="K230" s="15"/>
       <c r="L230" s="16"/>
       <c r="M230" s="17"/>
-      <c r="N230" s="18" t="str">
-        <f aca="false">IF(B230="","",IF(J230="Sí","Multa aplicada",IF(J230="No","Sin multa",IF(H230="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="231" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="6" t="str">
@@ -16206,10 +15291,6 @@
       <c r="K231" s="15"/>
       <c r="L231" s="16"/>
       <c r="M231" s="17"/>
-      <c r="N231" s="18" t="str">
-        <f aca="false">IF(B231="","",IF(J231="Sí","Multa aplicada",IF(J231="No","Sin multa",IF(H231="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="232" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="6" t="str">
@@ -16246,10 +15327,6 @@
       <c r="K232" s="15"/>
       <c r="L232" s="16"/>
       <c r="M232" s="17"/>
-      <c r="N232" s="18" t="str">
-        <f aca="false">IF(B232="","",IF(J232="Sí","Multa aplicada",IF(J232="No","Sin multa",IF(H232="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="233" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="6" t="str">
@@ -16286,10 +15363,6 @@
       <c r="K233" s="15"/>
       <c r="L233" s="16"/>
       <c r="M233" s="17"/>
-      <c r="N233" s="18" t="str">
-        <f aca="false">IF(B233="","",IF(J233="Sí","Multa aplicada",IF(J233="No","Sin multa",IF(H233="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="234" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="6" t="str">
@@ -16326,10 +15399,6 @@
       <c r="K234" s="15"/>
       <c r="L234" s="16"/>
       <c r="M234" s="17"/>
-      <c r="N234" s="18" t="str">
-        <f aca="false">IF(B234="","",IF(J234="Sí","Multa aplicada",IF(J234="No","Sin multa",IF(H234="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="235" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="6" t="str">
@@ -16366,10 +15435,6 @@
       <c r="K235" s="15"/>
       <c r="L235" s="16"/>
       <c r="M235" s="17"/>
-      <c r="N235" s="18" t="str">
-        <f aca="false">IF(B235="","",IF(J235="Sí","Multa aplicada",IF(J235="No","Sin multa",IF(H235="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="236" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="6" t="str">
@@ -16406,10 +15471,6 @@
       <c r="K236" s="15"/>
       <c r="L236" s="16"/>
       <c r="M236" s="17"/>
-      <c r="N236" s="18" t="str">
-        <f aca="false">IF(B236="","",IF(J236="Sí","Multa aplicada",IF(J236="No","Sin multa",IF(H236="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="237" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="6" t="str">
@@ -16446,10 +15507,6 @@
       <c r="K237" s="15"/>
       <c r="L237" s="16"/>
       <c r="M237" s="17"/>
-      <c r="N237" s="18" t="str">
-        <f aca="false">IF(B237="","",IF(J237="Sí","Multa aplicada",IF(J237="No","Sin multa",IF(H237="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="238" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="6" t="str">
@@ -16486,10 +15543,6 @@
       <c r="K238" s="15"/>
       <c r="L238" s="16"/>
       <c r="M238" s="17"/>
-      <c r="N238" s="18" t="str">
-        <f aca="false">IF(B238="","",IF(J238="Sí","Multa aplicada",IF(J238="No","Sin multa",IF(H238="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="239" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="6" t="str">
@@ -16526,10 +15579,6 @@
       <c r="K239" s="15"/>
       <c r="L239" s="16"/>
       <c r="M239" s="17"/>
-      <c r="N239" s="18" t="str">
-        <f aca="false">IF(B239="","",IF(J239="Sí","Multa aplicada",IF(J239="No","Sin multa",IF(H239="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="240" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="6" t="str">
@@ -16566,10 +15615,6 @@
       <c r="K240" s="15"/>
       <c r="L240" s="16"/>
       <c r="M240" s="17"/>
-      <c r="N240" s="18" t="str">
-        <f aca="false">IF(B240="","",IF(J240="Sí","Multa aplicada",IF(J240="No","Sin multa",IF(H240="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="241" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="6" t="str">
@@ -16606,10 +15651,6 @@
       <c r="K241" s="15"/>
       <c r="L241" s="16"/>
       <c r="M241" s="17"/>
-      <c r="N241" s="18" t="str">
-        <f aca="false">IF(B241="","",IF(J241="Sí","Multa aplicada",IF(J241="No","Sin multa",IF(H241="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="242" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="6" t="str">
@@ -16646,10 +15687,6 @@
       <c r="K242" s="15"/>
       <c r="L242" s="16"/>
       <c r="M242" s="17"/>
-      <c r="N242" s="18" t="str">
-        <f aca="false">IF(B242="","",IF(J242="Sí","Multa aplicada",IF(J242="No","Sin multa",IF(H242="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="243" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="6" t="str">
@@ -16686,10 +15723,6 @@
       <c r="K243" s="15"/>
       <c r="L243" s="16"/>
       <c r="M243" s="17"/>
-      <c r="N243" s="18" t="str">
-        <f aca="false">IF(B243="","",IF(J243="Sí","Multa aplicada",IF(J243="No","Sin multa",IF(H243="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="244" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="6" t="str">
@@ -16726,10 +15759,6 @@
       <c r="K244" s="15"/>
       <c r="L244" s="16"/>
       <c r="M244" s="17"/>
-      <c r="N244" s="18" t="str">
-        <f aca="false">IF(B244="","",IF(J244="Sí","Multa aplicada",IF(J244="No","Sin multa",IF(H244="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="245" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="6" t="str">
@@ -16766,10 +15795,6 @@
       <c r="K245" s="15"/>
       <c r="L245" s="16"/>
       <c r="M245" s="17"/>
-      <c r="N245" s="18" t="str">
-        <f aca="false">IF(B245="","",IF(J245="Sí","Multa aplicada",IF(J245="No","Sin multa",IF(H245="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="246" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="6" t="str">
@@ -16806,10 +15831,6 @@
       <c r="K246" s="15"/>
       <c r="L246" s="16"/>
       <c r="M246" s="17"/>
-      <c r="N246" s="18" t="str">
-        <f aca="false">IF(B246="","",IF(J246="Sí","Multa aplicada",IF(J246="No","Sin multa",IF(H246="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="247" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="6" t="str">
@@ -16846,10 +15867,6 @@
       <c r="K247" s="15"/>
       <c r="L247" s="16"/>
       <c r="M247" s="17"/>
-      <c r="N247" s="18" t="str">
-        <f aca="false">IF(B247="","",IF(J247="Sí","Multa aplicada",IF(J247="No","Sin multa",IF(H247="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="248" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="6" t="str">
@@ -16886,10 +15903,6 @@
       <c r="K248" s="15"/>
       <c r="L248" s="16"/>
       <c r="M248" s="17"/>
-      <c r="N248" s="18" t="str">
-        <f aca="false">IF(B248="","",IF(J248="Sí","Multa aplicada",IF(J248="No","Sin multa",IF(H248="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="249" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="6" t="str">
@@ -16926,10 +15939,6 @@
       <c r="K249" s="15"/>
       <c r="L249" s="16"/>
       <c r="M249" s="17"/>
-      <c r="N249" s="18" t="str">
-        <f aca="false">IF(B249="","",IF(J249="Sí","Multa aplicada",IF(J249="No","Sin multa",IF(H249="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="250" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="6" t="str">
@@ -16966,10 +15975,6 @@
       <c r="K250" s="15"/>
       <c r="L250" s="16"/>
       <c r="M250" s="17"/>
-      <c r="N250" s="18" t="str">
-        <f aca="false">IF(B250="","",IF(J250="Sí","Multa aplicada",IF(J250="No","Sin multa",IF(H250="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="251" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="6" t="str">
@@ -17006,10 +16011,6 @@
       <c r="K251" s="15"/>
       <c r="L251" s="16"/>
       <c r="M251" s="17"/>
-      <c r="N251" s="18" t="str">
-        <f aca="false">IF(B251="","",IF(J251="Sí","Multa aplicada",IF(J251="No","Sin multa",IF(H251="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="252" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="6" t="str">
@@ -17046,10 +16047,6 @@
       <c r="K252" s="15"/>
       <c r="L252" s="16"/>
       <c r="M252" s="17"/>
-      <c r="N252" s="18" t="str">
-        <f aca="false">IF(B252="","",IF(J252="Sí","Multa aplicada",IF(J252="No","Sin multa",IF(H252="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="253" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="6" t="str">
@@ -17086,10 +16083,6 @@
       <c r="K253" s="15"/>
       <c r="L253" s="16"/>
       <c r="M253" s="17"/>
-      <c r="N253" s="18" t="str">
-        <f aca="false">IF(B253="","",IF(J253="Sí","Multa aplicada",IF(J253="No","Sin multa",IF(H253="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="254" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="6" t="str">
@@ -17126,10 +16119,6 @@
       <c r="K254" s="15"/>
       <c r="L254" s="16"/>
       <c r="M254" s="17"/>
-      <c r="N254" s="18" t="str">
-        <f aca="false">IF(B254="","",IF(J254="Sí","Multa aplicada",IF(J254="No","Sin multa",IF(H254="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="255" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="6" t="str">
@@ -17166,10 +16155,6 @@
       <c r="K255" s="15"/>
       <c r="L255" s="16"/>
       <c r="M255" s="17"/>
-      <c r="N255" s="18" t="str">
-        <f aca="false">IF(B255="","",IF(J255="Sí","Multa aplicada",IF(J255="No","Sin multa",IF(H255="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="256" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="6" t="str">
@@ -17206,10 +16191,6 @@
       <c r="K256" s="15"/>
       <c r="L256" s="16"/>
       <c r="M256" s="17"/>
-      <c r="N256" s="18" t="str">
-        <f aca="false">IF(B256="","",IF(J256="Sí","Multa aplicada",IF(J256="No","Sin multa",IF(H256="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="257" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="6" t="str">
@@ -17246,10 +16227,6 @@
       <c r="K257" s="15"/>
       <c r="L257" s="16"/>
       <c r="M257" s="17"/>
-      <c r="N257" s="18" t="str">
-        <f aca="false">IF(B257="","",IF(J257="Sí","Multa aplicada",IF(J257="No","Sin multa",IF(H257="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="258" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="6" t="str">
@@ -17286,10 +16263,6 @@
       <c r="K258" s="15"/>
       <c r="L258" s="16"/>
       <c r="M258" s="17"/>
-      <c r="N258" s="18" t="str">
-        <f aca="false">IF(B258="","",IF(J258="Sí","Multa aplicada",IF(J258="No","Sin multa",IF(H258="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="259" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="6" t="str">
@@ -17326,10 +16299,6 @@
       <c r="K259" s="15"/>
       <c r="L259" s="16"/>
       <c r="M259" s="17"/>
-      <c r="N259" s="18" t="str">
-        <f aca="false">IF(B259="","",IF(J259="Sí","Multa aplicada",IF(J259="No","Sin multa",IF(H259="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="260" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="6" t="str">
@@ -17366,10 +16335,6 @@
       <c r="K260" s="15"/>
       <c r="L260" s="16"/>
       <c r="M260" s="17"/>
-      <c r="N260" s="18" t="str">
-        <f aca="false">IF(B260="","",IF(J260="Sí","Multa aplicada",IF(J260="No","Sin multa",IF(H260="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="261" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="6" t="str">
@@ -17406,10 +16371,6 @@
       <c r="K261" s="15"/>
       <c r="L261" s="16"/>
       <c r="M261" s="17"/>
-      <c r="N261" s="18" t="str">
-        <f aca="false">IF(B261="","",IF(J261="Sí","Multa aplicada",IF(J261="No","Sin multa",IF(H261="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="262" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="6" t="str">
@@ -17446,10 +16407,6 @@
       <c r="K262" s="15"/>
       <c r="L262" s="16"/>
       <c r="M262" s="17"/>
-      <c r="N262" s="18" t="str">
-        <f aca="false">IF(B262="","",IF(J262="Sí","Multa aplicada",IF(J262="No","Sin multa",IF(H262="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="263" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="6" t="str">
@@ -17486,10 +16443,6 @@
       <c r="K263" s="15"/>
       <c r="L263" s="16"/>
       <c r="M263" s="17"/>
-      <c r="N263" s="18" t="str">
-        <f aca="false">IF(B263="","",IF(J263="Sí","Multa aplicada",IF(J263="No","Sin multa",IF(H263="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="264" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="6" t="str">
@@ -17526,10 +16479,6 @@
       <c r="K264" s="15"/>
       <c r="L264" s="16"/>
       <c r="M264" s="17"/>
-      <c r="N264" s="18" t="str">
-        <f aca="false">IF(B264="","",IF(J264="Sí","Multa aplicada",IF(J264="No","Sin multa",IF(H264="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="265" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="6" t="str">
@@ -17566,10 +16515,6 @@
       <c r="K265" s="15"/>
       <c r="L265" s="16"/>
       <c r="M265" s="17"/>
-      <c r="N265" s="18" t="str">
-        <f aca="false">IF(B265="","",IF(J265="Sí","Multa aplicada",IF(J265="No","Sin multa",IF(H265="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="266" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="6" t="str">
@@ -17606,10 +16551,6 @@
       <c r="K266" s="15"/>
       <c r="L266" s="16"/>
       <c r="M266" s="17"/>
-      <c r="N266" s="18" t="str">
-        <f aca="false">IF(B266="","",IF(J266="Sí","Multa aplicada",IF(J266="No","Sin multa",IF(H266="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="267" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="6" t="str">
@@ -17646,10 +16587,6 @@
       <c r="K267" s="15"/>
       <c r="L267" s="16"/>
       <c r="M267" s="17"/>
-      <c r="N267" s="18" t="str">
-        <f aca="false">IF(B267="","",IF(J267="Sí","Multa aplicada",IF(J267="No","Sin multa",IF(H267="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="268" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="6" t="str">
@@ -17686,10 +16623,6 @@
       <c r="K268" s="15"/>
       <c r="L268" s="16"/>
       <c r="M268" s="17"/>
-      <c r="N268" s="18" t="str">
-        <f aca="false">IF(B268="","",IF(J268="Sí","Multa aplicada",IF(J268="No","Sin multa",IF(H268="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="269" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="6" t="str">
@@ -17726,10 +16659,6 @@
       <c r="K269" s="15"/>
       <c r="L269" s="16"/>
       <c r="M269" s="17"/>
-      <c r="N269" s="18" t="str">
-        <f aca="false">IF(B269="","",IF(J269="Sí","Multa aplicada",IF(J269="No","Sin multa",IF(H269="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="270" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="6" t="str">
@@ -17766,10 +16695,6 @@
       <c r="K270" s="15"/>
       <c r="L270" s="16"/>
       <c r="M270" s="17"/>
-      <c r="N270" s="18" t="str">
-        <f aca="false">IF(B270="","",IF(J270="Sí","Multa aplicada",IF(J270="No","Sin multa",IF(H270="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="271" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="6" t="str">
@@ -17806,10 +16731,6 @@
       <c r="K271" s="15"/>
       <c r="L271" s="16"/>
       <c r="M271" s="17"/>
-      <c r="N271" s="18" t="str">
-        <f aca="false">IF(B271="","",IF(J271="Sí","Multa aplicada",IF(J271="No","Sin multa",IF(H271="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="272" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="6" t="str">
@@ -17846,10 +16767,6 @@
       <c r="K272" s="15"/>
       <c r="L272" s="16"/>
       <c r="M272" s="17"/>
-      <c r="N272" s="18" t="str">
-        <f aca="false">IF(B272="","",IF(J272="Sí","Multa aplicada",IF(J272="No","Sin multa",IF(H272="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="273" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="6" t="str">
@@ -17886,10 +16803,6 @@
       <c r="K273" s="15"/>
       <c r="L273" s="16"/>
       <c r="M273" s="17"/>
-      <c r="N273" s="18" t="str">
-        <f aca="false">IF(B273="","",IF(J273="Sí","Multa aplicada",IF(J273="No","Sin multa",IF(H273="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="274" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="6" t="str">
@@ -17926,10 +16839,6 @@
       <c r="K274" s="15"/>
       <c r="L274" s="16"/>
       <c r="M274" s="17"/>
-      <c r="N274" s="18" t="str">
-        <f aca="false">IF(B274="","",IF(J274="Sí","Multa aplicada",IF(J274="No","Sin multa",IF(H274="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="275" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="6" t="str">
@@ -17966,10 +16875,6 @@
       <c r="K275" s="15"/>
       <c r="L275" s="16"/>
       <c r="M275" s="17"/>
-      <c r="N275" s="18" t="str">
-        <f aca="false">IF(B275="","",IF(J275="Sí","Multa aplicada",IF(J275="No","Sin multa",IF(H275="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="276" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="6" t="str">
@@ -18006,10 +16911,6 @@
       <c r="K276" s="15"/>
       <c r="L276" s="16"/>
       <c r="M276" s="17"/>
-      <c r="N276" s="18" t="str">
-        <f aca="false">IF(B276="","",IF(J276="Sí","Multa aplicada",IF(J276="No","Sin multa",IF(H276="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="277" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="6" t="str">
@@ -18046,10 +16947,6 @@
       <c r="K277" s="15"/>
       <c r="L277" s="16"/>
       <c r="M277" s="17"/>
-      <c r="N277" s="18" t="str">
-        <f aca="false">IF(B277="","",IF(J277="Sí","Multa aplicada",IF(J277="No","Sin multa",IF(H277="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="278" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="6" t="str">
@@ -18086,10 +16983,6 @@
       <c r="K278" s="15"/>
       <c r="L278" s="16"/>
       <c r="M278" s="17"/>
-      <c r="N278" s="18" t="str">
-        <f aca="false">IF(B278="","",IF(J278="Sí","Multa aplicada",IF(J278="No","Sin multa",IF(H278="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="279" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="6" t="str">
@@ -18126,10 +17019,6 @@
       <c r="K279" s="15"/>
       <c r="L279" s="16"/>
       <c r="M279" s="17"/>
-      <c r="N279" s="18" t="str">
-        <f aca="false">IF(B279="","",IF(J279="Sí","Multa aplicada",IF(J279="No","Sin multa",IF(H279="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="280" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="6" t="str">
@@ -18166,10 +17055,6 @@
       <c r="K280" s="15"/>
       <c r="L280" s="16"/>
       <c r="M280" s="17"/>
-      <c r="N280" s="18" t="str">
-        <f aca="false">IF(B280="","",IF(J280="Sí","Multa aplicada",IF(J280="No","Sin multa",IF(H280="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="281" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="6" t="str">
@@ -18206,10 +17091,6 @@
       <c r="K281" s="15"/>
       <c r="L281" s="16"/>
       <c r="M281" s="17"/>
-      <c r="N281" s="18" t="str">
-        <f aca="false">IF(B281="","",IF(J281="Sí","Multa aplicada",IF(J281="No","Sin multa",IF(H281="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="282" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="6" t="str">
@@ -18246,10 +17127,6 @@
       <c r="K282" s="15"/>
       <c r="L282" s="16"/>
       <c r="M282" s="17"/>
-      <c r="N282" s="18" t="str">
-        <f aca="false">IF(B282="","",IF(J282="Sí","Multa aplicada",IF(J282="No","Sin multa",IF(H282="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="283" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="6" t="str">
@@ -18286,10 +17163,6 @@
       <c r="K283" s="15"/>
       <c r="L283" s="16"/>
       <c r="M283" s="17"/>
-      <c r="N283" s="18" t="str">
-        <f aca="false">IF(B283="","",IF(J283="Sí","Multa aplicada",IF(J283="No","Sin multa",IF(H283="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="284" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="6" t="str">
@@ -18326,10 +17199,6 @@
       <c r="K284" s="15"/>
       <c r="L284" s="16"/>
       <c r="M284" s="17"/>
-      <c r="N284" s="18" t="str">
-        <f aca="false">IF(B284="","",IF(J284="Sí","Multa aplicada",IF(J284="No","Sin multa",IF(H284="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="285" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="6" t="str">
@@ -18366,10 +17235,6 @@
       <c r="K285" s="15"/>
       <c r="L285" s="16"/>
       <c r="M285" s="17"/>
-      <c r="N285" s="18" t="str">
-        <f aca="false">IF(B285="","",IF(J285="Sí","Multa aplicada",IF(J285="No","Sin multa",IF(H285="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="286" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="6" t="str">
@@ -18406,10 +17271,6 @@
       <c r="K286" s="15"/>
       <c r="L286" s="16"/>
       <c r="M286" s="17"/>
-      <c r="N286" s="18" t="str">
-        <f aca="false">IF(B286="","",IF(J286="Sí","Multa aplicada",IF(J286="No","Sin multa",IF(H286="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="287" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="6" t="str">
@@ -18446,10 +17307,6 @@
       <c r="K287" s="15"/>
       <c r="L287" s="16"/>
       <c r="M287" s="17"/>
-      <c r="N287" s="18" t="str">
-        <f aca="false">IF(B287="","",IF(J287="Sí","Multa aplicada",IF(J287="No","Sin multa",IF(H287="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="288" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="6" t="str">
@@ -18486,10 +17343,6 @@
       <c r="K288" s="15"/>
       <c r="L288" s="16"/>
       <c r="M288" s="17"/>
-      <c r="N288" s="18" t="str">
-        <f aca="false">IF(B288="","",IF(J288="Sí","Multa aplicada",IF(J288="No","Sin multa",IF(H288="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="289" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="6" t="str">
@@ -18526,10 +17379,6 @@
       <c r="K289" s="15"/>
       <c r="L289" s="16"/>
       <c r="M289" s="17"/>
-      <c r="N289" s="18" t="str">
-        <f aca="false">IF(B289="","",IF(J289="Sí","Multa aplicada",IF(J289="No","Sin multa",IF(H289="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="290" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="6" t="str">
@@ -18566,10 +17415,6 @@
       <c r="K290" s="15"/>
       <c r="L290" s="16"/>
       <c r="M290" s="17"/>
-      <c r="N290" s="18" t="str">
-        <f aca="false">IF(B290="","",IF(J290="Sí","Multa aplicada",IF(J290="No","Sin multa",IF(H290="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="291" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="6" t="str">
@@ -18606,10 +17451,6 @@
       <c r="K291" s="15"/>
       <c r="L291" s="16"/>
       <c r="M291" s="17"/>
-      <c r="N291" s="18" t="str">
-        <f aca="false">IF(B291="","",IF(J291="Sí","Multa aplicada",IF(J291="No","Sin multa",IF(H291="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="292" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="6" t="str">
@@ -18646,10 +17487,6 @@
       <c r="K292" s="15"/>
       <c r="L292" s="16"/>
       <c r="M292" s="17"/>
-      <c r="N292" s="18" t="str">
-        <f aca="false">IF(B292="","",IF(J292="Sí","Multa aplicada",IF(J292="No","Sin multa",IF(H292="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="293" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="6" t="str">
@@ -18686,10 +17523,6 @@
       <c r="K293" s="15"/>
       <c r="L293" s="16"/>
       <c r="M293" s="17"/>
-      <c r="N293" s="18" t="str">
-        <f aca="false">IF(B293="","",IF(J293="Sí","Multa aplicada",IF(J293="No","Sin multa",IF(H293="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="294" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="6" t="str">
@@ -18726,10 +17559,6 @@
       <c r="K294" s="15"/>
       <c r="L294" s="16"/>
       <c r="M294" s="17"/>
-      <c r="N294" s="18" t="str">
-        <f aca="false">IF(B294="","",IF(J294="Sí","Multa aplicada",IF(J294="No","Sin multa",IF(H294="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="295" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="6" t="str">
@@ -18766,10 +17595,6 @@
       <c r="K295" s="15"/>
       <c r="L295" s="16"/>
       <c r="M295" s="17"/>
-      <c r="N295" s="18" t="str">
-        <f aca="false">IF(B295="","",IF(J295="Sí","Multa aplicada",IF(J295="No","Sin multa",IF(H295="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="296" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="6" t="str">
@@ -18806,10 +17631,6 @@
       <c r="K296" s="15"/>
       <c r="L296" s="16"/>
       <c r="M296" s="17"/>
-      <c r="N296" s="18" t="str">
-        <f aca="false">IF(B296="","",IF(J296="Sí","Multa aplicada",IF(J296="No","Sin multa",IF(H296="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="297" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="6" t="str">
@@ -18846,10 +17667,6 @@
       <c r="K297" s="15"/>
       <c r="L297" s="16"/>
       <c r="M297" s="17"/>
-      <c r="N297" s="18" t="str">
-        <f aca="false">IF(B297="","",IF(J297="Sí","Multa aplicada",IF(J297="No","Sin multa",IF(H297="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="298" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="6" t="str">
@@ -18886,10 +17703,6 @@
       <c r="K298" s="15"/>
       <c r="L298" s="16"/>
       <c r="M298" s="17"/>
-      <c r="N298" s="18" t="str">
-        <f aca="false">IF(B298="","",IF(J298="Sí","Multa aplicada",IF(J298="No","Sin multa",IF(H298="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="299" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="6" t="str">
@@ -18926,10 +17739,6 @@
       <c r="K299" s="15"/>
       <c r="L299" s="16"/>
       <c r="M299" s="17"/>
-      <c r="N299" s="18" t="str">
-        <f aca="false">IF(B299="","",IF(J299="Sí","Multa aplicada",IF(J299="No","Sin multa",IF(H299="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="300" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="6" t="str">
@@ -18966,10 +17775,6 @@
       <c r="K300" s="15"/>
       <c r="L300" s="16"/>
       <c r="M300" s="17"/>
-      <c r="N300" s="18" t="str">
-        <f aca="false">IF(B300="","",IF(J300="Sí","Multa aplicada",IF(J300="No","Sin multa",IF(H300="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="301" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="6" t="str">
@@ -19006,10 +17811,6 @@
       <c r="K301" s="15"/>
       <c r="L301" s="16"/>
       <c r="M301" s="17"/>
-      <c r="N301" s="18" t="str">
-        <f aca="false">IF(B301="","",IF(J301="Sí","Multa aplicada",IF(J301="No","Sin multa",IF(H301="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="302" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="6" t="str">
@@ -19046,10 +17847,6 @@
       <c r="K302" s="15"/>
       <c r="L302" s="16"/>
       <c r="M302" s="17"/>
-      <c r="N302" s="18" t="str">
-        <f aca="false">IF(B302="","",IF(J302="Sí","Multa aplicada",IF(J302="No","Sin multa",IF(H302="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="303" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="6" t="str">
@@ -19086,10 +17883,6 @@
       <c r="K303" s="15"/>
       <c r="L303" s="16"/>
       <c r="M303" s="17"/>
-      <c r="N303" s="18" t="str">
-        <f aca="false">IF(B303="","",IF(J303="Sí","Multa aplicada",IF(J303="No","Sin multa",IF(H303="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="304" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="6" t="str">
@@ -19126,10 +17919,6 @@
       <c r="K304" s="15"/>
       <c r="L304" s="16"/>
       <c r="M304" s="17"/>
-      <c r="N304" s="18" t="str">
-        <f aca="false">IF(B304="","",IF(J304="Sí","Multa aplicada",IF(J304="No","Sin multa",IF(H304="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="305" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="6" t="str">
@@ -19166,10 +17955,6 @@
       <c r="K305" s="15"/>
       <c r="L305" s="16"/>
       <c r="M305" s="17"/>
-      <c r="N305" s="18" t="str">
-        <f aca="false">IF(B305="","",IF(J305="Sí","Multa aplicada",IF(J305="No","Sin multa",IF(H305="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="306" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="6" t="str">
@@ -19206,10 +17991,6 @@
       <c r="K306" s="15"/>
       <c r="L306" s="16"/>
       <c r="M306" s="17"/>
-      <c r="N306" s="18" t="str">
-        <f aca="false">IF(B306="","",IF(J306="Sí","Multa aplicada",IF(J306="No","Sin multa",IF(H306="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="307" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="6" t="str">
@@ -19246,10 +18027,6 @@
       <c r="K307" s="15"/>
       <c r="L307" s="16"/>
       <c r="M307" s="17"/>
-      <c r="N307" s="18" t="str">
-        <f aca="false">IF(B307="","",IF(J307="Sí","Multa aplicada",IF(J307="No","Sin multa",IF(H307="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="308" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="6" t="str">
@@ -19286,10 +18063,6 @@
       <c r="K308" s="15"/>
       <c r="L308" s="16"/>
       <c r="M308" s="17"/>
-      <c r="N308" s="18" t="str">
-        <f aca="false">IF(B308="","",IF(J308="Sí","Multa aplicada",IF(J308="No","Sin multa",IF(H308="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="309" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="6" t="str">
@@ -19326,10 +18099,6 @@
       <c r="K309" s="15"/>
       <c r="L309" s="16"/>
       <c r="M309" s="17"/>
-      <c r="N309" s="18" t="str">
-        <f aca="false">IF(B309="","",IF(J309="Sí","Multa aplicada",IF(J309="No","Sin multa",IF(H309="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="310" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="6" t="str">
@@ -19366,10 +18135,6 @@
       <c r="K310" s="15"/>
       <c r="L310" s="16"/>
       <c r="M310" s="17"/>
-      <c r="N310" s="18" t="str">
-        <f aca="false">IF(B310="","",IF(J310="Sí","Multa aplicada",IF(J310="No","Sin multa",IF(H310="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="311" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="6" t="str">
@@ -19406,10 +18171,6 @@
       <c r="K311" s="15"/>
       <c r="L311" s="16"/>
       <c r="M311" s="17"/>
-      <c r="N311" s="18" t="str">
-        <f aca="false">IF(B311="","",IF(J311="Sí","Multa aplicada",IF(J311="No","Sin multa",IF(H311="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="312" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="6" t="str">
@@ -19446,10 +18207,6 @@
       <c r="K312" s="15"/>
       <c r="L312" s="16"/>
       <c r="M312" s="17"/>
-      <c r="N312" s="18" t="str">
-        <f aca="false">IF(B312="","",IF(J312="Sí","Multa aplicada",IF(J312="No","Sin multa",IF(H312="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="313" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="6" t="str">
@@ -19486,10 +18243,6 @@
       <c r="K313" s="15"/>
       <c r="L313" s="16"/>
       <c r="M313" s="17"/>
-      <c r="N313" s="18" t="str">
-        <f aca="false">IF(B313="","",IF(J313="Sí","Multa aplicada",IF(J313="No","Sin multa",IF(H313="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="314" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="6" t="str">
@@ -19526,10 +18279,6 @@
       <c r="K314" s="15"/>
       <c r="L314" s="16"/>
       <c r="M314" s="17"/>
-      <c r="N314" s="18" t="str">
-        <f aca="false">IF(B314="","",IF(J314="Sí","Multa aplicada",IF(J314="No","Sin multa",IF(H314="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="315" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="6" t="str">
@@ -19566,10 +18315,6 @@
       <c r="K315" s="15"/>
       <c r="L315" s="16"/>
       <c r="M315" s="17"/>
-      <c r="N315" s="18" t="str">
-        <f aca="false">IF(B315="","",IF(J315="Sí","Multa aplicada",IF(J315="No","Sin multa",IF(H315="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="316" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="6" t="str">
@@ -19606,10 +18351,6 @@
       <c r="K316" s="15"/>
       <c r="L316" s="16"/>
       <c r="M316" s="17"/>
-      <c r="N316" s="18" t="str">
-        <f aca="false">IF(B316="","",IF(J316="Sí","Multa aplicada",IF(J316="No","Sin multa",IF(H316="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="317" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="6" t="str">
@@ -19646,10 +18387,6 @@
       <c r="K317" s="15"/>
       <c r="L317" s="16"/>
       <c r="M317" s="17"/>
-      <c r="N317" s="18" t="str">
-        <f aca="false">IF(B317="","",IF(J317="Sí","Multa aplicada",IF(J317="No","Sin multa",IF(H317="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="318" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="6" t="str">
@@ -19686,10 +18423,6 @@
       <c r="K318" s="15"/>
       <c r="L318" s="16"/>
       <c r="M318" s="17"/>
-      <c r="N318" s="18" t="str">
-        <f aca="false">IF(B318="","",IF(J318="Sí","Multa aplicada",IF(J318="No","Sin multa",IF(H318="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="319" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="6" t="str">
@@ -19726,10 +18459,6 @@
       <c r="K319" s="15"/>
       <c r="L319" s="16"/>
       <c r="M319" s="17"/>
-      <c r="N319" s="18" t="str">
-        <f aca="false">IF(B319="","",IF(J319="Sí","Multa aplicada",IF(J319="No","Sin multa",IF(H319="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="320" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="6" t="str">
@@ -19766,10 +18495,6 @@
       <c r="K320" s="15"/>
       <c r="L320" s="16"/>
       <c r="M320" s="17"/>
-      <c r="N320" s="18" t="str">
-        <f aca="false">IF(B320="","",IF(J320="Sí","Multa aplicada",IF(J320="No","Sin multa",IF(H320="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="321" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="6" t="str">
@@ -19806,10 +18531,6 @@
       <c r="K321" s="15"/>
       <c r="L321" s="16"/>
       <c r="M321" s="17"/>
-      <c r="N321" s="18" t="str">
-        <f aca="false">IF(B321="","",IF(J321="Sí","Multa aplicada",IF(J321="No","Sin multa",IF(H321="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="322" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="6" t="str">
@@ -19846,10 +18567,6 @@
       <c r="K322" s="15"/>
       <c r="L322" s="16"/>
       <c r="M322" s="17"/>
-      <c r="N322" s="18" t="str">
-        <f aca="false">IF(B322="","",IF(J322="Sí","Multa aplicada",IF(J322="No","Sin multa",IF(H322="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="323" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="6" t="str">
@@ -19886,10 +18603,6 @@
       <c r="K323" s="15"/>
       <c r="L323" s="16"/>
       <c r="M323" s="17"/>
-      <c r="N323" s="18" t="str">
-        <f aca="false">IF(B323="","",IF(J323="Sí","Multa aplicada",IF(J323="No","Sin multa",IF(H323="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="324" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="6" t="str">
@@ -19926,10 +18639,6 @@
       <c r="K324" s="15"/>
       <c r="L324" s="16"/>
       <c r="M324" s="17"/>
-      <c r="N324" s="18" t="str">
-        <f aca="false">IF(B324="","",IF(J324="Sí","Multa aplicada",IF(J324="No","Sin multa",IF(H324="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="325" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="6" t="str">
@@ -19966,10 +18675,6 @@
       <c r="K325" s="15"/>
       <c r="L325" s="16"/>
       <c r="M325" s="17"/>
-      <c r="N325" s="18" t="str">
-        <f aca="false">IF(B325="","",IF(J325="Sí","Multa aplicada",IF(J325="No","Sin multa",IF(H325="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="326" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="6" t="str">
@@ -20006,10 +18711,6 @@
       <c r="K326" s="15"/>
       <c r="L326" s="16"/>
       <c r="M326" s="17"/>
-      <c r="N326" s="18" t="str">
-        <f aca="false">IF(B326="","",IF(J326="Sí","Multa aplicada",IF(J326="No","Sin multa",IF(H326="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="327" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="6" t="str">
@@ -20046,10 +18747,6 @@
       <c r="K327" s="15"/>
       <c r="L327" s="16"/>
       <c r="M327" s="17"/>
-      <c r="N327" s="18" t="str">
-        <f aca="false">IF(B327="","",IF(J327="Sí","Multa aplicada",IF(J327="No","Sin multa",IF(H327="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="328" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="6" t="str">
@@ -20086,10 +18783,6 @@
       <c r="K328" s="15"/>
       <c r="L328" s="16"/>
       <c r="M328" s="17"/>
-      <c r="N328" s="18" t="str">
-        <f aca="false">IF(B328="","",IF(J328="Sí","Multa aplicada",IF(J328="No","Sin multa",IF(H328="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="329" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="6" t="str">
@@ -20126,10 +18819,6 @@
       <c r="K329" s="15"/>
       <c r="L329" s="16"/>
       <c r="M329" s="17"/>
-      <c r="N329" s="18" t="str">
-        <f aca="false">IF(B329="","",IF(J329="Sí","Multa aplicada",IF(J329="No","Sin multa",IF(H329="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="330" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="6" t="str">
@@ -20166,10 +18855,6 @@
       <c r="K330" s="15"/>
       <c r="L330" s="16"/>
       <c r="M330" s="17"/>
-      <c r="N330" s="18" t="str">
-        <f aca="false">IF(B330="","",IF(J330="Sí","Multa aplicada",IF(J330="No","Sin multa",IF(H330="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="331" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="6" t="str">
@@ -20206,10 +18891,6 @@
       <c r="K331" s="15"/>
       <c r="L331" s="16"/>
       <c r="M331" s="17"/>
-      <c r="N331" s="18" t="str">
-        <f aca="false">IF(B331="","",IF(J331="Sí","Multa aplicada",IF(J331="No","Sin multa",IF(H331="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="332" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="6" t="str">
@@ -20246,10 +18927,6 @@
       <c r="K332" s="15"/>
       <c r="L332" s="16"/>
       <c r="M332" s="17"/>
-      <c r="N332" s="18" t="str">
-        <f aca="false">IF(B332="","",IF(J332="Sí","Multa aplicada",IF(J332="No","Sin multa",IF(H332="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="333" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="6" t="str">
@@ -20286,10 +18963,6 @@
       <c r="K333" s="15"/>
       <c r="L333" s="16"/>
       <c r="M333" s="17"/>
-      <c r="N333" s="18" t="str">
-        <f aca="false">IF(B333="","",IF(J333="Sí","Multa aplicada",IF(J333="No","Sin multa",IF(H333="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="334" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="6" t="str">
@@ -20326,10 +18999,6 @@
       <c r="K334" s="15"/>
       <c r="L334" s="16"/>
       <c r="M334" s="17"/>
-      <c r="N334" s="18" t="str">
-        <f aca="false">IF(B334="","",IF(J334="Sí","Multa aplicada",IF(J334="No","Sin multa",IF(H334="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="335" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="6" t="str">
@@ -20366,10 +19035,6 @@
       <c r="K335" s="15"/>
       <c r="L335" s="16"/>
       <c r="M335" s="17"/>
-      <c r="N335" s="18" t="str">
-        <f aca="false">IF(B335="","",IF(J335="Sí","Multa aplicada",IF(J335="No","Sin multa",IF(H335="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="336" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="6" t="str">
@@ -20406,10 +19071,6 @@
       <c r="K336" s="15"/>
       <c r="L336" s="16"/>
       <c r="M336" s="17"/>
-      <c r="N336" s="18" t="str">
-        <f aca="false">IF(B336="","",IF(J336="Sí","Multa aplicada",IF(J336="No","Sin multa",IF(H336="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="337" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="6" t="str">
@@ -20446,10 +19107,6 @@
       <c r="K337" s="15"/>
       <c r="L337" s="16"/>
       <c r="M337" s="17"/>
-      <c r="N337" s="18" t="str">
-        <f aca="false">IF(B337="","",IF(J337="Sí","Multa aplicada",IF(J337="No","Sin multa",IF(H337="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="338" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="6" t="str">
@@ -20486,10 +19143,6 @@
       <c r="K338" s="15"/>
       <c r="L338" s="16"/>
       <c r="M338" s="17"/>
-      <c r="N338" s="18" t="str">
-        <f aca="false">IF(B338="","",IF(J338="Sí","Multa aplicada",IF(J338="No","Sin multa",IF(H338="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="339" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="6" t="str">
@@ -20526,10 +19179,6 @@
       <c r="K339" s="15"/>
       <c r="L339" s="16"/>
       <c r="M339" s="17"/>
-      <c r="N339" s="18" t="str">
-        <f aca="false">IF(B339="","",IF(J339="Sí","Multa aplicada",IF(J339="No","Sin multa",IF(H339="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="340" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="6" t="str">
@@ -20566,10 +19215,6 @@
       <c r="K340" s="15"/>
       <c r="L340" s="16"/>
       <c r="M340" s="17"/>
-      <c r="N340" s="18" t="str">
-        <f aca="false">IF(B340="","",IF(J340="Sí","Multa aplicada",IF(J340="No","Sin multa",IF(H340="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="341" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="6" t="str">
@@ -20606,10 +19251,6 @@
       <c r="K341" s="15"/>
       <c r="L341" s="16"/>
       <c r="M341" s="17"/>
-      <c r="N341" s="18" t="str">
-        <f aca="false">IF(B341="","",IF(J341="Sí","Multa aplicada",IF(J341="No","Sin multa",IF(H341="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="342" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="6" t="str">
@@ -20646,10 +19287,6 @@
       <c r="K342" s="15"/>
       <c r="L342" s="16"/>
       <c r="M342" s="17"/>
-      <c r="N342" s="18" t="str">
-        <f aca="false">IF(B342="","",IF(J342="Sí","Multa aplicada",IF(J342="No","Sin multa",IF(H342="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="343" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="6" t="str">
@@ -20686,10 +19323,6 @@
       <c r="K343" s="15"/>
       <c r="L343" s="16"/>
       <c r="M343" s="17"/>
-      <c r="N343" s="18" t="str">
-        <f aca="false">IF(B343="","",IF(J343="Sí","Multa aplicada",IF(J343="No","Sin multa",IF(H343="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="344" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="6" t="str">
@@ -20726,10 +19359,6 @@
       <c r="K344" s="15"/>
       <c r="L344" s="16"/>
       <c r="M344" s="17"/>
-      <c r="N344" s="18" t="str">
-        <f aca="false">IF(B344="","",IF(J344="Sí","Multa aplicada",IF(J344="No","Sin multa",IF(H344="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="345" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="6" t="str">
@@ -20766,10 +19395,6 @@
       <c r="K345" s="15"/>
       <c r="L345" s="16"/>
       <c r="M345" s="17"/>
-      <c r="N345" s="18" t="str">
-        <f aca="false">IF(B345="","",IF(J345="Sí","Multa aplicada",IF(J345="No","Sin multa",IF(H345="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="346" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="6" t="str">
@@ -20806,10 +19431,6 @@
       <c r="K346" s="15"/>
       <c r="L346" s="16"/>
       <c r="M346" s="17"/>
-      <c r="N346" s="18" t="str">
-        <f aca="false">IF(B346="","",IF(J346="Sí","Multa aplicada",IF(J346="No","Sin multa",IF(H346="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="347" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="6" t="str">
@@ -20846,10 +19467,6 @@
       <c r="K347" s="15"/>
       <c r="L347" s="16"/>
       <c r="M347" s="17"/>
-      <c r="N347" s="18" t="str">
-        <f aca="false">IF(B347="","",IF(J347="Sí","Multa aplicada",IF(J347="No","Sin multa",IF(H347="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="348" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="6" t="str">
@@ -20886,10 +19503,6 @@
       <c r="K348" s="15"/>
       <c r="L348" s="16"/>
       <c r="M348" s="17"/>
-      <c r="N348" s="18" t="str">
-        <f aca="false">IF(B348="","",IF(J348="Sí","Multa aplicada",IF(J348="No","Sin multa",IF(H348="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="349" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="6" t="str">
@@ -20926,10 +19539,6 @@
       <c r="K349" s="15"/>
       <c r="L349" s="16"/>
       <c r="M349" s="17"/>
-      <c r="N349" s="18" t="str">
-        <f aca="false">IF(B349="","",IF(J349="Sí","Multa aplicada",IF(J349="No","Sin multa",IF(H349="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="350" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="6" t="str">
@@ -20966,10 +19575,6 @@
       <c r="K350" s="15"/>
       <c r="L350" s="16"/>
       <c r="M350" s="17"/>
-      <c r="N350" s="18" t="str">
-        <f aca="false">IF(B350="","",IF(J350="Sí","Multa aplicada",IF(J350="No","Sin multa",IF(H350="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="351" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="6" t="str">
@@ -21006,10 +19611,6 @@
       <c r="K351" s="15"/>
       <c r="L351" s="16"/>
       <c r="M351" s="17"/>
-      <c r="N351" s="18" t="str">
-        <f aca="false">IF(B351="","",IF(J351="Sí","Multa aplicada",IF(J351="No","Sin multa",IF(H351="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="352" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="6" t="str">
@@ -21046,10 +19647,6 @@
       <c r="K352" s="15"/>
       <c r="L352" s="16"/>
       <c r="M352" s="17"/>
-      <c r="N352" s="18" t="str">
-        <f aca="false">IF(B352="","",IF(J352="Sí","Multa aplicada",IF(J352="No","Sin multa",IF(H352="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="353" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="6" t="str">
@@ -21086,10 +19683,6 @@
       <c r="K353" s="15"/>
       <c r="L353" s="16"/>
       <c r="M353" s="17"/>
-      <c r="N353" s="18" t="str">
-        <f aca="false">IF(B353="","",IF(J353="Sí","Multa aplicada",IF(J353="No","Sin multa",IF(H353="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="354" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="6" t="str">
@@ -21126,10 +19719,6 @@
       <c r="K354" s="15"/>
       <c r="L354" s="16"/>
       <c r="M354" s="17"/>
-      <c r="N354" s="18" t="str">
-        <f aca="false">IF(B354="","",IF(J354="Sí","Multa aplicada",IF(J354="No","Sin multa",IF(H354="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="355" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="6" t="str">
@@ -21166,10 +19755,6 @@
       <c r="K355" s="15"/>
       <c r="L355" s="16"/>
       <c r="M355" s="17"/>
-      <c r="N355" s="18" t="str">
-        <f aca="false">IF(B355="","",IF(J355="Sí","Multa aplicada",IF(J355="No","Sin multa",IF(H355="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="356" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="6" t="str">
@@ -21206,10 +19791,6 @@
       <c r="K356" s="15"/>
       <c r="L356" s="16"/>
       <c r="M356" s="17"/>
-      <c r="N356" s="18" t="str">
-        <f aca="false">IF(B356="","",IF(J356="Sí","Multa aplicada",IF(J356="No","Sin multa",IF(H356="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="357" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="6" t="str">
@@ -21246,10 +19827,6 @@
       <c r="K357" s="15"/>
       <c r="L357" s="16"/>
       <c r="M357" s="17"/>
-      <c r="N357" s="18" t="str">
-        <f aca="false">IF(B357="","",IF(J357="Sí","Multa aplicada",IF(J357="No","Sin multa",IF(H357="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="358" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="6" t="str">
@@ -21286,10 +19863,6 @@
       <c r="K358" s="15"/>
       <c r="L358" s="16"/>
       <c r="M358" s="17"/>
-      <c r="N358" s="18" t="str">
-        <f aca="false">IF(B358="","",IF(J358="Sí","Multa aplicada",IF(J358="No","Sin multa",IF(H358="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="359" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="6" t="str">
@@ -21326,10 +19899,6 @@
       <c r="K359" s="15"/>
       <c r="L359" s="16"/>
       <c r="M359" s="17"/>
-      <c r="N359" s="18" t="str">
-        <f aca="false">IF(B359="","",IF(J359="Sí","Multa aplicada",IF(J359="No","Sin multa",IF(H359="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="360" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="6" t="str">
@@ -21366,10 +19935,6 @@
       <c r="K360" s="15"/>
       <c r="L360" s="16"/>
       <c r="M360" s="17"/>
-      <c r="N360" s="18" t="str">
-        <f aca="false">IF(B360="","",IF(J360="Sí","Multa aplicada",IF(J360="No","Sin multa",IF(H360="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="361" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="6" t="str">
@@ -21406,10 +19971,6 @@
       <c r="K361" s="15"/>
       <c r="L361" s="16"/>
       <c r="M361" s="17"/>
-      <c r="N361" s="18" t="str">
-        <f aca="false">IF(B361="","",IF(J361="Sí","Multa aplicada",IF(J361="No","Sin multa",IF(H361="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="362" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="6" t="str">
@@ -21446,10 +20007,6 @@
       <c r="K362" s="15"/>
       <c r="L362" s="16"/>
       <c r="M362" s="17"/>
-      <c r="N362" s="18" t="str">
-        <f aca="false">IF(B362="","",IF(J362="Sí","Multa aplicada",IF(J362="No","Sin multa",IF(H362="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="363" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="6" t="str">
@@ -21486,10 +20043,6 @@
       <c r="K363" s="15"/>
       <c r="L363" s="16"/>
       <c r="M363" s="17"/>
-      <c r="N363" s="18" t="str">
-        <f aca="false">IF(B363="","",IF(J363="Sí","Multa aplicada",IF(J363="No","Sin multa",IF(H363="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="364" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="6" t="str">
@@ -21526,10 +20079,6 @@
       <c r="K364" s="15"/>
       <c r="L364" s="16"/>
       <c r="M364" s="17"/>
-      <c r="N364" s="18" t="str">
-        <f aca="false">IF(B364="","",IF(J364="Sí","Multa aplicada",IF(J364="No","Sin multa",IF(H364="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="365" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="6" t="str">
@@ -21566,10 +20115,6 @@
       <c r="K365" s="15"/>
       <c r="L365" s="16"/>
       <c r="M365" s="17"/>
-      <c r="N365" s="18" t="str">
-        <f aca="false">IF(B365="","",IF(J365="Sí","Multa aplicada",IF(J365="No","Sin multa",IF(H365="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="366" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="6" t="str">
@@ -21606,10 +20151,6 @@
       <c r="K366" s="15"/>
       <c r="L366" s="16"/>
       <c r="M366" s="17"/>
-      <c r="N366" s="18" t="str">
-        <f aca="false">IF(B366="","",IF(J366="Sí","Multa aplicada",IF(J366="No","Sin multa",IF(H366="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="367" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="6" t="str">
@@ -21646,10 +20187,6 @@
       <c r="K367" s="15"/>
       <c r="L367" s="16"/>
       <c r="M367" s="17"/>
-      <c r="N367" s="18" t="str">
-        <f aca="false">IF(B367="","",IF(J367="Sí","Multa aplicada",IF(J367="No","Sin multa",IF(H367="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="368" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="6" t="str">
@@ -21686,10 +20223,6 @@
       <c r="K368" s="15"/>
       <c r="L368" s="16"/>
       <c r="M368" s="17"/>
-      <c r="N368" s="18" t="str">
-        <f aca="false">IF(B368="","",IF(J368="Sí","Multa aplicada",IF(J368="No","Sin multa",IF(H368="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="369" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="6" t="str">
@@ -21726,10 +20259,6 @@
       <c r="K369" s="15"/>
       <c r="L369" s="16"/>
       <c r="M369" s="17"/>
-      <c r="N369" s="18" t="str">
-        <f aca="false">IF(B369="","",IF(J369="Sí","Multa aplicada",IF(J369="No","Sin multa",IF(H369="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="370" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="6" t="str">
@@ -21766,10 +20295,6 @@
       <c r="K370" s="15"/>
       <c r="L370" s="16"/>
       <c r="M370" s="17"/>
-      <c r="N370" s="18" t="str">
-        <f aca="false">IF(B370="","",IF(J370="Sí","Multa aplicada",IF(J370="No","Sin multa",IF(H370="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="371" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="6" t="str">
@@ -21806,10 +20331,6 @@
       <c r="K371" s="15"/>
       <c r="L371" s="16"/>
       <c r="M371" s="17"/>
-      <c r="N371" s="18" t="str">
-        <f aca="false">IF(B371="","",IF(J371="Sí","Multa aplicada",IF(J371="No","Sin multa",IF(H371="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="372" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="6" t="str">
@@ -21846,10 +20367,6 @@
       <c r="K372" s="15"/>
       <c r="L372" s="16"/>
       <c r="M372" s="17"/>
-      <c r="N372" s="18" t="str">
-        <f aca="false">IF(B372="","",IF(J372="Sí","Multa aplicada",IF(J372="No","Sin multa",IF(H372="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="373" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="6" t="str">
@@ -21886,10 +20403,6 @@
       <c r="K373" s="15"/>
       <c r="L373" s="16"/>
       <c r="M373" s="17"/>
-      <c r="N373" s="18" t="str">
-        <f aca="false">IF(B373="","",IF(J373="Sí","Multa aplicada",IF(J373="No","Sin multa",IF(H373="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="374" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="6" t="str">
@@ -21926,10 +20439,6 @@
       <c r="K374" s="15"/>
       <c r="L374" s="16"/>
       <c r="M374" s="17"/>
-      <c r="N374" s="18" t="str">
-        <f aca="false">IF(B374="","",IF(J374="Sí","Multa aplicada",IF(J374="No","Sin multa",IF(H374="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="375" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="6" t="str">
@@ -21966,10 +20475,6 @@
       <c r="K375" s="15"/>
       <c r="L375" s="16"/>
       <c r="M375" s="17"/>
-      <c r="N375" s="18" t="str">
-        <f aca="false">IF(B375="","",IF(J375="Sí","Multa aplicada",IF(J375="No","Sin multa",IF(H375="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="376" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="6" t="str">
@@ -22006,10 +20511,6 @@
       <c r="K376" s="15"/>
       <c r="L376" s="16"/>
       <c r="M376" s="17"/>
-      <c r="N376" s="18" t="str">
-        <f aca="false">IF(B376="","",IF(J376="Sí","Multa aplicada",IF(J376="No","Sin multa",IF(H376="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="377" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="6" t="str">
@@ -22046,10 +20547,6 @@
       <c r="K377" s="15"/>
       <c r="L377" s="16"/>
       <c r="M377" s="17"/>
-      <c r="N377" s="18" t="str">
-        <f aca="false">IF(B377="","",IF(J377="Sí","Multa aplicada",IF(J377="No","Sin multa",IF(H377="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="378" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="6" t="str">
@@ -22086,10 +20583,6 @@
       <c r="K378" s="15"/>
       <c r="L378" s="16"/>
       <c r="M378" s="17"/>
-      <c r="N378" s="18" t="str">
-        <f aca="false">IF(B378="","",IF(J378="Sí","Multa aplicada",IF(J378="No","Sin multa",IF(H378="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="379" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="6" t="str">
@@ -22126,10 +20619,6 @@
       <c r="K379" s="15"/>
       <c r="L379" s="16"/>
       <c r="M379" s="17"/>
-      <c r="N379" s="18" t="str">
-        <f aca="false">IF(B379="","",IF(J379="Sí","Multa aplicada",IF(J379="No","Sin multa",IF(H379="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="380" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="6" t="str">
@@ -22166,10 +20655,6 @@
       <c r="K380" s="15"/>
       <c r="L380" s="16"/>
       <c r="M380" s="17"/>
-      <c r="N380" s="18" t="str">
-        <f aca="false">IF(B380="","",IF(J380="Sí","Multa aplicada",IF(J380="No","Sin multa",IF(H380="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="381" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="6" t="str">
@@ -22206,10 +20691,6 @@
       <c r="K381" s="15"/>
       <c r="L381" s="16"/>
       <c r="M381" s="17"/>
-      <c r="N381" s="18" t="str">
-        <f aca="false">IF(B381="","",IF(J381="Sí","Multa aplicada",IF(J381="No","Sin multa",IF(H381="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="382" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="6" t="str">
@@ -22246,10 +20727,6 @@
       <c r="K382" s="15"/>
       <c r="L382" s="16"/>
       <c r="M382" s="17"/>
-      <c r="N382" s="18" t="str">
-        <f aca="false">IF(B382="","",IF(J382="Sí","Multa aplicada",IF(J382="No","Sin multa",IF(H382="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="383" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="6" t="str">
@@ -22286,10 +20763,6 @@
       <c r="K383" s="15"/>
       <c r="L383" s="16"/>
       <c r="M383" s="17"/>
-      <c r="N383" s="18" t="str">
-        <f aca="false">IF(B383="","",IF(J383="Sí","Multa aplicada",IF(J383="No","Sin multa",IF(H383="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="384" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="6" t="str">
@@ -22326,10 +20799,6 @@
       <c r="K384" s="15"/>
       <c r="L384" s="16"/>
       <c r="M384" s="17"/>
-      <c r="N384" s="18" t="str">
-        <f aca="false">IF(B384="","",IF(J384="Sí","Multa aplicada",IF(J384="No","Sin multa",IF(H384="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="385" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="6" t="str">
@@ -22366,10 +20835,6 @@
       <c r="K385" s="15"/>
       <c r="L385" s="16"/>
       <c r="M385" s="17"/>
-      <c r="N385" s="18" t="str">
-        <f aca="false">IF(B385="","",IF(J385="Sí","Multa aplicada",IF(J385="No","Sin multa",IF(H385="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="386" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="6" t="str">
@@ -22406,10 +20871,6 @@
       <c r="K386" s="15"/>
       <c r="L386" s="16"/>
       <c r="M386" s="17"/>
-      <c r="N386" s="18" t="str">
-        <f aca="false">IF(B386="","",IF(J386="Sí","Multa aplicada",IF(J386="No","Sin multa",IF(H386="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="387" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="6" t="str">
@@ -22446,10 +20907,6 @@
       <c r="K387" s="15"/>
       <c r="L387" s="16"/>
       <c r="M387" s="17"/>
-      <c r="N387" s="18" t="str">
-        <f aca="false">IF(B387="","",IF(J387="Sí","Multa aplicada",IF(J387="No","Sin multa",IF(H387="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="388" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="6" t="str">
@@ -22486,10 +20943,6 @@
       <c r="K388" s="15"/>
       <c r="L388" s="16"/>
       <c r="M388" s="17"/>
-      <c r="N388" s="18" t="str">
-        <f aca="false">IF(B388="","",IF(J388="Sí","Multa aplicada",IF(J388="No","Sin multa",IF(H388="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="389" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="6" t="str">
@@ -22526,10 +20979,6 @@
       <c r="K389" s="15"/>
       <c r="L389" s="16"/>
       <c r="M389" s="17"/>
-      <c r="N389" s="18" t="str">
-        <f aca="false">IF(B389="","",IF(J389="Sí","Multa aplicada",IF(J389="No","Sin multa",IF(H389="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="390" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="6" t="str">
@@ -22566,10 +21015,6 @@
       <c r="K390" s="15"/>
       <c r="L390" s="16"/>
       <c r="M390" s="17"/>
-      <c r="N390" s="18" t="str">
-        <f aca="false">IF(B390="","",IF(J390="Sí","Multa aplicada",IF(J390="No","Sin multa",IF(H390="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="391" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="6" t="str">
@@ -22606,10 +21051,6 @@
       <c r="K391" s="15"/>
       <c r="L391" s="16"/>
       <c r="M391" s="17"/>
-      <c r="N391" s="18" t="str">
-        <f aca="false">IF(B391="","",IF(J391="Sí","Multa aplicada",IF(J391="No","Sin multa",IF(H391="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="392" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="6" t="str">
@@ -22646,10 +21087,6 @@
       <c r="K392" s="15"/>
       <c r="L392" s="16"/>
       <c r="M392" s="17"/>
-      <c r="N392" s="18" t="str">
-        <f aca="false">IF(B392="","",IF(J392="Sí","Multa aplicada",IF(J392="No","Sin multa",IF(H392="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="393" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="6" t="str">
@@ -22686,10 +21123,6 @@
       <c r="K393" s="15"/>
       <c r="L393" s="16"/>
       <c r="M393" s="17"/>
-      <c r="N393" s="18" t="str">
-        <f aca="false">IF(B393="","",IF(J393="Sí","Multa aplicada",IF(J393="No","Sin multa",IF(H393="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="394" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="6" t="str">
@@ -22726,10 +21159,6 @@
       <c r="K394" s="15"/>
       <c r="L394" s="16"/>
       <c r="M394" s="17"/>
-      <c r="N394" s="18" t="str">
-        <f aca="false">IF(B394="","",IF(J394="Sí","Multa aplicada",IF(J394="No","Sin multa",IF(H394="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="395" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="6" t="str">
@@ -22766,10 +21195,6 @@
       <c r="K395" s="15"/>
       <c r="L395" s="16"/>
       <c r="M395" s="17"/>
-      <c r="N395" s="18" t="str">
-        <f aca="false">IF(B395="","",IF(J395="Sí","Multa aplicada",IF(J395="No","Sin multa",IF(H395="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="396" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="6" t="str">
@@ -22806,10 +21231,6 @@
       <c r="K396" s="15"/>
       <c r="L396" s="16"/>
       <c r="M396" s="17"/>
-      <c r="N396" s="18" t="str">
-        <f aca="false">IF(B396="","",IF(J396="Sí","Multa aplicada",IF(J396="No","Sin multa",IF(H396="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="397" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="6" t="str">
@@ -22846,10 +21267,6 @@
       <c r="K397" s="15"/>
       <c r="L397" s="16"/>
       <c r="M397" s="17"/>
-      <c r="N397" s="18" t="str">
-        <f aca="false">IF(B397="","",IF(J397="Sí","Multa aplicada",IF(J397="No","Sin multa",IF(H397="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="398" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="6" t="str">
@@ -22886,10 +21303,6 @@
       <c r="K398" s="15"/>
       <c r="L398" s="16"/>
       <c r="M398" s="17"/>
-      <c r="N398" s="18" t="str">
-        <f aca="false">IF(B398="","",IF(J398="Sí","Multa aplicada",IF(J398="No","Sin multa",IF(H398="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="399" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="6" t="str">
@@ -22926,10 +21339,6 @@
       <c r="K399" s="15"/>
       <c r="L399" s="16"/>
       <c r="M399" s="17"/>
-      <c r="N399" s="18" t="str">
-        <f aca="false">IF(B399="","",IF(J399="Sí","Multa aplicada",IF(J399="No","Sin multa",IF(H399="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="400" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="6" t="str">
@@ -22966,10 +21375,6 @@
       <c r="K400" s="15"/>
       <c r="L400" s="16"/>
       <c r="M400" s="17"/>
-      <c r="N400" s="18" t="str">
-        <f aca="false">IF(B400="","",IF(J400="Sí","Multa aplicada",IF(J400="No","Sin multa",IF(H400="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="401" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="6" t="str">
@@ -23006,10 +21411,6 @@
       <c r="K401" s="15"/>
       <c r="L401" s="16"/>
       <c r="M401" s="17"/>
-      <c r="N401" s="18" t="str">
-        <f aca="false">IF(B401="","",IF(J401="Sí","Multa aplicada",IF(J401="No","Sin multa",IF(H401="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="402" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="6" t="str">
@@ -23046,10 +21447,6 @@
       <c r="K402" s="15"/>
       <c r="L402" s="16"/>
       <c r="M402" s="17"/>
-      <c r="N402" s="18" t="str">
-        <f aca="false">IF(B402="","",IF(J402="Sí","Multa aplicada",IF(J402="No","Sin multa",IF(H402="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="403" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="6" t="str">
@@ -23086,10 +21483,6 @@
       <c r="K403" s="15"/>
       <c r="L403" s="16"/>
       <c r="M403" s="17"/>
-      <c r="N403" s="18" t="str">
-        <f aca="false">IF(B403="","",IF(J403="Sí","Multa aplicada",IF(J403="No","Sin multa",IF(H403="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="404" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="6" t="str">
@@ -23126,10 +21519,6 @@
       <c r="K404" s="15"/>
       <c r="L404" s="16"/>
       <c r="M404" s="17"/>
-      <c r="N404" s="18" t="str">
-        <f aca="false">IF(B404="","",IF(J404="Sí","Multa aplicada",IF(J404="No","Sin multa",IF(H404="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="405" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="6" t="str">
@@ -23166,10 +21555,6 @@
       <c r="K405" s="15"/>
       <c r="L405" s="16"/>
       <c r="M405" s="17"/>
-      <c r="N405" s="18" t="str">
-        <f aca="false">IF(B405="","",IF(J405="Sí","Multa aplicada",IF(J405="No","Sin multa",IF(H405="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="406" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="6" t="str">
@@ -23206,10 +21591,6 @@
       <c r="K406" s="15"/>
       <c r="L406" s="16"/>
       <c r="M406" s="17"/>
-      <c r="N406" s="18" t="str">
-        <f aca="false">IF(B406="","",IF(J406="Sí","Multa aplicada",IF(J406="No","Sin multa",IF(H406="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="407" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="6" t="str">
@@ -23246,10 +21627,6 @@
       <c r="K407" s="15"/>
       <c r="L407" s="16"/>
       <c r="M407" s="17"/>
-      <c r="N407" s="18" t="str">
-        <f aca="false">IF(B407="","",IF(J407="Sí","Multa aplicada",IF(J407="No","Sin multa",IF(H407="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="408" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="6" t="str">
@@ -23286,10 +21663,6 @@
       <c r="K408" s="15"/>
       <c r="L408" s="16"/>
       <c r="M408" s="17"/>
-      <c r="N408" s="18" t="str">
-        <f aca="false">IF(B408="","",IF(J408="Sí","Multa aplicada",IF(J408="No","Sin multa",IF(H408="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="409" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="6" t="str">
@@ -23326,10 +21699,6 @@
       <c r="K409" s="15"/>
       <c r="L409" s="16"/>
       <c r="M409" s="17"/>
-      <c r="N409" s="18" t="str">
-        <f aca="false">IF(B409="","",IF(J409="Sí","Multa aplicada",IF(J409="No","Sin multa",IF(H409="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="410" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="6" t="str">
@@ -23366,10 +21735,6 @@
       <c r="K410" s="15"/>
       <c r="L410" s="16"/>
       <c r="M410" s="17"/>
-      <c r="N410" s="18" t="str">
-        <f aca="false">IF(B410="","",IF(J410="Sí","Multa aplicada",IF(J410="No","Sin multa",IF(H410="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="411" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="6" t="str">
@@ -23406,10 +21771,6 @@
       <c r="K411" s="15"/>
       <c r="L411" s="16"/>
       <c r="M411" s="17"/>
-      <c r="N411" s="18" t="str">
-        <f aca="false">IF(B411="","",IF(J411="Sí","Multa aplicada",IF(J411="No","Sin multa",IF(H411="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="412" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="6" t="str">
@@ -23446,10 +21807,6 @@
       <c r="K412" s="15"/>
       <c r="L412" s="16"/>
       <c r="M412" s="17"/>
-      <c r="N412" s="18" t="str">
-        <f aca="false">IF(B412="","",IF(J412="Sí","Multa aplicada",IF(J412="No","Sin multa",IF(H412="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="413" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="6" t="str">
@@ -23486,10 +21843,6 @@
       <c r="K413" s="15"/>
       <c r="L413" s="16"/>
       <c r="M413" s="17"/>
-      <c r="N413" s="18" t="str">
-        <f aca="false">IF(B413="","",IF(J413="Sí","Multa aplicada",IF(J413="No","Sin multa",IF(H413="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="414" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="6" t="str">
@@ -23526,10 +21879,6 @@
       <c r="K414" s="15"/>
       <c r="L414" s="16"/>
       <c r="M414" s="17"/>
-      <c r="N414" s="18" t="str">
-        <f aca="false">IF(B414="","",IF(J414="Sí","Multa aplicada",IF(J414="No","Sin multa",IF(H414="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="415" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="6" t="str">
@@ -23566,10 +21915,6 @@
       <c r="K415" s="15"/>
       <c r="L415" s="16"/>
       <c r="M415" s="17"/>
-      <c r="N415" s="18" t="str">
-        <f aca="false">IF(B415="","",IF(J415="Sí","Multa aplicada",IF(J415="No","Sin multa",IF(H415="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="416" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="6" t="str">
@@ -23606,10 +21951,6 @@
       <c r="K416" s="15"/>
       <c r="L416" s="16"/>
       <c r="M416" s="17"/>
-      <c r="N416" s="18" t="str">
-        <f aca="false">IF(B416="","",IF(J416="Sí","Multa aplicada",IF(J416="No","Sin multa",IF(H416="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="417" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="6" t="str">
@@ -23646,10 +21987,6 @@
       <c r="K417" s="15"/>
       <c r="L417" s="16"/>
       <c r="M417" s="17"/>
-      <c r="N417" s="18" t="str">
-        <f aca="false">IF(B417="","",IF(J417="Sí","Multa aplicada",IF(J417="No","Sin multa",IF(H417="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="418" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="6" t="str">
@@ -23686,10 +22023,6 @@
       <c r="K418" s="15"/>
       <c r="L418" s="16"/>
       <c r="M418" s="17"/>
-      <c r="N418" s="18" t="str">
-        <f aca="false">IF(B418="","",IF(J418="Sí","Multa aplicada",IF(J418="No","Sin multa",IF(H418="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="419" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="6" t="str">
@@ -23726,10 +22059,6 @@
       <c r="K419" s="15"/>
       <c r="L419" s="16"/>
       <c r="M419" s="17"/>
-      <c r="N419" s="18" t="str">
-        <f aca="false">IF(B419="","",IF(J419="Sí","Multa aplicada",IF(J419="No","Sin multa",IF(H419="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="420" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="6" t="str">
@@ -23766,10 +22095,6 @@
       <c r="K420" s="15"/>
       <c r="L420" s="16"/>
       <c r="M420" s="17"/>
-      <c r="N420" s="18" t="str">
-        <f aca="false">IF(B420="","",IF(J420="Sí","Multa aplicada",IF(J420="No","Sin multa",IF(H420="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="421" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="6" t="str">
@@ -23806,10 +22131,6 @@
       <c r="K421" s="15"/>
       <c r="L421" s="16"/>
       <c r="M421" s="17"/>
-      <c r="N421" s="18" t="str">
-        <f aca="false">IF(B421="","",IF(J421="Sí","Multa aplicada",IF(J421="No","Sin multa",IF(H421="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="422" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="6" t="str">
@@ -23846,10 +22167,6 @@
       <c r="K422" s="15"/>
       <c r="L422" s="16"/>
       <c r="M422" s="17"/>
-      <c r="N422" s="18" t="str">
-        <f aca="false">IF(B422="","",IF(J422="Sí","Multa aplicada",IF(J422="No","Sin multa",IF(H422="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="423" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="6" t="str">
@@ -23886,10 +22203,6 @@
       <c r="K423" s="15"/>
       <c r="L423" s="16"/>
       <c r="M423" s="17"/>
-      <c r="N423" s="18" t="str">
-        <f aca="false">IF(B423="","",IF(J423="Sí","Multa aplicada",IF(J423="No","Sin multa",IF(H423="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="424" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="6" t="str">
@@ -23926,10 +22239,6 @@
       <c r="K424" s="15"/>
       <c r="L424" s="16"/>
       <c r="M424" s="17"/>
-      <c r="N424" s="18" t="str">
-        <f aca="false">IF(B424="","",IF(J424="Sí","Multa aplicada",IF(J424="No","Sin multa",IF(H424="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="425" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="6" t="str">
@@ -23966,10 +22275,6 @@
       <c r="K425" s="15"/>
       <c r="L425" s="16"/>
       <c r="M425" s="17"/>
-      <c r="N425" s="18" t="str">
-        <f aca="false">IF(B425="","",IF(J425="Sí","Multa aplicada",IF(J425="No","Sin multa",IF(H425="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="426" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="6" t="str">
@@ -24006,10 +22311,6 @@
       <c r="K426" s="15"/>
       <c r="L426" s="16"/>
       <c r="M426" s="17"/>
-      <c r="N426" s="18" t="str">
-        <f aca="false">IF(B426="","",IF(J426="Sí","Multa aplicada",IF(J426="No","Sin multa",IF(H426="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="427" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="6" t="str">
@@ -24046,10 +22347,6 @@
       <c r="K427" s="15"/>
       <c r="L427" s="16"/>
       <c r="M427" s="17"/>
-      <c r="N427" s="18" t="str">
-        <f aca="false">IF(B427="","",IF(J427="Sí","Multa aplicada",IF(J427="No","Sin multa",IF(H427="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="428" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="6" t="str">
@@ -24086,10 +22383,6 @@
       <c r="K428" s="15"/>
       <c r="L428" s="16"/>
       <c r="M428" s="17"/>
-      <c r="N428" s="18" t="str">
-        <f aca="false">IF(B428="","",IF(J428="Sí","Multa aplicada",IF(J428="No","Sin multa",IF(H428="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="429" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="6" t="str">
@@ -24126,10 +22419,6 @@
       <c r="K429" s="15"/>
       <c r="L429" s="16"/>
       <c r="M429" s="17"/>
-      <c r="N429" s="18" t="str">
-        <f aca="false">IF(B429="","",IF(J429="Sí","Multa aplicada",IF(J429="No","Sin multa",IF(H429="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="430" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="6" t="str">
@@ -24166,10 +22455,6 @@
       <c r="K430" s="15"/>
       <c r="L430" s="16"/>
       <c r="M430" s="17"/>
-      <c r="N430" s="18" t="str">
-        <f aca="false">IF(B430="","",IF(J430="Sí","Multa aplicada",IF(J430="No","Sin multa",IF(H430="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="431" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="6" t="str">
@@ -24206,10 +22491,6 @@
       <c r="K431" s="15"/>
       <c r="L431" s="16"/>
       <c r="M431" s="17"/>
-      <c r="N431" s="18" t="str">
-        <f aca="false">IF(B431="","",IF(J431="Sí","Multa aplicada",IF(J431="No","Sin multa",IF(H431="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="432" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="6" t="str">
@@ -24246,10 +22527,6 @@
       <c r="K432" s="15"/>
       <c r="L432" s="16"/>
       <c r="M432" s="17"/>
-      <c r="N432" s="18" t="str">
-        <f aca="false">IF(B432="","",IF(J432="Sí","Multa aplicada",IF(J432="No","Sin multa",IF(H432="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="433" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="6" t="str">
@@ -24286,10 +22563,6 @@
       <c r="K433" s="15"/>
       <c r="L433" s="16"/>
       <c r="M433" s="17"/>
-      <c r="N433" s="18" t="str">
-        <f aca="false">IF(B433="","",IF(J433="Sí","Multa aplicada",IF(J433="No","Sin multa",IF(H433="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="434" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="6" t="str">
@@ -24326,10 +22599,6 @@
       <c r="K434" s="15"/>
       <c r="L434" s="16"/>
       <c r="M434" s="17"/>
-      <c r="N434" s="18" t="str">
-        <f aca="false">IF(B434="","",IF(J434="Sí","Multa aplicada",IF(J434="No","Sin multa",IF(H434="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="435" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="6" t="str">
@@ -24366,10 +22635,6 @@
       <c r="K435" s="15"/>
       <c r="L435" s="16"/>
       <c r="M435" s="17"/>
-      <c r="N435" s="18" t="str">
-        <f aca="false">IF(B435="","",IF(J435="Sí","Multa aplicada",IF(J435="No","Sin multa",IF(H435="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="436" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="6" t="str">
@@ -24406,10 +22671,6 @@
       <c r="K436" s="15"/>
       <c r="L436" s="16"/>
       <c r="M436" s="17"/>
-      <c r="N436" s="18" t="str">
-        <f aca="false">IF(B436="","",IF(J436="Sí","Multa aplicada",IF(J436="No","Sin multa",IF(H436="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="437" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="6" t="str">
@@ -24446,10 +22707,6 @@
       <c r="K437" s="15"/>
       <c r="L437" s="16"/>
       <c r="M437" s="17"/>
-      <c r="N437" s="18" t="str">
-        <f aca="false">IF(B437="","",IF(J437="Sí","Multa aplicada",IF(J437="No","Sin multa",IF(H437="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="438" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="6" t="str">
@@ -24486,10 +22743,6 @@
       <c r="K438" s="15"/>
       <c r="L438" s="16"/>
       <c r="M438" s="17"/>
-      <c r="N438" s="18" t="str">
-        <f aca="false">IF(B438="","",IF(J438="Sí","Multa aplicada",IF(J438="No","Sin multa",IF(H438="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="439" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="6" t="str">
@@ -24526,10 +22779,6 @@
       <c r="K439" s="15"/>
       <c r="L439" s="16"/>
       <c r="M439" s="17"/>
-      <c r="N439" s="18" t="str">
-        <f aca="false">IF(B439="","",IF(J439="Sí","Multa aplicada",IF(J439="No","Sin multa",IF(H439="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="440" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="6" t="str">
@@ -24566,10 +22815,6 @@
       <c r="K440" s="15"/>
       <c r="L440" s="16"/>
       <c r="M440" s="17"/>
-      <c r="N440" s="18" t="str">
-        <f aca="false">IF(B440="","",IF(J440="Sí","Multa aplicada",IF(J440="No","Sin multa",IF(H440="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="441" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="6" t="str">
@@ -24606,10 +22851,6 @@
       <c r="K441" s="15"/>
       <c r="L441" s="16"/>
       <c r="M441" s="17"/>
-      <c r="N441" s="18" t="str">
-        <f aca="false">IF(B441="","",IF(J441="Sí","Multa aplicada",IF(J441="No","Sin multa",IF(H441="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="442" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="6" t="str">
@@ -24646,10 +22887,6 @@
       <c r="K442" s="15"/>
       <c r="L442" s="16"/>
       <c r="M442" s="17"/>
-      <c r="N442" s="18" t="str">
-        <f aca="false">IF(B442="","",IF(J442="Sí","Multa aplicada",IF(J442="No","Sin multa",IF(H442="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="443" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="6" t="str">
@@ -24686,10 +22923,6 @@
       <c r="K443" s="15"/>
       <c r="L443" s="16"/>
       <c r="M443" s="17"/>
-      <c r="N443" s="18" t="str">
-        <f aca="false">IF(B443="","",IF(J443="Sí","Multa aplicada",IF(J443="No","Sin multa",IF(H443="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="444" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="6" t="str">
@@ -24726,10 +22959,6 @@
       <c r="K444" s="15"/>
       <c r="L444" s="16"/>
       <c r="M444" s="17"/>
-      <c r="N444" s="18" t="str">
-        <f aca="false">IF(B444="","",IF(J444="Sí","Multa aplicada",IF(J444="No","Sin multa",IF(H444="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="445" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="6" t="str">
@@ -24766,10 +22995,6 @@
       <c r="K445" s="15"/>
       <c r="L445" s="16"/>
       <c r="M445" s="17"/>
-      <c r="N445" s="18" t="str">
-        <f aca="false">IF(B445="","",IF(J445="Sí","Multa aplicada",IF(J445="No","Sin multa",IF(H445="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="446" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="6" t="str">
@@ -24806,10 +23031,6 @@
       <c r="K446" s="15"/>
       <c r="L446" s="16"/>
       <c r="M446" s="17"/>
-      <c r="N446" s="18" t="str">
-        <f aca="false">IF(B446="","",IF(J446="Sí","Multa aplicada",IF(J446="No","Sin multa",IF(H446="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="447" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="6" t="str">
@@ -24846,10 +23067,6 @@
       <c r="K447" s="15"/>
       <c r="L447" s="16"/>
       <c r="M447" s="17"/>
-      <c r="N447" s="18" t="str">
-        <f aca="false">IF(B447="","",IF(J447="Sí","Multa aplicada",IF(J447="No","Sin multa",IF(H447="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="448" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="6" t="str">
@@ -24886,10 +23103,6 @@
       <c r="K448" s="15"/>
       <c r="L448" s="16"/>
       <c r="M448" s="17"/>
-      <c r="N448" s="18" t="str">
-        <f aca="false">IF(B448="","",IF(J448="Sí","Multa aplicada",IF(J448="No","Sin multa",IF(H448="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="449" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="6" t="str">
@@ -24926,10 +23139,6 @@
       <c r="K449" s="15"/>
       <c r="L449" s="16"/>
       <c r="M449" s="17"/>
-      <c r="N449" s="18" t="str">
-        <f aca="false">IF(B449="","",IF(J449="Sí","Multa aplicada",IF(J449="No","Sin multa",IF(H449="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="450" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="6" t="str">
@@ -24966,10 +23175,6 @@
       <c r="K450" s="15"/>
       <c r="L450" s="16"/>
       <c r="M450" s="17"/>
-      <c r="N450" s="18" t="str">
-        <f aca="false">IF(B450="","",IF(J450="Sí","Multa aplicada",IF(J450="No","Sin multa",IF(H450="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="451" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="6" t="str">
@@ -25006,10 +23211,6 @@
       <c r="K451" s="15"/>
       <c r="L451" s="16"/>
       <c r="M451" s="17"/>
-      <c r="N451" s="18" t="str">
-        <f aca="false">IF(B451="","",IF(J451="Sí","Multa aplicada",IF(J451="No","Sin multa",IF(H451="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="452" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="6" t="str">
@@ -25046,10 +23247,6 @@
       <c r="K452" s="15"/>
       <c r="L452" s="16"/>
       <c r="M452" s="17"/>
-      <c r="N452" s="18" t="str">
-        <f aca="false">IF(B452="","",IF(J452="Sí","Multa aplicada",IF(J452="No","Sin multa",IF(H452="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="453" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="6" t="str">
@@ -25086,10 +23283,6 @@
       <c r="K453" s="15"/>
       <c r="L453" s="16"/>
       <c r="M453" s="17"/>
-      <c r="N453" s="18" t="str">
-        <f aca="false">IF(B453="","",IF(J453="Sí","Multa aplicada",IF(J453="No","Sin multa",IF(H453="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="454" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="6" t="str">
@@ -25126,10 +23319,6 @@
       <c r="K454" s="15"/>
       <c r="L454" s="16"/>
       <c r="M454" s="17"/>
-      <c r="N454" s="18" t="str">
-        <f aca="false">IF(B454="","",IF(J454="Sí","Multa aplicada",IF(J454="No","Sin multa",IF(H454="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="455" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="6" t="str">
@@ -25166,10 +23355,6 @@
       <c r="K455" s="15"/>
       <c r="L455" s="16"/>
       <c r="M455" s="17"/>
-      <c r="N455" s="18" t="str">
-        <f aca="false">IF(B455="","",IF(J455="Sí","Multa aplicada",IF(J455="No","Sin multa",IF(H455="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="456" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="6" t="str">
@@ -25206,10 +23391,6 @@
       <c r="K456" s="15"/>
       <c r="L456" s="16"/>
       <c r="M456" s="17"/>
-      <c r="N456" s="18" t="str">
-        <f aca="false">IF(B456="","",IF(J456="Sí","Multa aplicada",IF(J456="No","Sin multa",IF(H456="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="457" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="6" t="str">
@@ -25246,10 +23427,6 @@
       <c r="K457" s="15"/>
       <c r="L457" s="16"/>
       <c r="M457" s="17"/>
-      <c r="N457" s="18" t="str">
-        <f aca="false">IF(B457="","",IF(J457="Sí","Multa aplicada",IF(J457="No","Sin multa",IF(H457="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="458" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="6" t="str">
@@ -25286,10 +23463,6 @@
       <c r="K458" s="15"/>
       <c r="L458" s="16"/>
       <c r="M458" s="17"/>
-      <c r="N458" s="18" t="str">
-        <f aca="false">IF(B458="","",IF(J458="Sí","Multa aplicada",IF(J458="No","Sin multa",IF(H458="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="459" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="6" t="str">
@@ -25326,10 +23499,6 @@
       <c r="K459" s="15"/>
       <c r="L459" s="16"/>
       <c r="M459" s="17"/>
-      <c r="N459" s="18" t="str">
-        <f aca="false">IF(B459="","",IF(J459="Sí","Multa aplicada",IF(J459="No","Sin multa",IF(H459="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="460" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="6" t="str">
@@ -25366,10 +23535,6 @@
       <c r="K460" s="15"/>
       <c r="L460" s="16"/>
       <c r="M460" s="17"/>
-      <c r="N460" s="18" t="str">
-        <f aca="false">IF(B460="","",IF(J460="Sí","Multa aplicada",IF(J460="No","Sin multa",IF(H460="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="461" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="6" t="str">
@@ -25406,10 +23571,6 @@
       <c r="K461" s="15"/>
       <c r="L461" s="16"/>
       <c r="M461" s="17"/>
-      <c r="N461" s="18" t="str">
-        <f aca="false">IF(B461="","",IF(J461="Sí","Multa aplicada",IF(J461="No","Sin multa",IF(H461="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="462" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="6" t="str">
@@ -25446,10 +23607,6 @@
       <c r="K462" s="15"/>
       <c r="L462" s="16"/>
       <c r="M462" s="17"/>
-      <c r="N462" s="18" t="str">
-        <f aca="false">IF(B462="","",IF(J462="Sí","Multa aplicada",IF(J462="No","Sin multa",IF(H462="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="463" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="6" t="str">
@@ -25486,10 +23643,6 @@
       <c r="K463" s="15"/>
       <c r="L463" s="16"/>
       <c r="M463" s="17"/>
-      <c r="N463" s="18" t="str">
-        <f aca="false">IF(B463="","",IF(J463="Sí","Multa aplicada",IF(J463="No","Sin multa",IF(H463="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="464" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="6" t="str">
@@ -25526,10 +23679,6 @@
       <c r="K464" s="15"/>
       <c r="L464" s="16"/>
       <c r="M464" s="17"/>
-      <c r="N464" s="18" t="str">
-        <f aca="false">IF(B464="","",IF(J464="Sí","Multa aplicada",IF(J464="No","Sin multa",IF(H464="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="465" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="6" t="str">
@@ -25566,10 +23715,6 @@
       <c r="K465" s="15"/>
       <c r="L465" s="16"/>
       <c r="M465" s="17"/>
-      <c r="N465" s="18" t="str">
-        <f aca="false">IF(B465="","",IF(J465="Sí","Multa aplicada",IF(J465="No","Sin multa",IF(H465="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="466" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="6" t="str">
@@ -25606,10 +23751,6 @@
       <c r="K466" s="15"/>
       <c r="L466" s="16"/>
       <c r="M466" s="17"/>
-      <c r="N466" s="18" t="str">
-        <f aca="false">IF(B466="","",IF(J466="Sí","Multa aplicada",IF(J466="No","Sin multa",IF(H466="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="467" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="6" t="str">
@@ -25646,10 +23787,6 @@
       <c r="K467" s="15"/>
       <c r="L467" s="16"/>
       <c r="M467" s="17"/>
-      <c r="N467" s="18" t="str">
-        <f aca="false">IF(B467="","",IF(J467="Sí","Multa aplicada",IF(J467="No","Sin multa",IF(H467="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="468" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="6" t="str">
@@ -25686,10 +23823,6 @@
       <c r="K468" s="15"/>
       <c r="L468" s="16"/>
       <c r="M468" s="17"/>
-      <c r="N468" s="18" t="str">
-        <f aca="false">IF(B468="","",IF(J468="Sí","Multa aplicada",IF(J468="No","Sin multa",IF(H468="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="469" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="6" t="str">
@@ -25726,10 +23859,6 @@
       <c r="K469" s="15"/>
       <c r="L469" s="16"/>
       <c r="M469" s="17"/>
-      <c r="N469" s="18" t="str">
-        <f aca="false">IF(B469="","",IF(J469="Sí","Multa aplicada",IF(J469="No","Sin multa",IF(H469="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="470" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="6" t="str">
@@ -25766,10 +23895,6 @@
       <c r="K470" s="15"/>
       <c r="L470" s="16"/>
       <c r="M470" s="17"/>
-      <c r="N470" s="18" t="str">
-        <f aca="false">IF(B470="","",IF(J470="Sí","Multa aplicada",IF(J470="No","Sin multa",IF(H470="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="471" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="6" t="str">
@@ -25806,10 +23931,6 @@
       <c r="K471" s="15"/>
       <c r="L471" s="16"/>
       <c r="M471" s="17"/>
-      <c r="N471" s="18" t="str">
-        <f aca="false">IF(B471="","",IF(J471="Sí","Multa aplicada",IF(J471="No","Sin multa",IF(H471="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="472" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="6" t="str">
@@ -25846,10 +23967,6 @@
       <c r="K472" s="15"/>
       <c r="L472" s="16"/>
       <c r="M472" s="17"/>
-      <c r="N472" s="18" t="str">
-        <f aca="false">IF(B472="","",IF(J472="Sí","Multa aplicada",IF(J472="No","Sin multa",IF(H472="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="473" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="6" t="str">
@@ -25886,10 +24003,6 @@
       <c r="K473" s="15"/>
       <c r="L473" s="16"/>
       <c r="M473" s="17"/>
-      <c r="N473" s="18" t="str">
-        <f aca="false">IF(B473="","",IF(J473="Sí","Multa aplicada",IF(J473="No","Sin multa",IF(H473="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="474" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="6" t="str">
@@ -25926,10 +24039,6 @@
       <c r="K474" s="15"/>
       <c r="L474" s="16"/>
       <c r="M474" s="17"/>
-      <c r="N474" s="18" t="str">
-        <f aca="false">IF(B474="","",IF(J474="Sí","Multa aplicada",IF(J474="No","Sin multa",IF(H474="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="475" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="6" t="str">
@@ -25966,10 +24075,6 @@
       <c r="K475" s="15"/>
       <c r="L475" s="16"/>
       <c r="M475" s="17"/>
-      <c r="N475" s="18" t="str">
-        <f aca="false">IF(B475="","",IF(J475="Sí","Multa aplicada",IF(J475="No","Sin multa",IF(H475="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="476" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="6" t="str">
@@ -26006,10 +24111,6 @@
       <c r="K476" s="15"/>
       <c r="L476" s="16"/>
       <c r="M476" s="17"/>
-      <c r="N476" s="18" t="str">
-        <f aca="false">IF(B476="","",IF(J476="Sí","Multa aplicada",IF(J476="No","Sin multa",IF(H476="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="477" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="6" t="str">
@@ -26046,10 +24147,6 @@
       <c r="K477" s="15"/>
       <c r="L477" s="16"/>
       <c r="M477" s="17"/>
-      <c r="N477" s="18" t="str">
-        <f aca="false">IF(B477="","",IF(J477="Sí","Multa aplicada",IF(J477="No","Sin multa",IF(H477="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="478" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="6" t="str">
@@ -26086,10 +24183,6 @@
       <c r="K478" s="15"/>
       <c r="L478" s="16"/>
       <c r="M478" s="17"/>
-      <c r="N478" s="18" t="str">
-        <f aca="false">IF(B478="","",IF(J478="Sí","Multa aplicada",IF(J478="No","Sin multa",IF(H478="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="479" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="6" t="str">
@@ -26126,10 +24219,6 @@
       <c r="K479" s="15"/>
       <c r="L479" s="16"/>
       <c r="M479" s="17"/>
-      <c r="N479" s="18" t="str">
-        <f aca="false">IF(B479="","",IF(J479="Sí","Multa aplicada",IF(J479="No","Sin multa",IF(H479="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="480" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A480" s="6" t="str">
@@ -26166,10 +24255,6 @@
       <c r="K480" s="15"/>
       <c r="L480" s="16"/>
       <c r="M480" s="17"/>
-      <c r="N480" s="18" t="str">
-        <f aca="false">IF(B480="","",IF(J480="Sí","Multa aplicada",IF(J480="No","Sin multa",IF(H480="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="481" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A481" s="6" t="str">
@@ -26206,10 +24291,6 @@
       <c r="K481" s="15"/>
       <c r="L481" s="16"/>
       <c r="M481" s="17"/>
-      <c r="N481" s="18" t="str">
-        <f aca="false">IF(B481="","",IF(J481="Sí","Multa aplicada",IF(J481="No","Sin multa",IF(H481="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="482" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A482" s="6" t="str">
@@ -26246,10 +24327,6 @@
       <c r="K482" s="15"/>
       <c r="L482" s="16"/>
       <c r="M482" s="17"/>
-      <c r="N482" s="18" t="str">
-        <f aca="false">IF(B482="","",IF(J482="Sí","Multa aplicada",IF(J482="No","Sin multa",IF(H482="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="483" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A483" s="6" t="str">
@@ -26286,10 +24363,6 @@
       <c r="K483" s="15"/>
       <c r="L483" s="16"/>
       <c r="M483" s="17"/>
-      <c r="N483" s="18" t="str">
-        <f aca="false">IF(B483="","",IF(J483="Sí","Multa aplicada",IF(J483="No","Sin multa",IF(H483="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="484" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="6" t="str">
@@ -26326,10 +24399,6 @@
       <c r="K484" s="15"/>
       <c r="L484" s="16"/>
       <c r="M484" s="17"/>
-      <c r="N484" s="18" t="str">
-        <f aca="false">IF(B484="","",IF(J484="Sí","Multa aplicada",IF(J484="No","Sin multa",IF(H484="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="485" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="6" t="str">
@@ -26366,10 +24435,6 @@
       <c r="K485" s="15"/>
       <c r="L485" s="16"/>
       <c r="M485" s="17"/>
-      <c r="N485" s="18" t="str">
-        <f aca="false">IF(B485="","",IF(J485="Sí","Multa aplicada",IF(J485="No","Sin multa",IF(H485="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="486" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A486" s="6" t="str">
@@ -26406,10 +24471,6 @@
       <c r="K486" s="15"/>
       <c r="L486" s="16"/>
       <c r="M486" s="17"/>
-      <c r="N486" s="18" t="str">
-        <f aca="false">IF(B486="","",IF(J486="Sí","Multa aplicada",IF(J486="No","Sin multa",IF(H486="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="487" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="6" t="str">
@@ -26446,10 +24507,6 @@
       <c r="K487" s="15"/>
       <c r="L487" s="16"/>
       <c r="M487" s="17"/>
-      <c r="N487" s="18" t="str">
-        <f aca="false">IF(B487="","",IF(J487="Sí","Multa aplicada",IF(J487="No","Sin multa",IF(H487="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="488" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A488" s="6" t="str">
@@ -26486,10 +24543,6 @@
       <c r="K488" s="15"/>
       <c r="L488" s="16"/>
       <c r="M488" s="17"/>
-      <c r="N488" s="18" t="str">
-        <f aca="false">IF(B488="","",IF(J488="Sí","Multa aplicada",IF(J488="No","Sin multa",IF(H488="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="489" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A489" s="6" t="str">
@@ -26526,10 +24579,6 @@
       <c r="K489" s="15"/>
       <c r="L489" s="16"/>
       <c r="M489" s="17"/>
-      <c r="N489" s="18" t="str">
-        <f aca="false">IF(B489="","",IF(J489="Sí","Multa aplicada",IF(J489="No","Sin multa",IF(H489="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="490" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A490" s="6" t="str">
@@ -26566,10 +24615,6 @@
       <c r="K490" s="15"/>
       <c r="L490" s="16"/>
       <c r="M490" s="17"/>
-      <c r="N490" s="18" t="str">
-        <f aca="false">IF(B490="","",IF(J490="Sí","Multa aplicada",IF(J490="No","Sin multa",IF(H490="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="491" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="6" t="str">
@@ -26606,10 +24651,6 @@
       <c r="K491" s="15"/>
       <c r="L491" s="16"/>
       <c r="M491" s="17"/>
-      <c r="N491" s="18" t="str">
-        <f aca="false">IF(B491="","",IF(J491="Sí","Multa aplicada",IF(J491="No","Sin multa",IF(H491="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="492" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A492" s="6" t="str">
@@ -26646,10 +24687,6 @@
       <c r="K492" s="15"/>
       <c r="L492" s="16"/>
       <c r="M492" s="17"/>
-      <c r="N492" s="18" t="str">
-        <f aca="false">IF(B492="","",IF(J492="Sí","Multa aplicada",IF(J492="No","Sin multa",IF(H492="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="493" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A493" s="6" t="str">
@@ -26686,10 +24723,6 @@
       <c r="K493" s="15"/>
       <c r="L493" s="16"/>
       <c r="M493" s="17"/>
-      <c r="N493" s="18" t="str">
-        <f aca="false">IF(B493="","",IF(J493="Sí","Multa aplicada",IF(J493="No","Sin multa",IF(H493="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="494" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A494" s="6" t="str">
@@ -26726,10 +24759,6 @@
       <c r="K494" s="15"/>
       <c r="L494" s="16"/>
       <c r="M494" s="17"/>
-      <c r="N494" s="18" t="str">
-        <f aca="false">IF(B494="","",IF(J494="Sí","Multa aplicada",IF(J494="No","Sin multa",IF(H494="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="495" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A495" s="6" t="str">
@@ -26766,10 +24795,6 @@
       <c r="K495" s="15"/>
       <c r="L495" s="16"/>
       <c r="M495" s="17"/>
-      <c r="N495" s="18" t="str">
-        <f aca="false">IF(B495="","",IF(J495="Sí","Multa aplicada",IF(J495="No","Sin multa",IF(H495="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="496" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A496" s="6" t="str">
@@ -26806,10 +24831,6 @@
       <c r="K496" s="15"/>
       <c r="L496" s="16"/>
       <c r="M496" s="17"/>
-      <c r="N496" s="18" t="str">
-        <f aca="false">IF(B496="","",IF(J496="Sí","Multa aplicada",IF(J496="No","Sin multa",IF(H496="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="497" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A497" s="6" t="str">
@@ -26846,10 +24867,6 @@
       <c r="K497" s="15"/>
       <c r="L497" s="16"/>
       <c r="M497" s="17"/>
-      <c r="N497" s="18" t="str">
-        <f aca="false">IF(B497="","",IF(J497="Sí","Multa aplicada",IF(J497="No","Sin multa",IF(H497="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="498" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A498" s="6" t="str">
@@ -26886,10 +24903,6 @@
       <c r="K498" s="15"/>
       <c r="L498" s="16"/>
       <c r="M498" s="17"/>
-      <c r="N498" s="18" t="str">
-        <f aca="false">IF(B498="","",IF(J498="Sí","Multa aplicada",IF(J498="No","Sin multa",IF(H498="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="499" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A499" s="6" t="str">
@@ -26926,10 +24939,6 @@
       <c r="K499" s="15"/>
       <c r="L499" s="16"/>
       <c r="M499" s="17"/>
-      <c r="N499" s="18" t="str">
-        <f aca="false">IF(B499="","",IF(J499="Sí","Multa aplicada",IF(J499="No","Sin multa",IF(H499="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="500" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A500" s="6" t="str">
@@ -26966,10 +24975,6 @@
       <c r="K500" s="15"/>
       <c r="L500" s="16"/>
       <c r="M500" s="17"/>
-      <c r="N500" s="18" t="str">
-        <f aca="false">IF(B500="","",IF(J500="Sí","Multa aplicada",IF(J500="No","Sin multa",IF(H500="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="501" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A501" s="6" t="str">
@@ -27006,10 +25011,6 @@
       <c r="K501" s="15"/>
       <c r="L501" s="16"/>
       <c r="M501" s="17"/>
-      <c r="N501" s="18" t="str">
-        <f aca="false">IF(B501="","",IF(J501="Sí","Multa aplicada",IF(J501="No","Sin multa",IF(H501="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="502" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A502" s="6" t="str">
@@ -27046,10 +25047,6 @@
       <c r="K502" s="15"/>
       <c r="L502" s="16"/>
       <c r="M502" s="17"/>
-      <c r="N502" s="18" t="str">
-        <f aca="false">IF(B502="","",IF(J502="Sí","Multa aplicada",IF(J502="No","Sin multa",IF(H502="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
     <row r="503" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A503" s="6" t="str">
@@ -27086,30 +25083,27 @@
       <c r="K503" s="15"/>
       <c r="L503" s="16"/>
       <c r="M503" s="17"/>
-      <c r="N503" s="18" t="str">
-        <f aca="false">IF(B503="","",IF(J503="Sí","Multa aplicada",IF(J503="No","Sin multa",IF(H503="Sí","Descargo enviado","Pendiente"))))</f>
-        <v/>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N503"/>
-  <conditionalFormatting sqref="N4:N503">
+  <autoFilter ref="A3:M503"/>
+  <conditionalFormatting sqref="J4:J503">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>N4="Pendiente"</formula>
+      <formula>J4="PENDIENTE"</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
-      <formula>N4="Descargo enviado"</formula>
+      <formula>J4="MULTA APLICADA"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
-      <formula>N4="Multa aplicada"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
-      <formula>N4="Sin multa"</formula>
+      <formula>J4="MULTA DE BAJA"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation allowBlank="true" error="Elegir Sí o No" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H4:H503 J4:J503" type="list">
-      <formula1>"Sí,No"</formula1>
+  <dataValidations count="3">
+    <dataValidation allowBlank="true" error="Elegir SI o NO" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="H4:H503" type="list">
+      <formula1>"SI,NO"</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Elegir PENDIENTE, MULTA APLICADA o MULTA DE BAJA" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="J4:J503" type="list">
+      <formula1>"PENDIENTE,MULTA APLICADA,MULTA DE BAJA"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" error="Ingresar fecha dd/mm/aaaa" errorStyle="stop" errorTitle="Fecha" operator="greaterThan" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="I4:I503 K4:K503" type="date">
@@ -27133,7 +25127,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -27152,99 +25146,111 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="20" t="n">
+      <c r="B4" s="19" t="n">
         <v>46296</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="20" t="n">
+      <c r="B5" s="19" t="n">
         <v>46326</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="21"/>
+      <c r="B6" s="20"/>
       <c r="C6" s="4" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="21" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="24" t="n">
+      <c r="B9" s="23" t="n">
         <f aca="false">IF($B$6="",COUNTIFS('Carga Administración'!$B$4:$B$503,"&gt;="&amp;$B$4,'Carga Administración'!$B$4:$B$503,"&lt;="&amp;$B$5),COUNTIFS('Carga Administración'!$B$4:$B$503,"&gt;="&amp;$B$4,'Carga Administración'!$B$4:$B$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6))</f>
         <v>1</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="24" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="24" t="n">
-        <f aca="false">IF($B$6="",COUNTIFS('Carga Administración'!$H$4:$H$503,"Sí",'Carga Administración'!$I$4:$I$503,"&gt;="&amp;$B$4,'Carga Administración'!$I$4:$I$503,"&lt;="&amp;$B$5),COUNTIFS('Carga Administración'!$H$4:$H$503,"Sí",'Carga Administración'!$I$4:$I$503,"&gt;="&amp;$B$4,'Carga Administración'!$I$4:$I$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6))</f>
+      <c r="B10" s="23" t="n">
+        <f aca="false">IF($B$6="",COUNTIFS('Carga Administración'!$H$4:$H$503,"SI",'Carga Administración'!$I$4:$I$503,"&gt;="&amp;$B$4,'Carga Administración'!$I$4:$I$503,"&lt;="&amp;$B$5),COUNTIFS('Carga Administración'!$H$4:$H$503,"SI",'Carga Administración'!$I$4:$I$503,"&gt;="&amp;$B$4,'Carga Administración'!$I$4:$I$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6))</f>
         <v>0</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="24" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="24" t="n">
-        <f aca="false">IF($B$6="",COUNTIFS('Carga Administración'!$J$4:$J$503,"Sí",'Carga Administración'!$K$4:$K$503,"&gt;="&amp;$B$4,'Carga Administración'!$K$4:$K$503,"&lt;="&amp;$B$5),COUNTIFS('Carga Administración'!$J$4:$J$503,"Sí",'Carga Administración'!$K$4:$K$503,"&gt;="&amp;$B$4,'Carga Administración'!$K$4:$K$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6))</f>
+      <c r="B11" s="23" t="n">
+        <f aca="false">IF($B$6="",COUNTIFS('Carga Administración'!$J$4:$J$503,"MULTA APLICADA",'Carga Administración'!$K$4:$K$503,"&gt;="&amp;$B$4,'Carga Administración'!$K$4:$K$503,"&lt;="&amp;$B$5),COUNTIFS('Carga Administración'!$J$4:$J$503,"MULTA APLICADA",'Carga Administración'!$K$4:$K$503,"&gt;="&amp;$B$4,'Carga Administración'!$K$4:$K$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6))</f>
         <v>0</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="24" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B12" s="26" t="n">
-        <f aca="false">IF($B$6="",SUMIFS('Carga Administración'!$L$4:$L$503,'Carga Administración'!$J$4:$J$503,"Sí",'Carga Administración'!$K$4:$K$503,"&gt;="&amp;$B$4,'Carga Administración'!$K$4:$K$503,"&lt;="&amp;$B$5),SUMIFS('Carga Administración'!$L$4:$L$503,'Carga Administración'!$J$4:$J$503,"Sí",'Carga Administración'!$K$4:$K$503,"&gt;="&amp;$B$4,'Carga Administración'!$K$4:$K$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6))</f>
+      <c r="B12" s="25" t="n">
+        <f aca="false">IF($B$6="",SUMIFS('Carga Administración'!$L$4:$L$503,'Carga Administración'!$J$4:$J$503,"MULTA APLICADA",'Carga Administración'!$K$4:$K$503,"&gt;="&amp;$B$4,'Carga Administración'!$K$4:$K$503,"&lt;="&amp;$B$5),SUMIFS('Carga Administración'!$L$4:$L$503,'Carga Administración'!$J$4:$J$503,"MULTA APLICADA",'Carga Administración'!$K$4:$K$503,"&gt;="&amp;$B$4,'Carga Administración'!$K$4:$K$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6))</f>
         <v>0</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="24" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="24" t="n">
-        <f aca="false">IF($B$6="",COUNTIFS('Carga Administración'!$N$4:$N$503,"Pendiente",'Carga Administración'!$B$4:$B$503,"&gt;="&amp;$B$4,'Carga Administración'!$B$4:$B$503,"&lt;="&amp;$B$5),COUNTIFS('Carga Administración'!$N$4:$N$503,"Pendiente",'Carga Administración'!$B$4:$B$503,"&gt;="&amp;$B$4,'Carga Administración'!$B$4:$B$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6))</f>
+      <c r="B13" s="23" t="n">
+        <f aca="false">IF($B$6="",COUNTIFS('Carga Administración'!$J$4:$J$503,"MULTA DE BAJA",'Carga Administración'!$K$4:$K$503,"&gt;="&amp;$B$4,'Carga Administración'!$K$4:$K$503,"&lt;="&amp;$B$5),COUNTIFS('Carga Administración'!$J$4:$J$503,"MULTA DE BAJA",'Carga Administración'!$K$4:$K$503,"&gt;="&amp;$B$4,'Carga Administración'!$K$4:$K$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6))</f>
+        <v>0</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="23" t="n">
+        <f aca="false">B9-(IF($B$6="",COUNTIFS('Carga Administración'!$J$4:$J$503,"MULTA APLICADA",'Carga Administración'!$B$4:$B$503,"&gt;="&amp;$B$4,'Carga Administración'!$B$4:$B$503,"&lt;="&amp;$B$5),COUNTIFS('Carga Administración'!$J$4:$J$503,"MULTA APLICADA",'Carga Administración'!$B$4:$B$503,"&gt;="&amp;$B$4,'Carga Administración'!$B$4:$B$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6)))-(IF($B$6="",COUNTIFS('Carga Administración'!$J$4:$J$503,"MULTA DE BAJA",'Carga Administración'!$B$4:$B$503,"&gt;="&amp;$B$4,'Carga Administración'!$B$4:$B$503,"&lt;="&amp;$B$5),COUNTIFS('Carga Administración'!$J$4:$J$503,"MULTA DE BAJA",'Carga Administración'!$B$4:$B$503,"&gt;="&amp;$B$4,'Carga Administración'!$B$4:$B$503,"&lt;="&amp;$B$5,'Carga Administración'!$E$4:$E$503,$B$6)))</f>
         <v>1</v>
       </c>
-      <c r="C13" s="25" t="s">
-        <v>52</v>
+      <c r="C14" s="24" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
